--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
@@ -567,16 +567,16 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>22.95</v>
+        <v>29.1</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>122947.88</v>
+        <v>129095.28</v>
       </c>
     </row>
     <row r="3">
@@ -593,11 +593,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F3" t="n">
         <v>5</v>
@@ -638,11 +638,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -683,11 +683,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -728,11 +728,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -773,11 +773,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -818,11 +818,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -863,11 +863,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -908,11 +908,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -953,11 +953,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
@@ -998,11 +998,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1040,11 +1040,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1124,11 +1124,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1166,11 +1166,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1208,11 +1208,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1250,11 +1250,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F18" t="n">
         <v>6</v>
@@ -1295,11 +1295,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -1340,11 +1340,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1385,11 +1385,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -1430,11 +1430,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -1520,11 +1520,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
@@ -1565,11 +1565,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F25" t="n">
         <v>2</v>
@@ -1610,11 +1610,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -2414,7 +2414,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily, starting capital 100,000, risk 1.0%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-20). generated 2026-07-23 22:01 UTC.</t>
+          <t>quickfix daily (target = 5R, or an opposite reversal nearer than 5R), starting capital 100,000, risk 1.0%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-23). generated 2026-07-25 00:34 UTC.</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -3016,7 +3016,7 @@
         <v>570.9</v>
       </c>
       <c r="I10" t="n">
-        <v>610.5</v>
+        <v>610</v>
       </c>
       <c r="J10" t="n">
         <v>610</v>
@@ -4691,6 +4691,14 @@
           <t>2026-07-17</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
       <c r="G40" t="n">
         <v>3984</v>
       </c>
@@ -4700,16 +4708,25 @@
       <c r="I40" t="n">
         <v>4089.5</v>
       </c>
+      <c r="J40" t="n">
+        <v>4089.5</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>target_5r</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>5</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="N40" t="n">
         <v>122947.88</v>
       </c>
       <c r="O40" t="n">
-        <v>122947.88</v>
+        <v>129095.28</v>
       </c>
     </row>
     <row r="41">
@@ -4746,7 +4763,7 @@
         <v>0.006454</v>
       </c>
       <c r="I41" t="n">
-        <v>0.006232</v>
+        <v>0.006254</v>
       </c>
       <c r="J41" t="n">
         <v>0.006454</v>
@@ -5088,7 +5105,7 @@
         <v>5.6774</v>
       </c>
       <c r="I47" t="n">
-        <v>6.2414</v>
+        <v>6.116</v>
       </c>
       <c r="J47" t="n">
         <v>5.6774</v>
@@ -5259,7 +5276,7 @@
         <v>3.354</v>
       </c>
       <c r="I50" t="n">
-        <v>3.06</v>
+        <v>3.095</v>
       </c>
       <c r="J50" t="n">
         <v>3.354</v>
@@ -5316,7 +5333,7 @@
         <v>3.356</v>
       </c>
       <c r="I51" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="J51" t="n">
         <v>3.12</v>
@@ -6393,7 +6410,7 @@
         <v>0.8658</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8394</v>
+        <v>0.8418</v>
       </c>
       <c r="J70" t="n">
         <v>0.8658</v>
@@ -6604,7 +6621,7 @@
         <v>97.569</v>
       </c>
       <c r="I74" t="n">
-        <v>99.039</v>
+        <v>98.976</v>
       </c>
       <c r="J74" t="n">
         <v>97.569</v>
@@ -6775,7 +6792,7 @@
         <v>100.361</v>
       </c>
       <c r="I77" t="n">
-        <v>98.59099999999999</v>
+        <v>99.004</v>
       </c>
       <c r="J77" t="n">
         <v>100.361</v>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -461,10 +461,11 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,20 +516,25 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>data_end</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>open_at_end</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>win_rate_%</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>return_%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>final_equity</t>
         </is>
@@ -570,12 +576,15 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>66.7</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="M2" s="2" t="n">
         <v>29.1</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="N2" s="3" t="n">
         <v>129095.28</v>
       </c>
     </row>
@@ -615,12 +624,15 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>80</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="M3" s="2" t="n">
         <v>20.25</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="N3" s="3" t="n">
         <v>120248.3</v>
       </c>
     </row>
@@ -660,12 +672,15 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>100</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="M4" s="2" t="n">
         <v>10.25</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="N4" s="3" t="n">
         <v>110250</v>
       </c>
     </row>
@@ -705,12 +720,15 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>66.7</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="M5" s="2" t="n">
         <v>9.15</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="N5" s="3" t="n">
         <v>109147.5</v>
       </c>
     </row>
@@ -750,12 +768,15 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>50</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="M6" s="2" t="n">
         <v>8.06</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="N6" s="3" t="n">
         <v>108056.02</v>
       </c>
     </row>
@@ -795,12 +816,15 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>100</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="M7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="N7" s="3" t="n">
         <v>105000</v>
       </c>
     </row>
@@ -840,12 +864,15 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>50</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="M8" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="N8" s="3" t="n">
         <v>103950</v>
       </c>
     </row>
@@ -885,12 +912,15 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>33.3</v>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="M9" s="2" t="n">
         <v>2.91</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="N9" s="3" t="n">
         <v>102910.5</v>
       </c>
     </row>
@@ -930,12 +960,15 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>50</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="M10" s="2" t="n">
         <v>2.59</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="N10" s="3" t="n">
         <v>102591.18</v>
       </c>
     </row>
@@ -975,12 +1008,15 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>25</v>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="M11" s="2" t="n">
         <v>1.88</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="N11" s="3" t="n">
         <v>101881.4</v>
       </c>
     </row>
@@ -1019,10 +1055,13 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1061,10 +1100,13 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1103,10 +1145,13 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1145,10 +1190,13 @@
       <c r="J15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1187,10 +1235,13 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1229,10 +1280,13 @@
       <c r="J17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1272,12 +1326,15 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>16.7</v>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="M18" s="5" t="n">
         <v>-0.15</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="N18" s="3" t="n">
         <v>99853.96000000001</v>
       </c>
     </row>
@@ -1314,15 +1371,18 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N19" s="3" t="n">
         <v>99000</v>
       </c>
     </row>
@@ -1364,10 +1424,13 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M20" s="3" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N20" s="3" t="n">
         <v>99000</v>
       </c>
     </row>
@@ -1409,10 +1472,13 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M21" s="3" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N21" s="3" t="n">
         <v>99000</v>
       </c>
     </row>
@@ -1454,10 +1520,13 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M22" s="3" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N22" s="3" t="n">
         <v>99000</v>
       </c>
     </row>
@@ -1499,10 +1568,13 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M23" s="3" t="n">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N23" s="3" t="n">
         <v>99000</v>
       </c>
     </row>
@@ -1544,10 +1616,13 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="5" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5" t="n">
         <v>-1.99</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="N24" s="3" t="n">
         <v>98010</v>
       </c>
     </row>
@@ -1589,10 +1664,13 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="5" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="5" t="n">
         <v>-1.99</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="N25" s="3" t="n">
         <v>98010</v>
       </c>
     </row>
@@ -1634,10 +1712,13 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="5" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="5" t="n">
         <v>-2.97</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="N26" s="3" t="n">
         <v>97029.89999999999</v>
       </c>
     </row>
@@ -1681,12 +1762,15 @@
         <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="L27" s="7" t="n">
+      <c r="M27" s="7" t="n">
         <v>10.25</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="N27" s="8" t="n">
         <v>110250</v>
       </c>
     </row>
@@ -1730,12 +1814,15 @@
         <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="6" t="n">
         <v>66.7</v>
       </c>
-      <c r="L28" s="7" t="n">
+      <c r="M28" s="7" t="n">
         <v>9.15</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="N28" s="8" t="n">
         <v>109147.5</v>
       </c>
     </row>
@@ -1779,12 +1866,15 @@
         <v>0</v>
       </c>
       <c r="K29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="6" t="n">
         <v>33.3</v>
       </c>
-      <c r="L29" s="7" t="n">
+      <c r="M29" s="7" t="n">
         <v>5.91</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="N29" s="8" t="n">
         <v>105905.71</v>
       </c>
     </row>
@@ -1828,12 +1918,15 @@
         <v>0</v>
       </c>
       <c r="K30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="L30" s="7" t="n">
+      <c r="M30" s="7" t="n">
         <v>5.35</v>
       </c>
-      <c r="M30" s="8" t="n">
+      <c r="N30" s="8" t="n">
         <v>105352.81</v>
       </c>
     </row>
@@ -1877,12 +1970,15 @@
         <v>0</v>
       </c>
       <c r="K31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="L31" s="7" t="n">
+      <c r="M31" s="7" t="n">
         <v>3.95</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="N31" s="8" t="n">
         <v>103950</v>
       </c>
     </row>
@@ -1926,12 +2022,15 @@
         <v>0</v>
       </c>
       <c r="K32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="L32" s="7" t="n">
+      <c r="M32" s="7" t="n">
         <v>3.28</v>
       </c>
-      <c r="M32" s="8" t="n">
+      <c r="N32" s="8" t="n">
         <v>103277.04</v>
       </c>
     </row>
@@ -1974,11 +2073,14 @@
       <c r="J33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="6" t="n"/>
-      <c r="L33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="8" t="n">
+      <c r="K33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="6" t="n"/>
+      <c r="M33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="8" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -2021,11 +2123,14 @@
       <c r="J34" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K34" s="6" t="n"/>
-      <c r="L34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="8" t="n">
+      <c r="K34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="6" t="n"/>
+      <c r="M34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="8" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -2068,11 +2173,14 @@
       <c r="J35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K35" s="6" t="n"/>
-      <c r="L35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="8" t="n">
+      <c r="K35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="6" t="n"/>
+      <c r="M35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="8" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -2115,11 +2223,14 @@
       <c r="J36" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K36" s="6" t="n"/>
-      <c r="L36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="8" t="n">
+      <c r="K36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="6" t="n"/>
+      <c r="M36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="8" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -2162,11 +2273,14 @@
       <c r="J37" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K37" s="6" t="n"/>
-      <c r="L37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="8" t="n">
+      <c r="K37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="6" t="n"/>
+      <c r="M37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="8" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -2209,11 +2323,14 @@
       <c r="J38" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K38" s="6" t="n"/>
-      <c r="L38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="8" t="n">
+      <c r="K38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="6" t="n"/>
+      <c r="M38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="8" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -2256,11 +2373,14 @@
       <c r="J39" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K39" s="6" t="n"/>
-      <c r="L39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="8" t="n">
+      <c r="K39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="6" t="n"/>
+      <c r="M39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="8" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -2306,10 +2426,13 @@
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M40" s="8" t="n">
+      <c r="L40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N40" s="8" t="n">
         <v>99000</v>
       </c>
     </row>
@@ -2338,10 +2461,10 @@
         <v>76</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="6" t="n">
         <v>2</v>
@@ -2355,11 +2478,14 @@
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="10" t="n">
-        <v>-1.99</v>
-      </c>
-      <c r="M41" s="8" t="n">
-        <v>98010</v>
+      <c r="L41" s="6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="M41" s="10" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>98990.10000000001</v>
       </c>
     </row>
     <row r="42">
@@ -2404,17 +2530,20 @@
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="10" t="n">
+      <c r="L42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="10" t="n">
         <v>-2.97</v>
       </c>
-      <c r="M42" s="8" t="n">
+      <c r="N42" s="8" t="n">
         <v>97029.89999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 5R, or an opposite reversal nearer than 5R), starting capital 100,000, risk 1.0%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-23). generated 2026-07-25 00:34 UTC.</t>
+          <t>quickfix daily (target = 5R, or an opposite reversal nearer than 5R), starting capital 100,000, risk 1.0%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-23); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-25 02:41 UTC.</t>
         </is>
       </c>
     </row>
@@ -6452,6 +6581,14 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
       <c r="G71" t="n">
         <v>0.8467</v>
       </c>
@@ -6461,16 +6598,25 @@
       <c r="I71" t="n">
         <v>0.8622</v>
       </c>
+      <c r="J71" t="n">
+        <v>0.8498</v>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>data_end</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N71" t="n">
         <v>98010</v>
       </c>
       <c r="O71" t="n">
-        <v>98010</v>
+        <v>98990.10000000001</v>
       </c>
     </row>
     <row r="72">

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
         <v>5</v>
@@ -624,7 +624,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>80</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>33.3</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1079,11 +1079,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1124,11 +1124,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1169,11 +1169,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1259,11 +1259,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1304,11 +1304,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F18" t="n">
         <v>6</v>
@@ -1352,11 +1352,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -1400,11 +1400,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1448,11 +1448,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F25" t="n">
         <v>2</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 5R, or an opposite reversal nearer than 5R), starting capital 100,000, risk 1.0%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-23); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-25 02:41 UTC.</t>
+          <t>quickfix daily (target = 5R, or an opposite reversal nearer than 5R), starting capital 100,000, risk 1.0%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 03:03 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -3285,58 +3285,41 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-01-14</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
+          <t>2026-07-24</t>
+        </is>
       </c>
       <c r="G13" t="n">
-        <v>5097</v>
+        <v>706</v>
       </c>
       <c r="H13" t="n">
-        <v>5050</v>
+        <v>711.3</v>
       </c>
       <c r="I13" t="n">
-        <v>5332</v>
-      </c>
-      <c r="J13" t="n">
-        <v>5050</v>
+        <v>679.5</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N13" t="n">
-        <v>100000</v>
+        <v>120248.3</v>
       </c>
       <c r="O13" t="n">
-        <v>99000</v>
+        <v>120248.3</v>
       </c>
     </row>
     <row r="14">
@@ -3346,7 +3329,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3355,28 +3338,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>4082</v>
+        <v>5097</v>
       </c>
       <c r="H14" t="n">
-        <v>3930</v>
+        <v>5050</v>
       </c>
       <c r="I14" t="n">
-        <v>4842</v>
+        <v>5332</v>
       </c>
       <c r="J14" t="n">
-        <v>3930</v>
+        <v>5050</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -3390,10 +3373,10 @@
         <v>-1</v>
       </c>
       <c r="N14" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O14" t="n">
         <v>99000</v>
-      </c>
-      <c r="O14" t="n">
-        <v>98010</v>
       </c>
     </row>
     <row r="15">
@@ -3403,7 +3386,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -3412,28 +3395,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
-        <v>2990</v>
+        <v>4082</v>
       </c>
       <c r="H15" t="n">
-        <v>2951</v>
+        <v>3930</v>
       </c>
       <c r="I15" t="n">
-        <v>3185</v>
+        <v>4842</v>
       </c>
       <c r="J15" t="n">
-        <v>2951</v>
+        <v>3930</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -3447,50 +3430,50 @@
         <v>-1</v>
       </c>
       <c r="N15" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O15" t="n">
         <v>98010</v>
-      </c>
-      <c r="O15" t="n">
-        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures</t>
+          <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>377.8</v>
+        <v>2990</v>
       </c>
       <c r="H16" t="n">
-        <v>382.86</v>
+        <v>2951</v>
       </c>
       <c r="I16" t="n">
-        <v>352.5</v>
+        <v>3185</v>
       </c>
       <c r="J16" t="n">
-        <v>382.86</v>
+        <v>2951</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -3504,10 +3487,10 @@
         <v>-1</v>
       </c>
       <c r="N16" t="n">
-        <v>100000</v>
+        <v>98010</v>
       </c>
       <c r="O16" t="n">
-        <v>99000</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3517,111 +3500,111 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>345.1</v>
+        <v>377.8</v>
       </c>
       <c r="H17" t="n">
-        <v>341.79</v>
+        <v>382.86</v>
       </c>
       <c r="I17" t="n">
-        <v>361.65</v>
+        <v>352.5</v>
       </c>
       <c r="J17" t="n">
-        <v>359.4</v>
+        <v>382.86</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>bullish_reversal</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.3202</v>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>4.3202</v>
+        <v>-1</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N17" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O17" t="n">
         <v>99000</v>
-      </c>
-      <c r="O17" t="n">
-        <v>103277.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures</t>
+          <t>Coffee_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>478.2</v>
+        <v>345.1</v>
       </c>
       <c r="H18" t="n">
-        <v>480.1</v>
+        <v>341.79</v>
       </c>
       <c r="I18" t="n">
-        <v>468.7</v>
+        <v>361.65</v>
       </c>
       <c r="J18" t="n">
-        <v>480.1</v>
+        <v>359.4</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>bullish_reversal</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>-1</v>
+        <v>4.3202</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>4.3202</v>
       </c>
       <c r="N18" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O18" t="n">
-        <v>99000</v>
+        <v>103277.04</v>
       </c>
     </row>
     <row r="19">
@@ -3631,7 +3614,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3640,45 +3623,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>486.4</v>
+        <v>478.2</v>
       </c>
       <c r="H19" t="n">
-        <v>487.5</v>
+        <v>480.1</v>
       </c>
       <c r="I19" t="n">
-        <v>480.9</v>
+        <v>468.7</v>
       </c>
       <c r="J19" t="n">
-        <v>480.9</v>
+        <v>480.1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N19" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O19" t="n">
         <v>99000</v>
-      </c>
-      <c r="O19" t="n">
-        <v>103950</v>
       </c>
     </row>
     <row r="20">
@@ -3688,121 +3671,121 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>411</v>
+        <v>486.4</v>
       </c>
       <c r="H20" t="n">
-        <v>408.3</v>
+        <v>487.5</v>
       </c>
       <c r="I20" t="n">
-        <v>424.5</v>
+        <v>480.9</v>
       </c>
       <c r="J20" t="n">
-        <v>408.3</v>
+        <v>480.9</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="N20" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O20" t="n">
         <v>103950</v>
-      </c>
-      <c r="O20" t="n">
-        <v>102910.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>49750</v>
+        <v>411</v>
       </c>
       <c r="H21" t="n">
-        <v>49811</v>
+        <v>408.3</v>
       </c>
       <c r="I21" t="n">
-        <v>49445</v>
+        <v>424.5</v>
       </c>
       <c r="J21" t="n">
-        <v>49445</v>
+        <v>408.3</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N21" t="n">
-        <v>100000</v>
+        <v>103950</v>
       </c>
       <c r="O21" t="n">
-        <v>105000</v>
+        <v>102910.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3811,45 +3794,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
+          <t>2026-07-24</t>
+        </is>
       </c>
       <c r="G22" t="n">
-        <v>51744</v>
+        <v>488.1</v>
       </c>
       <c r="H22" t="n">
-        <v>51850</v>
+        <v>492.1</v>
       </c>
       <c r="I22" t="n">
-        <v>51214</v>
-      </c>
-      <c r="J22" t="n">
-        <v>51214</v>
+        <v>468.1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>target_5r</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>5</v>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>5</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N22" t="n">
-        <v>105000</v>
+        <v>102910.5</v>
       </c>
       <c r="O22" t="n">
-        <v>110250</v>
+        <v>102910.5</v>
       </c>
     </row>
     <row r="23">
@@ -3859,7 +3825,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3868,55 +3834,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>52734</v>
+        <v>49750</v>
       </c>
       <c r="H23" t="n">
-        <v>53106</v>
+        <v>49811</v>
       </c>
       <c r="I23" t="n">
-        <v>50874</v>
+        <v>49445</v>
       </c>
       <c r="J23" t="n">
-        <v>53106</v>
+        <v>49445</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>110250</v>
+        <v>100000</v>
       </c>
       <c r="O23" t="n">
-        <v>109147.5</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3925,91 +3891,108 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1.1783</v>
+        <v>51744</v>
       </c>
       <c r="H24" t="n">
-        <v>1.17986</v>
+        <v>51850</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1705</v>
+        <v>51214</v>
       </c>
       <c r="J24" t="n">
-        <v>1.17986</v>
+        <v>51214</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>100000</v>
+        <v>105000</v>
       </c>
       <c r="O24" t="n">
-        <v>99000</v>
+        <v>110250</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>1.1391</v>
+        <v>52734</v>
       </c>
       <c r="H25" t="n">
-        <v>1.13634</v>
+        <v>53106</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1529</v>
+        <v>50874</v>
+      </c>
+      <c r="J25" t="n">
+        <v>53106</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N25" t="n">
-        <v>99000</v>
+        <v>110250</v>
       </c>
       <c r="O25" t="n">
-        <v>99000</v>
+        <v>109147.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -4022,51 +4005,51 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>6043.4</v>
+        <v>1.1783</v>
       </c>
       <c r="H26" t="n">
-        <v>6073.35</v>
+        <v>1.17986</v>
       </c>
       <c r="I26" t="n">
-        <v>5893.65</v>
+        <v>1.1705</v>
       </c>
       <c r="J26" t="n">
-        <v>5893.65</v>
+        <v>1.17986</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5</v>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N26" t="n">
         <v>100000</v>
       </c>
       <c r="O26" t="n">
-        <v>105000</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -4074,56 +4057,39 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>2</v>
+          <t>2026-06-24</t>
+        </is>
       </c>
       <c r="G27" t="n">
-        <v>6060.23</v>
+        <v>1.1391</v>
       </c>
       <c r="H27" t="n">
-        <v>6078.29</v>
+        <v>1.13634</v>
       </c>
       <c r="I27" t="n">
-        <v>5969.93</v>
-      </c>
-      <c r="J27" t="n">
-        <v>6078.29</v>
+        <v>1.1529</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M27" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N27" t="n">
-        <v>105000</v>
+        <v>99000</v>
       </c>
       <c r="O27" t="n">
-        <v>103950</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance</t>
+          <t>EURO_STOXX_50_Index</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -4131,56 +4097,56 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>2812</v>
+        <v>6043.4</v>
       </c>
       <c r="H28" t="n">
-        <v>2754</v>
+        <v>6073.35</v>
       </c>
       <c r="I28" t="n">
-        <v>3102</v>
+        <v>5893.65</v>
       </c>
       <c r="J28" t="n">
-        <v>2754</v>
+        <v>5893.65</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="N28" t="n">
         <v>100000</v>
       </c>
       <c r="O28" t="n">
-        <v>99000</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance</t>
+          <t>EURO_STOXX_50_Index</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -4188,47 +4154,47 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>1818</v>
+        <v>6060.23</v>
       </c>
       <c r="H29" t="n">
-        <v>1799</v>
+        <v>6078.29</v>
       </c>
       <c r="I29" t="n">
-        <v>1913</v>
+        <v>5969.93</v>
       </c>
       <c r="J29" t="n">
-        <v>1913</v>
+        <v>6078.29</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N29" t="n">
-        <v>99000</v>
+        <v>105000</v>
       </c>
       <c r="O29" t="n">
         <v>103950</v>
@@ -4241,98 +4207,98 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>2370</v>
+        <v>2812</v>
       </c>
       <c r="H30" t="n">
-        <v>2386</v>
+        <v>2754</v>
       </c>
       <c r="I30" t="n">
-        <v>2290</v>
+        <v>3102</v>
       </c>
       <c r="J30" t="n">
-        <v>2290</v>
+        <v>2754</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5</v>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N30" t="n">
-        <v>103950</v>
+        <v>100000</v>
       </c>
       <c r="O30" t="n">
-        <v>109147.5</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>German_Long_Bund</t>
+          <t>Ethereum_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>127.47</v>
+        <v>1818</v>
       </c>
       <c r="H31" t="n">
-        <v>127.7</v>
+        <v>1799</v>
       </c>
       <c r="I31" t="n">
-        <v>126.32</v>
+        <v>1913</v>
       </c>
       <c r="J31" t="n">
-        <v>126.32</v>
+        <v>1913</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -4342,20 +4308,20 @@
         <v>5</v>
       </c>
       <c r="N31" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O31" t="n">
-        <v>105000</v>
+        <v>103950</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>Ethereum_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4364,32 +4330,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>4393</v>
+        <v>2370</v>
       </c>
       <c r="H32" t="n">
-        <v>4409.6</v>
+        <v>2386</v>
       </c>
       <c r="I32" t="n">
-        <v>4310</v>
+        <v>2290</v>
       </c>
       <c r="J32" t="n">
-        <v>4310</v>
+        <v>2290</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -4399,20 +4365,20 @@
         <v>5</v>
       </c>
       <c r="N32" t="n">
-        <v>100000</v>
+        <v>103950</v>
       </c>
       <c r="O32" t="n">
-        <v>105000</v>
+        <v>109147.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>German_Long_Bund</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4421,45 +4387,45 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>4393</v>
+        <v>127.47</v>
       </c>
       <c r="H33" t="n">
-        <v>4420.6</v>
+        <v>127.7</v>
       </c>
       <c r="I33" t="n">
-        <v>4255</v>
+        <v>126.32</v>
       </c>
       <c r="J33" t="n">
-        <v>4420.6</v>
+        <v>126.32</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="N33" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O33" t="n">
         <v>105000</v>
-      </c>
-      <c r="O33" t="n">
-        <v>103950</v>
       </c>
     </row>
     <row r="34">
@@ -4469,7 +4435,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4478,45 +4444,45 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4393</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4409.6</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4310</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4310</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
         <v>5</v>
       </c>
-      <c r="G34" t="n">
-        <v>5358.1</v>
-      </c>
-      <c r="H34" t="n">
-        <v>5434.2</v>
-      </c>
-      <c r="I34" t="n">
-        <v>4977.6</v>
-      </c>
-      <c r="J34" t="n">
-        <v>5035</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>bearish_reversal</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>4.2457</v>
-      </c>
       <c r="M34" s="2" t="n">
-        <v>4.2457</v>
+        <v>5</v>
       </c>
       <c r="N34" t="n">
-        <v>103950</v>
+        <v>100000</v>
       </c>
       <c r="O34" t="n">
-        <v>108363.44</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="35">
@@ -4526,54 +4492,54 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>4335</v>
+        <v>4393</v>
       </c>
       <c r="H35" t="n">
-        <v>4306.2</v>
+        <v>4420.6</v>
       </c>
       <c r="I35" t="n">
-        <v>4479</v>
+        <v>4255</v>
       </c>
       <c r="J35" t="n">
-        <v>4479</v>
+        <v>4420.6</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5</v>
-      </c>
-      <c r="M35" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N35" t="n">
-        <v>108363.44</v>
+        <v>105000</v>
       </c>
       <c r="O35" t="n">
-        <v>113781.61</v>
+        <v>103950</v>
       </c>
     </row>
     <row r="36">
@@ -4583,51 +4549,54 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>5</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
       <c r="G36" t="n">
-        <v>4746</v>
+        <v>5358.1</v>
       </c>
       <c r="H36" t="n">
-        <v>4758.5</v>
+        <v>5434.2</v>
       </c>
       <c r="I36" t="n">
-        <v>4683.5</v>
+        <v>4977.6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5035</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>bearish_reversal</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v>-1</v>
+        <v>4.2457</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>4.2457</v>
       </c>
       <c r="N36" t="n">
-        <v>113781.61</v>
+        <v>103950</v>
       </c>
       <c r="O36" t="n">
-        <v>112643.79</v>
+        <v>108363.44</v>
       </c>
     </row>
     <row r="37">
@@ -4637,7 +4606,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4646,45 +4615,45 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>4347</v>
+        <v>4335</v>
       </c>
       <c r="H37" t="n">
-        <v>4292.9</v>
+        <v>4306.2</v>
       </c>
       <c r="I37" t="n">
-        <v>4617.5</v>
+        <v>4479</v>
       </c>
       <c r="J37" t="n">
-        <v>4292.9</v>
+        <v>4479</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="N37" t="n">
-        <v>112643.79</v>
+        <v>108363.44</v>
       </c>
       <c r="O37" t="n">
-        <v>111517.35</v>
+        <v>113781.61</v>
       </c>
     </row>
     <row r="38">
@@ -4694,54 +4663,51 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>4103</v>
+        <v>4746</v>
       </c>
       <c r="H38" t="n">
-        <v>4046.1</v>
+        <v>4758.5</v>
       </c>
       <c r="I38" t="n">
-        <v>4387.5</v>
-      </c>
-      <c r="J38" t="n">
-        <v>4387.5</v>
+        <v>4683.5</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>5</v>
-      </c>
-      <c r="M38" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N38" t="n">
-        <v>111517.35</v>
+        <v>113781.61</v>
       </c>
       <c r="O38" t="n">
-        <v>117093.22</v>
+        <v>112643.79</v>
       </c>
     </row>
     <row r="39">
@@ -4751,7 +4717,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4760,45 +4726,45 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>3984</v>
+        <v>4347</v>
       </c>
       <c r="H39" t="n">
-        <v>3955.3</v>
+        <v>4292.9</v>
       </c>
       <c r="I39" t="n">
-        <v>4127.5</v>
+        <v>4617.5</v>
       </c>
       <c r="J39" t="n">
-        <v>4127.5</v>
+        <v>4292.9</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>5</v>
-      </c>
-      <c r="M39" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N39" t="n">
-        <v>117093.22</v>
+        <v>112643.79</v>
       </c>
       <c r="O39" t="n">
-        <v>122947.88</v>
+        <v>111517.35</v>
       </c>
     </row>
     <row r="40">
@@ -4808,7 +4774,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4817,32 +4783,32 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>2</v>
       </c>
       <c r="G40" t="n">
-        <v>3984</v>
+        <v>4103</v>
       </c>
       <c r="H40" t="n">
-        <v>3962.9</v>
+        <v>4046.1</v>
       </c>
       <c r="I40" t="n">
-        <v>4089.5</v>
+        <v>4387.5</v>
       </c>
       <c r="J40" t="n">
-        <v>4089.5</v>
+        <v>4387.5</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -4852,134 +4818,134 @@
         <v>5</v>
       </c>
       <c r="N40" t="n">
-        <v>122947.88</v>
+        <v>111517.35</v>
       </c>
       <c r="O40" t="n">
-        <v>129095.28</v>
+        <v>117093.22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0.006417</v>
+        <v>3984</v>
       </c>
       <c r="H41" t="n">
-        <v>0.006454</v>
+        <v>3955.3</v>
       </c>
       <c r="I41" t="n">
-        <v>0.006254</v>
+        <v>4127.5</v>
       </c>
       <c r="J41" t="n">
-        <v>0.006454</v>
+        <v>4127.5</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M41" s="5" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="N41" t="n">
-        <v>100000</v>
+        <v>117093.22</v>
       </c>
       <c r="O41" t="n">
-        <v>99000</v>
+        <v>122947.88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" t="n">
-        <v>239.06</v>
+        <v>3984</v>
       </c>
       <c r="H42" t="n">
-        <v>239.73</v>
+        <v>3962.9</v>
       </c>
       <c r="I42" t="n">
-        <v>235.71</v>
+        <v>4089.5</v>
       </c>
       <c r="J42" t="n">
-        <v>239.73</v>
+        <v>4089.5</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M42" s="5" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="N42" t="n">
-        <v>100000</v>
+        <v>122947.88</v>
       </c>
       <c r="O42" t="n">
-        <v>99000</v>
+        <v>129095.28</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4988,45 +4954,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43" t="n">
-        <v>251.58</v>
+        <v>0.006417</v>
       </c>
       <c r="H43" t="n">
-        <v>251.91</v>
+        <v>0.006454</v>
       </c>
       <c r="I43" t="n">
-        <v>249.93</v>
+        <v>0.006254</v>
       </c>
       <c r="J43" t="n">
-        <v>249.93</v>
+        <v>0.006454</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5</v>
-      </c>
-      <c r="M43" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N43" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O43" t="n">
         <v>99000</v>
-      </c>
-      <c r="O43" t="n">
-        <v>103950</v>
       </c>
     </row>
     <row r="44">
@@ -5036,7 +5002,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5045,45 +5011,45 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>255.38</v>
+        <v>239.06</v>
       </c>
       <c r="H44" t="n">
-        <v>256.63</v>
+        <v>239.73</v>
       </c>
       <c r="I44" t="n">
-        <v>249.13</v>
+        <v>235.71</v>
       </c>
       <c r="J44" t="n">
-        <v>249.13</v>
+        <v>239.73</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5</v>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N44" t="n">
-        <v>103950</v>
+        <v>100000</v>
       </c>
       <c r="O44" t="n">
-        <v>109147.5</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="45">
@@ -5093,151 +5059,151 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>235.2</v>
+        <v>251.58</v>
       </c>
       <c r="H45" t="n">
-        <v>234.36</v>
+        <v>251.91</v>
       </c>
       <c r="I45" t="n">
-        <v>239.4</v>
+        <v>249.93</v>
       </c>
       <c r="J45" t="n">
-        <v>234.36</v>
+        <v>249.93</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="N45" t="n">
-        <v>109147.5</v>
+        <v>99000</v>
       </c>
       <c r="O45" t="n">
-        <v>108056.02</v>
+        <v>103950</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G46" t="n">
-        <v>5.7714</v>
+        <v>255.38</v>
       </c>
       <c r="H46" t="n">
-        <v>5.6849</v>
+        <v>256.63</v>
       </c>
       <c r="I46" t="n">
-        <v>6.2039</v>
+        <v>249.13</v>
       </c>
       <c r="J46" t="n">
-        <v>5.6849</v>
+        <v>249.13</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="N46" t="n">
-        <v>100000</v>
+        <v>103950</v>
       </c>
       <c r="O46" t="n">
-        <v>99000</v>
+        <v>109147.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
         <v>2</v>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
       <c r="G47" t="n">
-        <v>5.7714</v>
+        <v>235.2</v>
       </c>
       <c r="H47" t="n">
-        <v>5.6774</v>
+        <v>234.36</v>
       </c>
       <c r="I47" t="n">
-        <v>6.116</v>
+        <v>239.4</v>
       </c>
       <c r="J47" t="n">
-        <v>5.6774</v>
+        <v>234.36</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -5251,10 +5217,10 @@
         <v>-1</v>
       </c>
       <c r="N47" t="n">
-        <v>99000</v>
+        <v>109147.5</v>
       </c>
       <c r="O47" t="n">
-        <v>98010</v>
+        <v>108056.02</v>
       </c>
     </row>
     <row r="48">
@@ -5264,7 +5230,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5273,45 +5239,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>5.3133</v>
+        <v>5.7714</v>
       </c>
       <c r="H48" t="n">
-        <v>5.2459</v>
+        <v>5.6849</v>
       </c>
       <c r="I48" t="n">
-        <v>5.6503</v>
+        <v>6.2039</v>
       </c>
       <c r="J48" t="n">
-        <v>5.6503</v>
+        <v>5.6849</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>5</v>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N48" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O48" t="n">
-        <v>102910.5</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="49">
@@ -5321,37 +5287,37 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>6.0956</v>
+        <v>5.7714</v>
       </c>
       <c r="H49" t="n">
-        <v>6.1481</v>
+        <v>5.6774</v>
       </c>
       <c r="I49" t="n">
-        <v>5.8331</v>
+        <v>6.116</v>
       </c>
       <c r="J49" t="n">
-        <v>6.1481</v>
+        <v>5.6774</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -5365,77 +5331,77 @@
         <v>-1</v>
       </c>
       <c r="N49" t="n">
-        <v>102910.5</v>
+        <v>99000</v>
       </c>
       <c r="O49" t="n">
-        <v>101881.4</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G50" t="n">
-        <v>3.305</v>
+        <v>5.3133</v>
       </c>
       <c r="H50" t="n">
-        <v>3.354</v>
+        <v>5.2459</v>
       </c>
       <c r="I50" t="n">
-        <v>3.095</v>
+        <v>5.6503</v>
       </c>
       <c r="J50" t="n">
-        <v>3.354</v>
+        <v>5.6503</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="N50" t="n">
-        <v>100000</v>
+        <v>98010</v>
       </c>
       <c r="O50" t="n">
-        <v>99000</v>
+        <v>102910.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5444,51 +5410,51 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G51" t="n">
-        <v>3.305</v>
+        <v>6.0956</v>
       </c>
       <c r="H51" t="n">
-        <v>3.356</v>
+        <v>6.1481</v>
       </c>
       <c r="I51" t="n">
-        <v>3.12</v>
+        <v>5.8331</v>
       </c>
       <c r="J51" t="n">
-        <v>3.12</v>
+        <v>6.1481</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>bearish_reversal</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.6275</v>
-      </c>
-      <c r="M51" s="2" t="n">
-        <v>3.6275</v>
+        <v>-1</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N51" t="n">
-        <v>99000</v>
+        <v>102910.5</v>
       </c>
       <c r="O51" t="n">
-        <v>102591.18</v>
+        <v>101881.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -5496,33 +5462,33 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>1360.4</v>
+        <v>3.305</v>
       </c>
       <c r="H52" t="n">
-        <v>1343.4</v>
+        <v>3.354</v>
       </c>
       <c r="I52" t="n">
-        <v>1445.4</v>
+        <v>3.095</v>
       </c>
       <c r="J52" t="n">
-        <v>1343.4</v>
+        <v>3.354</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -5545,7 +5511,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -5553,56 +5519,56 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>1167</v>
+        <v>3.305</v>
       </c>
       <c r="H53" t="n">
-        <v>1159.4</v>
+        <v>3.356</v>
       </c>
       <c r="I53" t="n">
-        <v>1205</v>
+        <v>3.12</v>
       </c>
       <c r="J53" t="n">
-        <v>1205</v>
+        <v>3.12</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>bearish_reversal</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>5</v>
+        <v>3.6275</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5</v>
+        <v>3.6275</v>
       </c>
       <c r="N53" t="n">
         <v>99000</v>
       </c>
       <c r="O53" t="n">
-        <v>103950</v>
+        <v>102591.18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -5610,33 +5576,33 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G54" t="n">
-        <v>2084.6</v>
+        <v>1360.4</v>
       </c>
       <c r="H54" t="n">
-        <v>2113.7</v>
+        <v>1343.4</v>
       </c>
       <c r="I54" t="n">
-        <v>1939.1</v>
+        <v>1445.4</v>
       </c>
       <c r="J54" t="n">
-        <v>2113.7</v>
+        <v>1343.4</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -5659,7 +5625,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -5672,45 +5638,45 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1641.5</v>
+        <v>1167</v>
       </c>
       <c r="H55" t="n">
-        <v>1621</v>
+        <v>1159.4</v>
       </c>
       <c r="I55" t="n">
-        <v>1744</v>
+        <v>1205</v>
       </c>
       <c r="J55" t="n">
-        <v>1621</v>
+        <v>1205</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M55" s="5" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="N55" t="n">
         <v>99000</v>
       </c>
       <c r="O55" t="n">
-        <v>98010</v>
+        <v>103950</v>
       </c>
     </row>
     <row r="56">
@@ -5720,37 +5686,37 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>1581.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H56" t="n">
-        <v>1547.6</v>
+        <v>2113.7</v>
       </c>
       <c r="I56" t="n">
-        <v>1751</v>
+        <v>1939.1</v>
       </c>
       <c r="J56" t="n">
-        <v>1547.6</v>
+        <v>2113.7</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -5764,50 +5730,50 @@
         <v>-1</v>
       </c>
       <c r="N56" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O56" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>27907</v>
+        <v>1641.5</v>
       </c>
       <c r="H57" t="n">
-        <v>27965.76</v>
+        <v>1621</v>
       </c>
       <c r="I57" t="n">
-        <v>27613.2</v>
+        <v>1744</v>
       </c>
       <c r="J57" t="n">
-        <v>27965.76</v>
+        <v>1621</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5821,50 +5787,50 @@
         <v>-1</v>
       </c>
       <c r="N57" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O57" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G58" t="n">
-        <v>7206.55</v>
+        <v>1581.5</v>
       </c>
       <c r="H58" t="n">
-        <v>7223.26</v>
+        <v>1547.6</v>
       </c>
       <c r="I58" t="n">
-        <v>7123</v>
+        <v>1751</v>
       </c>
       <c r="J58" t="n">
-        <v>7223.26</v>
+        <v>1547.6</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5878,16 +5844,16 @@
         <v>-1</v>
       </c>
       <c r="N58" t="n">
-        <v>100000</v>
+        <v>98010</v>
       </c>
       <c r="O58" t="n">
-        <v>99000</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -5900,85 +5866,85 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>6957.43</v>
+        <v>27907</v>
       </c>
       <c r="H59" t="n">
-        <v>6965.7</v>
+        <v>27965.76</v>
       </c>
       <c r="I59" t="n">
-        <v>6916.08</v>
+        <v>27613.2</v>
       </c>
       <c r="J59" t="n">
-        <v>6916.08</v>
+        <v>27965.76</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>5</v>
-      </c>
-      <c r="M59" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M59" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N59" t="n">
         <v>100000</v>
       </c>
       <c r="O59" t="n">
-        <v>105000</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
         <v>2</v>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
       <c r="G60" t="n">
-        <v>6982.4</v>
+        <v>7206.55</v>
       </c>
       <c r="H60" t="n">
-        <v>6988.83</v>
+        <v>7223.26</v>
       </c>
       <c r="I60" t="n">
-        <v>6950.25</v>
+        <v>7123</v>
       </c>
       <c r="J60" t="n">
-        <v>6988.83</v>
+        <v>7223.26</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5992,10 +5958,10 @@
         <v>-1</v>
       </c>
       <c r="N60" t="n">
-        <v>105000</v>
+        <v>100000</v>
       </c>
       <c r="O60" t="n">
-        <v>103950</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="61">
@@ -6005,7 +5971,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6014,32 +5980,32 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H61" t="n">
-        <v>6992.85</v>
+        <v>6965.7</v>
       </c>
       <c r="I61" t="n">
-        <v>6930.15</v>
+        <v>6916.08</v>
       </c>
       <c r="J61" t="n">
-        <v>6930.15</v>
+        <v>6916.08</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -6049,10 +6015,10 @@
         <v>5</v>
       </c>
       <c r="N61" t="n">
-        <v>103950</v>
+        <v>100000</v>
       </c>
       <c r="O61" t="n">
-        <v>109147.5</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="62">
@@ -6062,7 +6028,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6071,12 +6037,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -6086,14 +6052,17 @@
         <v>6982.4</v>
       </c>
       <c r="H62" t="n">
-        <v>6991.93</v>
+        <v>6988.83</v>
       </c>
       <c r="I62" t="n">
-        <v>6934.75</v>
+        <v>6950.25</v>
+      </c>
+      <c r="J62" t="n">
+        <v>6988.83</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -6103,10 +6072,10 @@
         <v>-1</v>
       </c>
       <c r="N62" t="n">
-        <v>109147.5</v>
+        <v>105000</v>
       </c>
       <c r="O62" t="n">
-        <v>108056.02</v>
+        <v>103950</v>
       </c>
     </row>
     <row r="63">
@@ -6116,7 +6085,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6125,12 +6094,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -6140,27 +6109,30 @@
         <v>6982.4</v>
       </c>
       <c r="H63" t="n">
-        <v>6986.84</v>
+        <v>6992.85</v>
       </c>
       <c r="I63" t="n">
-        <v>6960.2</v>
+        <v>6930.15</v>
+      </c>
+      <c r="J63" t="n">
+        <v>6930.15</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M63" s="5" t="n">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="N63" t="n">
-        <v>108056.02</v>
+        <v>103950</v>
       </c>
       <c r="O63" t="n">
-        <v>106975.46</v>
+        <v>109147.5</v>
       </c>
     </row>
     <row r="64">
@@ -6170,41 +6142,38 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H64" t="n">
-        <v>6770.77</v>
+        <v>6991.93</v>
       </c>
       <c r="I64" t="n">
-        <v>6912.55</v>
-      </c>
-      <c r="J64" t="n">
-        <v>6770.77</v>
+        <v>6934.75</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -6214,20 +6183,20 @@
         <v>-1</v>
       </c>
       <c r="N64" t="n">
-        <v>106975.46</v>
+        <v>109147.5</v>
       </c>
       <c r="O64" t="n">
-        <v>105905.71</v>
+        <v>108056.02</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -6236,32 +6205,29 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H65" t="n">
-        <v>88.001</v>
+        <v>6986.84</v>
       </c>
       <c r="I65" t="n">
-        <v>76.48099999999999</v>
-      </c>
-      <c r="J65" t="n">
-        <v>88.001</v>
+        <v>6960.2</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -6271,20 +6237,20 @@
         <v>-1</v>
       </c>
       <c r="N65" t="n">
-        <v>100000</v>
+        <v>108056.02</v>
       </c>
       <c r="O65" t="n">
-        <v>99000</v>
+        <v>106975.46</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -6293,28 +6259,28 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>73.84399999999999</v>
+        <v>6794.4</v>
       </c>
       <c r="H66" t="n">
-        <v>71.999</v>
+        <v>6770.77</v>
       </c>
       <c r="I66" t="n">
-        <v>83.069</v>
+        <v>6912.55</v>
       </c>
       <c r="J66" t="n">
-        <v>71.999</v>
+        <v>6770.77</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -6328,16 +6294,16 @@
         <v>-1</v>
       </c>
       <c r="N66" t="n">
-        <v>99000</v>
+        <v>106975.46</v>
       </c>
       <c r="O66" t="n">
-        <v>98010</v>
+        <v>105905.71</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -6350,28 +6316,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>15</v>
+        <v>86.081</v>
       </c>
       <c r="H67" t="n">
-        <v>15.26</v>
+        <v>88.001</v>
       </c>
       <c r="I67" t="n">
-        <v>13.7</v>
+        <v>76.48099999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>15.26</v>
+        <v>88.001</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -6394,41 +6360,41 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G68" t="n">
-        <v>20.89</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>21.07</v>
+        <v>71.999</v>
       </c>
       <c r="I68" t="n">
-        <v>19.99</v>
+        <v>83.069</v>
       </c>
       <c r="J68" t="n">
-        <v>21.07</v>
+        <v>71.999</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6442,16 +6408,16 @@
         <v>-1</v>
       </c>
       <c r="N68" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O68" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -6464,28 +6430,28 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>0.8614000000000001</v>
+        <v>15</v>
       </c>
       <c r="H69" t="n">
-        <v>0.8637</v>
+        <v>15.26</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8499</v>
+        <v>13.7</v>
       </c>
       <c r="J69" t="n">
-        <v>0.8637</v>
+        <v>15.26</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6508,11 +6474,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -6521,28 +6487,28 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>0.8614000000000001</v>
+        <v>20.89</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8658</v>
+        <v>21.07</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8418</v>
+        <v>19.99</v>
       </c>
       <c r="J70" t="n">
-        <v>0.8658</v>
+        <v>21.07</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6556,10 +6522,10 @@
         <v>-1</v>
       </c>
       <c r="N70" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O70" t="n">
         <v>99000</v>
-      </c>
-      <c r="O70" t="n">
-        <v>98010</v>
       </c>
     </row>
     <row r="71">
@@ -6569,64 +6535,64 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.8467</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8436</v>
+        <v>0.8637</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8622</v>
+        <v>0.8499</v>
       </c>
       <c r="J71" t="n">
-        <v>0.8498</v>
+        <v>0.8637</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
-      </c>
-      <c r="M71" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
+      </c>
+      <c r="M71" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N71" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O71" t="n">
-        <v>98990.10000000001</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -6635,28 +6601,28 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>116.5</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H72" t="n">
-        <v>116.79</v>
+        <v>0.8658</v>
       </c>
       <c r="I72" t="n">
-        <v>115.05</v>
+        <v>0.8418</v>
       </c>
       <c r="J72" t="n">
-        <v>116.79</v>
+        <v>0.8658</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6670,73 +6636,73 @@
         <v>-1</v>
       </c>
       <c r="N72" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O72" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>118.02</v>
+        <v>0.8467</v>
       </c>
       <c r="H73" t="n">
-        <v>118.16</v>
+        <v>0.8436</v>
       </c>
       <c r="I73" t="n">
-        <v>117.32</v>
+        <v>0.8622</v>
       </c>
       <c r="J73" t="n">
-        <v>118.16</v>
+        <v>0.8498</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M73" s="5" t="n">
-        <v>-1</v>
+        <v>1</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>99000</v>
+        <v>98010</v>
       </c>
       <c r="O73" t="n">
-        <v>98010</v>
+        <v>98990.10000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -6744,33 +6710,33 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>97.81399999999999</v>
+        <v>116.5</v>
       </c>
       <c r="H74" t="n">
-        <v>97.569</v>
+        <v>116.79</v>
       </c>
       <c r="I74" t="n">
-        <v>98.976</v>
+        <v>115.05</v>
       </c>
       <c r="J74" t="n">
-        <v>97.569</v>
+        <v>116.79</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6793,7 +6759,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -6806,28 +6772,28 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G75" t="n">
-        <v>99.376</v>
+        <v>118.02</v>
       </c>
       <c r="H75" t="n">
-        <v>99.571</v>
+        <v>118.16</v>
       </c>
       <c r="I75" t="n">
-        <v>98.401</v>
+        <v>117.32</v>
       </c>
       <c r="J75" t="n">
-        <v>99.571</v>
+        <v>118.16</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6854,37 +6820,37 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>3</v>
       </c>
       <c r="G76" t="n">
-        <v>100.066</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>100.201</v>
+        <v>97.569</v>
       </c>
       <c r="I76" t="n">
-        <v>99.39100000000001</v>
+        <v>98.976</v>
       </c>
       <c r="J76" t="n">
-        <v>100.201</v>
+        <v>97.569</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6898,10 +6864,10 @@
         <v>-1</v>
       </c>
       <c r="N76" t="n">
-        <v>98010</v>
+        <v>100000</v>
       </c>
       <c r="O76" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="77">
@@ -6911,7 +6877,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -6920,28 +6886,28 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G77" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H77" t="n">
-        <v>100.361</v>
+        <v>99.571</v>
       </c>
       <c r="I77" t="n">
-        <v>99.004</v>
+        <v>98.401</v>
       </c>
       <c r="J77" t="n">
-        <v>100.361</v>
+        <v>99.571</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6955,10 +6921,10 @@
         <v>-1</v>
       </c>
       <c r="N77" t="n">
-        <v>97029.89999999999</v>
+        <v>99000</v>
       </c>
       <c r="O77" t="n">
-        <v>96059.60000000001</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="78">
@@ -6968,7 +6934,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -6977,28 +6943,28 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G78" t="n">
-        <v>100.621</v>
+        <v>100.066</v>
       </c>
       <c r="H78" t="n">
-        <v>100.911</v>
+        <v>100.201</v>
       </c>
       <c r="I78" t="n">
-        <v>99.17100000000001</v>
+        <v>99.39100000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>100.911</v>
+        <v>100.201</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -7012,10 +6978,10 @@
         <v>-1</v>
       </c>
       <c r="N78" t="n">
-        <v>96059.60000000001</v>
+        <v>98010</v>
       </c>
       <c r="O78" t="n">
-        <v>95099</v>
+        <v>97029.89999999999</v>
       </c>
     </row>
     <row r="79">
@@ -7025,7 +6991,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -7034,55 +7000,55 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H79" t="n">
-        <v>101.526</v>
+        <v>100.361</v>
       </c>
       <c r="I79" t="n">
-        <v>100.836</v>
+        <v>99.004</v>
       </c>
       <c r="J79" t="n">
-        <v>100.836</v>
+        <v>100.361</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>5</v>
-      </c>
-      <c r="M79" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M79" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N79" t="n">
-        <v>95099</v>
+        <v>97029.89999999999</v>
       </c>
       <c r="O79" t="n">
-        <v>99853.96000000001</v>
+        <v>96059.60000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -7091,55 +7057,55 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G80" t="n">
-        <v>121.72</v>
+        <v>100.621</v>
       </c>
       <c r="H80" t="n">
-        <v>123.03</v>
+        <v>100.911</v>
       </c>
       <c r="I80" t="n">
-        <v>115.17</v>
+        <v>99.17100000000001</v>
       </c>
       <c r="J80" t="n">
-        <v>115.17</v>
+        <v>100.911</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>5</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M80" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N80" t="n">
-        <v>100000</v>
+        <v>96059.60000000001</v>
       </c>
       <c r="O80" t="n">
-        <v>105000</v>
+        <v>95099</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -7148,32 +7114,32 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>130.16</v>
+        <v>101.411</v>
       </c>
       <c r="H81" t="n">
-        <v>130.94</v>
+        <v>101.526</v>
       </c>
       <c r="I81" t="n">
-        <v>126.26</v>
+        <v>100.836</v>
       </c>
       <c r="J81" t="n">
-        <v>126.26</v>
+        <v>100.836</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -7183,9 +7149,123 @@
         <v>5</v>
       </c>
       <c r="N81" t="n">
+        <v>95099</v>
+      </c>
+      <c r="O81" t="n">
+        <v>99853.96000000001</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H82" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="I82" t="n">
+        <v>115.17</v>
+      </c>
+      <c r="J82" t="n">
+        <v>115.17</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>5</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N82" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O82" t="n">
         <v>105000</v>
       </c>
-      <c r="O81" t="n">
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="n">
+        <v>130.16</v>
+      </c>
+      <c r="H83" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="I83" t="n">
+        <v>126.26</v>
+      </c>
+      <c r="J83" t="n">
+        <v>126.26</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>5</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N83" t="n">
+        <v>105000</v>
+      </c>
+      <c r="O83" t="n">
         <v>110250</v>
       </c>
     </row>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 5R, or an opposite reversal nearer than 5R), starting capital 100,000, risk 1.0%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 03:03 UTC.</t>
+          <t>quickfix daily (target = 5R, or an opposite reversal nearer than 5R), starting capital 100,000, risk 1.0%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 04:17 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -564,10 +564,10 @@
         <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -579,19 +579,19 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>29.1</v>
+        <v>26.91</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>129095.28</v>
+        <v>126907.74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -624,28 +624,28 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>20.25</v>
+        <v>20.19</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>120248.3</v>
+        <v>120185.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -657,13 +657,13 @@
         <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -672,28 +672,28 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10.25</v>
+        <v>14.85</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>110250</v>
+        <v>114847.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -702,19 +702,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -723,25 +723,25 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9.15</v>
+        <v>10.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>109147.5</v>
+        <v>110501.55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Bitcoin_Per_USD_CME</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -771,19 +771,19 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8.06</v>
+        <v>8.02</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>108056.02</v>
+        <v>108019.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>German_Long_Bund</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -822,16 +822,16 @@
         <v>100</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5</v>
+        <v>8.02</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>105000</v>
+        <v>108019.65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -849,11 +849,11 @@
         <v>64</v>
       </c>
       <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
@@ -867,19 +867,19 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3.95</v>
+        <v>6.32</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>103950</v>
+        <v>106320.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures</t>
+          <t>German_Long_Bund</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -912,28 +912,28 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2.91</v>
+        <v>3.93</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>102910.5</v>
+        <v>103932.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -945,13 +945,13 @@
         <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -963,25 +963,25 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2.59</v>
+        <v>3.93</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>102591.18</v>
+        <v>103932.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -990,19 +990,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1011,19 +1011,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>101881.4</v>
+        <v>102297.64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CME_SOFR_Futures_3M</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1038,16 +1038,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1058,23 +1058,26 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
+      <c r="L12" t="n">
+        <v>50</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>2.3</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>100000</v>
+        <v>102297.64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Global_X_Uranium_ETF</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1083,16 +1086,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1103,17 +1106,20 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="4" t="n">
-        <v>0</v>
+      <c r="L13" t="n">
+        <v>50</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>2.3</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>100000</v>
+        <v>102297.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Japanese_10_Year_Bond_Futures</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1128,37 +1134,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>100000</v>
+        <v>100688.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NY_Crude_Oil_Futures</t>
+          <t>CME_SOFR_Futures_3M</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1173,7 +1182,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1203,13 +1212,13 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Proshares_VIX_Short_Term_Futures_ETF</t>
+          <t>Global_X_Uranium_ETF</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1218,7 +1227,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1248,7 +1257,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>US_10_Year_T_Note_Futures</t>
+          <t>Japanese_10_Year_Bond_Futures</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1263,7 +1272,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1293,7 +1302,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>NY_Crude_Oil_Futures</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1308,16 +1317,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1328,26 +1337,23 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>-0.15</v>
+      <c r="M18" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>99853.96000000001</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>Proshares_VIX_Short_Term_Futures_ETF</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1356,16 +1362,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1374,22 +1380,19 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>US_10_Year_T_Note_Futures</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1407,13 +1410,13 @@
         <v>64</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1424,26 +1427,23 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>-1</v>
+      <c r="M20" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1452,16 +1452,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1473,25 +1473,25 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>99000</v>
+        <v>99104.67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1524,16 +1524,16 @@
         <v>0</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-1</v>
+        <v>-1.57</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1572,22 +1572,22 @@
         <v>0</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-1</v>
+        <v>-1.57</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1596,16 +1596,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1620,22 +1620,22 @@
         <v>0</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>-1.99</v>
+        <v>-1.57</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>98010</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F25" t="n">
         <v>2</v>
@@ -1668,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-1.99</v>
+        <v>-3.12</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1716,16 +1716,16 @@
         <v>0</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>-2.97</v>
+        <v>-4.65</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>97029.89999999999</v>
+        <v>95354.84</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>EURO_STOXX_50_Index</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1744,13 +1744,13 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>0</v>
@@ -1768,16 +1768,16 @@
         <v>100</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>10.25</v>
+        <v>12.27</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>110250</v>
+        <v>112267.52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance</t>
+          <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1787,25 +1787,25 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
@@ -1817,19 +1817,19 @@
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>9.15</v>
+        <v>8.02</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>109147.5</v>
+        <v>108019.65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Ethereum_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1839,28 +1839,28 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
         <v>0</v>
@@ -1869,13 +1869,13 @@
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>5.91</v>
+        <v>6.32</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>105905.71</v>
+        <v>106320.5</v>
       </c>
     </row>
     <row r="30">
@@ -1924,16 +1924,16 @@
         <v>50</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>5.35</v>
+        <v>4.65</v>
       </c>
       <c r="N30" s="8" t="n">
-        <v>105352.81</v>
+        <v>104648.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index</t>
+          <t>Coffee_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>2</v>
@@ -1976,16 +1976,16 @@
         <v>50</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>3.95</v>
+        <v>2.3</v>
       </c>
       <c r="N31" s="8" t="n">
-        <v>103950</v>
+        <v>102297.64</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -2007,16 +2007,16 @@
         <v>73</v>
       </c>
       <c r="F32" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G32" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G32" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="H32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>0</v>
@@ -2025,19 +2025,19 @@
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>3.28</v>
+        <v>1.38</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>103277.04</v>
+        <v>101381.74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>iShares_Silver_Trust</t>
+          <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -2059,16 +2059,16 @@
         <v>73</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="6" t="n">
         <v>0</v>
@@ -2076,18 +2076,20 @@
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="6" t="n"/>
-      <c r="M33" s="9" t="n">
-        <v>0</v>
+      <c r="L33" s="6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>100000</v>
+        <v>100688.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>JPY_EUR_Cross_Rate</t>
+          <t>iShares_Silver_Trust</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -2097,7 +2099,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -2106,7 +2108,7 @@
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>0</v>
@@ -2137,7 +2139,7 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>NASDAQ_100_Index</t>
+          <t>JPY_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -2147,7 +2149,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -2156,7 +2158,7 @@
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>0</v>
@@ -2187,7 +2189,7 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>NIKKEI_225_Index</t>
+          <t>NASDAQ_100_Index</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2197,7 +2199,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -2237,7 +2239,7 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>ProShares_UltraPro_Dow</t>
+          <t>NIKKEI_225_Index</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -2247,7 +2249,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -2256,7 +2258,7 @@
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>0</v>
@@ -2287,7 +2289,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>SPDR_Gold_Shares</t>
+          <t>ProShares_UltraPro_Dow</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2306,7 +2308,7 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>0</v>
@@ -2337,7 +2339,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>United_States_Natural_Gas_Fund_LP</t>
+          <t>SPDR_Gold_Shares</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -2347,7 +2349,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -2387,7 +2389,7 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>United_States_Natural_Gas_Fund_LP</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -2397,7 +2399,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -2409,13 +2411,13 @@
         <v>73</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
@@ -2426,20 +2428,18 @@
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="10" t="n">
-        <v>-1</v>
+      <c r="L40" s="6" t="n"/>
+      <c r="M40" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -2458,40 +2458,40 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="M41" s="10" t="n">
-        <v>-1.01</v>
+        <v>-1.57</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>98990.10000000001</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2510,40 +2510,40 @@
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="M42" s="10" t="n">
-        <v>-2.97</v>
+        <v>-1.6</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>97029.89999999999</v>
+        <v>98402.64999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 5R, or an opposite reversal nearer than 5R), starting capital 100,000, risk 1.0%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 04:17 UTC.</t>
+          <t>quickfix daily (target = 2.5R, or an opposite reversal nearer than 2.5R), starting capital 100,000, risk 1.573%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 06:17 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2571,7 +2571,7 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
@@ -2689,7 +2689,7 @@
         <v>74618</v>
       </c>
       <c r="I2" t="n">
-        <v>85958</v>
+        <v>81233</v>
       </c>
       <c r="J2" t="n">
         <v>74618</v>
@@ -2703,13 +2703,13 @@
         <v>-1</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N2" t="n">
         <v>100000</v>
       </c>
       <c r="O2" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="3">
@@ -2733,11 +2733,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>62630</v>
@@ -2746,27 +2746,27 @@
         <v>60074</v>
       </c>
       <c r="I3" t="n">
-        <v>75410</v>
+        <v>69020</v>
       </c>
       <c r="J3" t="n">
-        <v>68696</v>
+        <v>69020</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>bullish_reversal</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.3732</v>
+        <v>2.5</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2.3732</v>
+        <v>3.9325</v>
       </c>
       <c r="N3" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O3" t="n">
-        <v>101349.51</v>
+        <v>102297.64</v>
       </c>
     </row>
     <row r="4">
@@ -2803,10 +2803,10 @@
         <v>76101</v>
       </c>
       <c r="I4" t="n">
-        <v>72123</v>
+        <v>73780</v>
       </c>
       <c r="J4" t="n">
-        <v>72123</v>
+        <v>73780</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -2814,16 +2814,16 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N4" t="n">
-        <v>101349.51</v>
+        <v>102297.64</v>
       </c>
       <c r="O4" t="n">
-        <v>106416.98</v>
+        <v>106320.5</v>
       </c>
     </row>
     <row r="5">
@@ -2860,7 +2860,7 @@
         <v>76040</v>
       </c>
       <c r="I5" t="n">
-        <v>69200</v>
+        <v>72050</v>
       </c>
       <c r="J5" t="n">
         <v>76040</v>
@@ -2874,13 +2874,13 @@
         <v>-1</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N5" t="n">
-        <v>106416.98</v>
+        <v>106320.5</v>
       </c>
       <c r="O5" t="n">
-        <v>105352.81</v>
+        <v>104648.08</v>
       </c>
     </row>
     <row r="6">
@@ -2917,10 +2917,10 @@
         <v>80226</v>
       </c>
       <c r="I6" t="n">
-        <v>77310</v>
+        <v>78525</v>
       </c>
       <c r="J6" t="n">
-        <v>77310</v>
+        <v>78525</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2928,16 +2928,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N6" t="n">
         <v>100000</v>
       </c>
       <c r="O6" t="n">
-        <v>105000</v>
+        <v>103932.5</v>
       </c>
     </row>
     <row r="7">
@@ -2974,10 +2974,10 @@
         <v>83601</v>
       </c>
       <c r="I7" t="n">
-        <v>80271</v>
+        <v>81658</v>
       </c>
       <c r="J7" t="n">
-        <v>80271</v>
+        <v>81658</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2985,16 +2985,16 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N7" t="n">
-        <v>105000</v>
+        <v>103932.5</v>
       </c>
       <c r="O7" t="n">
-        <v>110250</v>
+        <v>108019.65</v>
       </c>
     </row>
     <row r="8">
@@ -3018,11 +3018,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>662.6</v>
@@ -3031,10 +3031,10 @@
         <v>671.5</v>
       </c>
       <c r="I8" t="n">
-        <v>618.1</v>
+        <v>640.4</v>
       </c>
       <c r="J8" t="n">
-        <v>618.1</v>
+        <v>640.4</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3042,16 +3042,16 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N8" t="n">
         <v>100000</v>
       </c>
       <c r="O8" t="n">
-        <v>105000</v>
+        <v>103932.5</v>
       </c>
     </row>
     <row r="9">
@@ -3088,10 +3088,10 @@
         <v>688.3</v>
       </c>
       <c r="I9" t="n">
-        <v>644.5</v>
+        <v>662.7</v>
       </c>
       <c r="J9" t="n">
-        <v>644.5</v>
+        <v>662.7</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3099,16 +3099,16 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N9" t="n">
-        <v>105000</v>
+        <v>103932.5</v>
       </c>
       <c r="O9" t="n">
-        <v>110250</v>
+        <v>108019.65</v>
       </c>
     </row>
     <row r="10">
@@ -3132,11 +3132,11 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>577.5</v>
@@ -3145,27 +3145,27 @@
         <v>570.9</v>
       </c>
       <c r="I10" t="n">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="J10" t="n">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>bullish_reversal</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.9242</v>
+        <v>2.5</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4.9242</v>
+        <v>3.9325</v>
       </c>
       <c r="N10" t="n">
-        <v>110250</v>
+        <v>108019.65</v>
       </c>
       <c r="O10" t="n">
-        <v>115678.98</v>
+        <v>112267.52</v>
       </c>
     </row>
     <row r="11">
@@ -3202,10 +3202,10 @@
         <v>573.9</v>
       </c>
       <c r="I11" t="n">
-        <v>598.5</v>
+        <v>588.2</v>
       </c>
       <c r="J11" t="n">
-        <v>598.5</v>
+        <v>588.2</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -3213,16 +3213,16 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N11" t="n">
-        <v>115678.98</v>
+        <v>112267.52</v>
       </c>
       <c r="O11" t="n">
-        <v>121462.93</v>
+        <v>116682.44</v>
       </c>
     </row>
     <row r="12">
@@ -3259,7 +3259,7 @@
         <v>653.1</v>
       </c>
       <c r="I12" t="n">
-        <v>604.5</v>
+        <v>624.8</v>
       </c>
       <c r="J12" t="n">
         <v>653.1</v>
@@ -3273,13 +3273,13 @@
         <v>-1</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N12" t="n">
-        <v>121462.93</v>
+        <v>116682.44</v>
       </c>
       <c r="O12" t="n">
-        <v>120248.3</v>
+        <v>114847.02</v>
       </c>
     </row>
     <row r="13">
@@ -3308,7 +3308,7 @@
         <v>711.3</v>
       </c>
       <c r="I13" t="n">
-        <v>679.5</v>
+        <v>692.7</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>120248.3</v>
+        <v>114847.02</v>
       </c>
       <c r="O13" t="n">
-        <v>120248.3</v>
+        <v>114847.02</v>
       </c>
     </row>
     <row r="14">
@@ -3356,27 +3356,24 @@
         <v>5050</v>
       </c>
       <c r="I14" t="n">
-        <v>5332</v>
-      </c>
-      <c r="J14" t="n">
-        <v>5050</v>
+        <v>5214</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L14" t="n">
         <v>-1</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N14" t="n">
         <v>100000</v>
       </c>
       <c r="O14" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="15">
@@ -3413,7 +3410,7 @@
         <v>3930</v>
       </c>
       <c r="I15" t="n">
-        <v>4842</v>
+        <v>4462</v>
       </c>
       <c r="J15" t="n">
         <v>3930</v>
@@ -3427,13 +3424,13 @@
         <v>-1</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N15" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O15" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="16">
@@ -3457,11 +3454,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
         <v>2990</v>
@@ -3470,27 +3467,27 @@
         <v>2951</v>
       </c>
       <c r="I16" t="n">
-        <v>3185</v>
+        <v>3088</v>
       </c>
       <c r="J16" t="n">
-        <v>2951</v>
+        <v>3088</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N16" t="n">
-        <v>98010</v>
+        <v>96878.74000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>97029.89999999999</v>
+        <v>100688.5</v>
       </c>
     </row>
     <row r="17">
@@ -3527,7 +3524,7 @@
         <v>382.86</v>
       </c>
       <c r="I17" t="n">
-        <v>352.5</v>
+        <v>365.15</v>
       </c>
       <c r="J17" t="n">
         <v>382.86</v>
@@ -3541,13 +3538,13 @@
         <v>-1</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N17" t="n">
         <v>100000</v>
       </c>
       <c r="O17" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="18">
@@ -3571,11 +3568,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
         <v>345.1</v>
@@ -3584,27 +3581,27 @@
         <v>341.79</v>
       </c>
       <c r="I18" t="n">
-        <v>361.65</v>
+        <v>353.38</v>
       </c>
       <c r="J18" t="n">
-        <v>359.4</v>
+        <v>353.38</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>bullish_reversal</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.3202</v>
+        <v>2.5</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4.3202</v>
+        <v>3.9325</v>
       </c>
       <c r="N18" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O18" t="n">
-        <v>103277.04</v>
+        <v>102297.64</v>
       </c>
     </row>
     <row r="19">
@@ -3641,27 +3638,24 @@
         <v>480.1</v>
       </c>
       <c r="I19" t="n">
-        <v>468.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>480.1</v>
+        <v>473.4</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>-1</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N19" t="n">
         <v>100000</v>
       </c>
       <c r="O19" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="20">
@@ -3698,10 +3692,10 @@
         <v>487.5</v>
       </c>
       <c r="I20" t="n">
-        <v>480.9</v>
+        <v>483.6</v>
       </c>
       <c r="J20" t="n">
-        <v>480.9</v>
+        <v>483.6</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -3709,16 +3703,16 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N20" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O20" t="n">
-        <v>103950</v>
+        <v>102297.64</v>
       </c>
     </row>
     <row r="21">
@@ -3755,7 +3749,7 @@
         <v>408.3</v>
       </c>
       <c r="I21" t="n">
-        <v>424.5</v>
+        <v>417.8</v>
       </c>
       <c r="J21" t="n">
         <v>408.3</v>
@@ -3769,13 +3763,13 @@
         <v>-1</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N21" t="n">
-        <v>103950</v>
+        <v>102297.64</v>
       </c>
       <c r="O21" t="n">
-        <v>102910.5</v>
+        <v>100688.5</v>
       </c>
     </row>
     <row r="22">
@@ -3804,7 +3798,7 @@
         <v>492.1</v>
       </c>
       <c r="I22" t="n">
-        <v>468.1</v>
+        <v>478.1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3812,10 +3806,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>102910.5</v>
+        <v>100688.5</v>
       </c>
       <c r="O22" t="n">
-        <v>102910.5</v>
+        <v>100688.5</v>
       </c>
     </row>
     <row r="23">
@@ -3852,10 +3846,10 @@
         <v>49811</v>
       </c>
       <c r="I23" t="n">
-        <v>49445</v>
+        <v>49598</v>
       </c>
       <c r="J23" t="n">
-        <v>49445</v>
+        <v>49598</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3863,16 +3857,16 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N23" t="n">
         <v>100000</v>
       </c>
       <c r="O23" t="n">
-        <v>105000</v>
+        <v>103932.5</v>
       </c>
     </row>
     <row r="24">
@@ -3909,10 +3903,10 @@
         <v>51850</v>
       </c>
       <c r="I24" t="n">
-        <v>51214</v>
+        <v>51479</v>
       </c>
       <c r="J24" t="n">
-        <v>51214</v>
+        <v>51479</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3920,16 +3914,16 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N24" t="n">
-        <v>105000</v>
+        <v>103932.5</v>
       </c>
       <c r="O24" t="n">
-        <v>110250</v>
+        <v>108019.65</v>
       </c>
     </row>
     <row r="25">
@@ -3966,7 +3960,7 @@
         <v>53106</v>
       </c>
       <c r="I25" t="n">
-        <v>50874</v>
+        <v>51804</v>
       </c>
       <c r="J25" t="n">
         <v>53106</v>
@@ -3980,13 +3974,13 @@
         <v>-1</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N25" t="n">
-        <v>110250</v>
+        <v>108019.65</v>
       </c>
       <c r="O25" t="n">
-        <v>109147.5</v>
+        <v>106320.5</v>
       </c>
     </row>
     <row r="26">
@@ -4023,27 +4017,24 @@
         <v>1.17986</v>
       </c>
       <c r="I26" t="n">
-        <v>1.1705</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1.17986</v>
+        <v>1.1744</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L26" t="n">
         <v>-1</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N26" t="n">
         <v>100000</v>
       </c>
       <c r="O26" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="27">
@@ -4065,6 +4056,14 @@
           <t>2026-06-24</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
       <c r="G27" t="n">
         <v>1.1391</v>
       </c>
@@ -4072,18 +4071,27 @@
         <v>1.13634</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1529</v>
+        <v>1.146</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.146</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N27" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="O27" t="n">
-        <v>99000</v>
+        <v>102297.64</v>
       </c>
     </row>
     <row r="28">
@@ -4120,10 +4128,10 @@
         <v>6073.35</v>
       </c>
       <c r="I28" t="n">
-        <v>5893.65</v>
+        <v>5968.52</v>
       </c>
       <c r="J28" t="n">
-        <v>5893.65</v>
+        <v>5968.52</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4131,16 +4139,16 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N28" t="n">
         <v>100000</v>
       </c>
       <c r="O28" t="n">
-        <v>105000</v>
+        <v>103932.5</v>
       </c>
     </row>
     <row r="29">
@@ -4164,11 +4172,11 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>6060.23</v>
@@ -4177,84 +4185,84 @@
         <v>6078.29</v>
       </c>
       <c r="I29" t="n">
-        <v>5969.93</v>
+        <v>6015.08</v>
       </c>
       <c r="J29" t="n">
-        <v>6078.29</v>
+        <v>6015.08</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M29" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N29" t="n">
-        <v>105000</v>
+        <v>103932.5</v>
       </c>
       <c r="O29" t="n">
-        <v>103950</v>
+        <v>108019.65</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance</t>
+          <t>EURO_STOXX_50_Index</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>2812</v>
+        <v>6060.23</v>
       </c>
       <c r="H30" t="n">
-        <v>2754</v>
+        <v>6099.08</v>
       </c>
       <c r="I30" t="n">
-        <v>3102</v>
+        <v>5963.1</v>
       </c>
       <c r="J30" t="n">
-        <v>2754</v>
+        <v>5963.1</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N30" t="n">
-        <v>100000</v>
+        <v>108019.65</v>
       </c>
       <c r="O30" t="n">
-        <v>99000</v>
+        <v>112267.52</v>
       </c>
     </row>
     <row r="31">
@@ -4264,7 +4272,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4273,45 +4281,45 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>1818</v>
+        <v>2812</v>
       </c>
       <c r="H31" t="n">
-        <v>1799</v>
+        <v>2754</v>
       </c>
       <c r="I31" t="n">
-        <v>1913</v>
+        <v>2957</v>
       </c>
       <c r="J31" t="n">
-        <v>1913</v>
+        <v>2754</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5</v>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>-1.573</v>
       </c>
       <c r="N31" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="O31" t="n">
-        <v>103950</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="32">
@@ -4321,37 +4329,37 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>2370</v>
+        <v>1818</v>
       </c>
       <c r="H32" t="n">
-        <v>2386</v>
+        <v>1799</v>
       </c>
       <c r="I32" t="n">
-        <v>2290</v>
+        <v>1866</v>
       </c>
       <c r="J32" t="n">
-        <v>2290</v>
+        <v>1866</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4359,26 +4367,26 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N32" t="n">
-        <v>103950</v>
+        <v>98427</v>
       </c>
       <c r="O32" t="n">
-        <v>109147.5</v>
+        <v>102297.64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>German_Long_Bund</t>
+          <t>Ethereum_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4387,28 +4395,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>127.47</v>
+        <v>2370</v>
       </c>
       <c r="H33" t="n">
-        <v>127.7</v>
+        <v>2386</v>
       </c>
       <c r="I33" t="n">
-        <v>126.32</v>
+        <v>2330</v>
       </c>
       <c r="J33" t="n">
-        <v>126.32</v>
+        <v>2330</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4416,22 +4424,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N33" t="n">
-        <v>100000</v>
+        <v>102297.64</v>
       </c>
       <c r="O33" t="n">
-        <v>105000</v>
+        <v>106320.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>German_Long_Bund</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -4444,28 +4452,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>4393</v>
+        <v>127.47</v>
       </c>
       <c r="H34" t="n">
-        <v>4409.6</v>
+        <v>127.7</v>
       </c>
       <c r="I34" t="n">
-        <v>4310</v>
+        <v>126.89</v>
       </c>
       <c r="J34" t="n">
-        <v>4310</v>
+        <v>126.89</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4473,16 +4481,16 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N34" t="n">
         <v>100000</v>
       </c>
       <c r="O34" t="n">
-        <v>105000</v>
+        <v>103932.5</v>
       </c>
     </row>
     <row r="35">
@@ -4492,7 +4500,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4501,45 +4509,45 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
         <v>4393</v>
       </c>
       <c r="H35" t="n">
-        <v>4420.6</v>
+        <v>4409.6</v>
       </c>
       <c r="I35" t="n">
-        <v>4255</v>
+        <v>4351.5</v>
       </c>
       <c r="J35" t="n">
-        <v>4420.6</v>
+        <v>4351.5</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M35" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N35" t="n">
-        <v>105000</v>
+        <v>100000</v>
       </c>
       <c r="O35" t="n">
-        <v>103950</v>
+        <v>103932.5</v>
       </c>
     </row>
     <row r="36">
@@ -4549,7 +4557,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4558,45 +4566,45 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>5358.1</v>
+        <v>4393</v>
       </c>
       <c r="H36" t="n">
-        <v>5434.2</v>
+        <v>4420.6</v>
       </c>
       <c r="I36" t="n">
-        <v>4977.6</v>
+        <v>4324</v>
       </c>
       <c r="J36" t="n">
-        <v>5035</v>
+        <v>4324</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>bearish_reversal</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.2457</v>
+        <v>2.5</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4.2457</v>
+        <v>3.9325</v>
       </c>
       <c r="N36" t="n">
-        <v>103950</v>
+        <v>103932.5</v>
       </c>
       <c r="O36" t="n">
-        <v>108363.44</v>
+        <v>108019.65</v>
       </c>
     </row>
     <row r="37">
@@ -4606,37 +4614,37 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>4335</v>
+        <v>5358.1</v>
       </c>
       <c r="H37" t="n">
-        <v>4306.2</v>
+        <v>5434.2</v>
       </c>
       <c r="I37" t="n">
-        <v>4479</v>
+        <v>5167.8</v>
       </c>
       <c r="J37" t="n">
-        <v>4479</v>
+        <v>5167.8</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4644,16 +4652,16 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N37" t="n">
-        <v>108363.44</v>
+        <v>108019.65</v>
       </c>
       <c r="O37" t="n">
-        <v>113781.61</v>
+        <v>112267.52</v>
       </c>
     </row>
     <row r="38">
@@ -4663,51 +4671,54 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>4746</v>
+        <v>4335</v>
       </c>
       <c r="H38" t="n">
-        <v>4758.5</v>
+        <v>4306.2</v>
       </c>
       <c r="I38" t="n">
-        <v>4683.5</v>
+        <v>4407</v>
+      </c>
+      <c r="J38" t="n">
+        <v>4407</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N38" t="n">
-        <v>113781.61</v>
+        <v>112267.52</v>
       </c>
       <c r="O38" t="n">
-        <v>112643.79</v>
+        <v>116682.44</v>
       </c>
     </row>
     <row r="39">
@@ -4717,54 +4728,51 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>4347</v>
+        <v>4746</v>
       </c>
       <c r="H39" t="n">
-        <v>4292.9</v>
+        <v>4758.5</v>
       </c>
       <c r="I39" t="n">
-        <v>4617.5</v>
-      </c>
-      <c r="J39" t="n">
-        <v>4292.9</v>
+        <v>4714.8</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L39" t="n">
         <v>-1</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N39" t="n">
-        <v>112643.79</v>
+        <v>116682.44</v>
       </c>
       <c r="O39" t="n">
-        <v>111517.35</v>
+        <v>114847.02</v>
       </c>
     </row>
     <row r="40">
@@ -4774,7 +4782,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4783,45 +4791,45 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>4103</v>
+        <v>4347</v>
       </c>
       <c r="H40" t="n">
-        <v>4046.1</v>
+        <v>4292.9</v>
       </c>
       <c r="I40" t="n">
-        <v>4387.5</v>
+        <v>4482.3</v>
       </c>
       <c r="J40" t="n">
-        <v>4387.5</v>
+        <v>4292.9</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>5</v>
-      </c>
-      <c r="M40" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>-1.573</v>
       </c>
       <c r="N40" t="n">
-        <v>111517.35</v>
+        <v>114847.02</v>
       </c>
       <c r="O40" t="n">
-        <v>117093.22</v>
+        <v>113040.48</v>
       </c>
     </row>
     <row r="41">
@@ -4831,7 +4839,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4840,28 +4848,28 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>3984</v>
+        <v>4103</v>
       </c>
       <c r="H41" t="n">
-        <v>3955.3</v>
+        <v>4046.1</v>
       </c>
       <c r="I41" t="n">
-        <v>4127.5</v>
+        <v>4245.2</v>
       </c>
       <c r="J41" t="n">
-        <v>4127.5</v>
+        <v>4245.2</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -4869,16 +4877,16 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N41" t="n">
-        <v>117093.22</v>
+        <v>113040.48</v>
       </c>
       <c r="O41" t="n">
-        <v>122947.88</v>
+        <v>117485.8</v>
       </c>
     </row>
     <row r="42">
@@ -4888,7 +4896,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4897,28 +4905,28 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
         <v>3984</v>
       </c>
       <c r="H42" t="n">
-        <v>3962.9</v>
+        <v>3955.3</v>
       </c>
       <c r="I42" t="n">
-        <v>4089.5</v>
+        <v>4055.7</v>
       </c>
       <c r="J42" t="n">
-        <v>4089.5</v>
+        <v>4055.7</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -4926,79 +4934,79 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N42" t="n">
-        <v>122947.88</v>
+        <v>117485.8</v>
       </c>
       <c r="O42" t="n">
-        <v>129095.28</v>
+        <v>122105.93</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0.006417</v>
+        <v>3984</v>
       </c>
       <c r="H43" t="n">
-        <v>0.006454</v>
+        <v>3962.9</v>
       </c>
       <c r="I43" t="n">
-        <v>0.006254</v>
+        <v>4036.8</v>
       </c>
       <c r="J43" t="n">
-        <v>0.006454</v>
+        <v>4036.8</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M43" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N43" t="n">
-        <v>100000</v>
+        <v>122105.93</v>
       </c>
       <c r="O43" t="n">
-        <v>99000</v>
+        <v>126907.74</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -5011,28 +5019,28 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>239.06</v>
+        <v>0.006417</v>
       </c>
       <c r="H44" t="n">
-        <v>239.73</v>
+        <v>0.006454</v>
       </c>
       <c r="I44" t="n">
-        <v>235.71</v>
+        <v>0.006324</v>
       </c>
       <c r="J44" t="n">
-        <v>239.73</v>
+        <v>0.006454</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -5043,13 +5051,13 @@
         <v>-1</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N44" t="n">
         <v>100000</v>
       </c>
       <c r="O44" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="45">
@@ -5059,7 +5067,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5068,45 +5076,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>251.58</v>
+        <v>239.06</v>
       </c>
       <c r="H45" t="n">
-        <v>251.91</v>
+        <v>239.73</v>
       </c>
       <c r="I45" t="n">
-        <v>249.93</v>
-      </c>
-      <c r="J45" t="n">
-        <v>249.93</v>
+        <v>237.39</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5</v>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>-1.573</v>
       </c>
       <c r="N45" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="O45" t="n">
-        <v>103950</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="46">
@@ -5116,7 +5121,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5125,28 +5130,28 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>255.38</v>
+        <v>251.58</v>
       </c>
       <c r="H46" t="n">
-        <v>256.63</v>
+        <v>251.91</v>
       </c>
       <c r="I46" t="n">
-        <v>249.13</v>
+        <v>250.76</v>
       </c>
       <c r="J46" t="n">
-        <v>249.13</v>
+        <v>250.76</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -5154,16 +5159,16 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N46" t="n">
-        <v>103950</v>
+        <v>98427</v>
       </c>
       <c r="O46" t="n">
-        <v>109147.5</v>
+        <v>102297.64</v>
       </c>
     </row>
     <row r="47">
@@ -5173,64 +5178,64 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>235.2</v>
+        <v>255.38</v>
       </c>
       <c r="H47" t="n">
-        <v>234.36</v>
+        <v>256.63</v>
       </c>
       <c r="I47" t="n">
-        <v>239.4</v>
+        <v>252.25</v>
       </c>
       <c r="J47" t="n">
-        <v>234.36</v>
+        <v>252.25</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M47" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N47" t="n">
-        <v>109147.5</v>
+        <v>102297.64</v>
       </c>
       <c r="O47" t="n">
-        <v>108056.02</v>
+        <v>106320.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5239,45 +5244,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>5.7714</v>
+        <v>235.2</v>
       </c>
       <c r="H48" t="n">
-        <v>5.6849</v>
+        <v>234.36</v>
       </c>
       <c r="I48" t="n">
-        <v>6.2039</v>
+        <v>237.3</v>
       </c>
       <c r="J48" t="n">
-        <v>5.6849</v>
+        <v>237.3</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N48" t="n">
-        <v>100000</v>
+        <v>106320.5</v>
       </c>
       <c r="O48" t="n">
-        <v>99000</v>
+        <v>110501.55</v>
       </c>
     </row>
     <row r="49">
@@ -5287,7 +5292,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5296,12 +5301,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5311,13 +5316,13 @@
         <v>5.7714</v>
       </c>
       <c r="H49" t="n">
-        <v>5.6774</v>
+        <v>5.6849</v>
       </c>
       <c r="I49" t="n">
-        <v>6.116</v>
+        <v>5.9877</v>
       </c>
       <c r="J49" t="n">
-        <v>5.6774</v>
+        <v>5.6849</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -5328,13 +5333,13 @@
         <v>-1</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N49" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="O49" t="n">
-        <v>98010</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="50">
@@ -5344,7 +5349,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5353,45 +5358,45 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>5.3133</v>
+        <v>5.7714</v>
       </c>
       <c r="H50" t="n">
-        <v>5.2459</v>
+        <v>5.6774</v>
       </c>
       <c r="I50" t="n">
-        <v>5.6503</v>
+        <v>6.0064</v>
       </c>
       <c r="J50" t="n">
-        <v>5.6503</v>
+        <v>5.6774</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>-1.573</v>
       </c>
       <c r="N50" t="n">
-        <v>98010</v>
+        <v>98427</v>
       </c>
       <c r="O50" t="n">
-        <v>102910.5</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="51">
@@ -5401,64 +5406,64 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>6.0956</v>
+        <v>5.3133</v>
       </c>
       <c r="H51" t="n">
-        <v>6.1481</v>
+        <v>5.2459</v>
       </c>
       <c r="I51" t="n">
-        <v>5.8331</v>
+        <v>5.4818</v>
       </c>
       <c r="J51" t="n">
-        <v>6.1481</v>
+        <v>5.4818</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N51" t="n">
-        <v>102910.5</v>
+        <v>96878.74000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>101881.4</v>
+        <v>100688.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5467,28 +5472,28 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
-        <v>3.305</v>
+        <v>6.0956</v>
       </c>
       <c r="H52" t="n">
-        <v>3.354</v>
+        <v>6.1481</v>
       </c>
       <c r="I52" t="n">
-        <v>3.095</v>
+        <v>5.9644</v>
       </c>
       <c r="J52" t="n">
-        <v>3.354</v>
+        <v>6.1481</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -5499,13 +5504,13 @@
         <v>-1</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N52" t="n">
-        <v>100000</v>
+        <v>100688.5</v>
       </c>
       <c r="O52" t="n">
-        <v>99000</v>
+        <v>99104.67</v>
       </c>
     </row>
     <row r="53">
@@ -5515,7 +5520,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5524,12 +5529,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5539,87 +5544,87 @@
         <v>3.305</v>
       </c>
       <c r="H53" t="n">
-        <v>3.356</v>
+        <v>3.354</v>
       </c>
       <c r="I53" t="n">
-        <v>3.12</v>
+        <v>3.183</v>
       </c>
       <c r="J53" t="n">
-        <v>3.12</v>
+        <v>3.354</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>bearish_reversal</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.6275</v>
-      </c>
-      <c r="M53" s="2" t="n">
-        <v>3.6275</v>
+        <v>-1</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>-1.573</v>
       </c>
       <c r="N53" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="O53" t="n">
-        <v>102591.18</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>1360.4</v>
+        <v>3.305</v>
       </c>
       <c r="H54" t="n">
-        <v>1343.4</v>
+        <v>3.356</v>
       </c>
       <c r="I54" t="n">
-        <v>1445.4</v>
+        <v>3.178</v>
       </c>
       <c r="J54" t="n">
-        <v>1343.4</v>
+        <v>3.178</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N54" t="n">
-        <v>100000</v>
+        <v>98427</v>
       </c>
       <c r="O54" t="n">
-        <v>99000</v>
+        <v>102297.64</v>
       </c>
     </row>
     <row r="55">
@@ -5629,7 +5634,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -5638,28 +5643,28 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H55" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="I55" t="n">
-        <v>1205</v>
+        <v>1402.9</v>
       </c>
       <c r="J55" t="n">
-        <v>1205</v>
+        <v>1402.9</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -5667,73 +5672,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N55" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="O55" t="n">
-        <v>103950</v>
+        <v>103932.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H56" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="I56" t="n">
-        <v>1939.1</v>
+        <v>1186</v>
       </c>
       <c r="J56" t="n">
-        <v>2113.7</v>
+        <v>1186</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N56" t="n">
-        <v>100000</v>
+        <v>103932.5</v>
       </c>
       <c r="O56" t="n">
-        <v>99000</v>
+        <v>108019.65</v>
       </c>
     </row>
     <row r="57">
@@ -5743,37 +5748,37 @@
         </is>
       </c>
       <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
         <v>2</v>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
       <c r="G57" t="n">
-        <v>1641.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H57" t="n">
-        <v>1621</v>
+        <v>2113.7</v>
       </c>
       <c r="I57" t="n">
-        <v>1744</v>
+        <v>2011.9</v>
       </c>
       <c r="J57" t="n">
-        <v>1621</v>
+        <v>2113.7</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5784,13 +5789,13 @@
         <v>-1</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N57" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="O57" t="n">
-        <v>98010</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="58">
@@ -5800,7 +5805,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -5809,28 +5814,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1581.5</v>
+        <v>1641.5</v>
       </c>
       <c r="H58" t="n">
-        <v>1547.6</v>
+        <v>1621</v>
       </c>
       <c r="I58" t="n">
-        <v>1751</v>
+        <v>1692.8</v>
       </c>
       <c r="J58" t="n">
-        <v>1547.6</v>
+        <v>1621</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5841,53 +5846,53 @@
         <v>-1</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N58" t="n">
-        <v>98010</v>
+        <v>98427</v>
       </c>
       <c r="O58" t="n">
-        <v>97029.89999999999</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G59" t="n">
-        <v>27907</v>
+        <v>1581.5</v>
       </c>
       <c r="H59" t="n">
-        <v>27965.76</v>
+        <v>1547.6</v>
       </c>
       <c r="I59" t="n">
-        <v>27613.2</v>
+        <v>1666.2</v>
       </c>
       <c r="J59" t="n">
-        <v>27965.76</v>
+        <v>1547.6</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5898,19 +5903,19 @@
         <v>-1</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N59" t="n">
-        <v>100000</v>
+        <v>96878.74000000001</v>
       </c>
       <c r="O59" t="n">
-        <v>99000</v>
+        <v>95354.84</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -5923,51 +5928,48 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>7206.55</v>
+        <v>27907</v>
       </c>
       <c r="H60" t="n">
-        <v>7223.26</v>
+        <v>27965.76</v>
       </c>
       <c r="I60" t="n">
-        <v>7123</v>
-      </c>
-      <c r="J60" t="n">
-        <v>7223.26</v>
+        <v>27760.1</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L60" t="n">
         <v>-1</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N60" t="n">
         <v>100000</v>
       </c>
       <c r="O60" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -5980,28 +5982,28 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>6957.43</v>
+        <v>7206.55</v>
       </c>
       <c r="H61" t="n">
-        <v>6965.7</v>
+        <v>7223.26</v>
       </c>
       <c r="I61" t="n">
-        <v>6916.08</v>
+        <v>7164.77</v>
       </c>
       <c r="J61" t="n">
-        <v>6916.08</v>
+        <v>7164.77</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -6009,16 +6011,16 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N61" t="n">
         <v>100000</v>
       </c>
       <c r="O61" t="n">
-        <v>105000</v>
+        <v>103932.5</v>
       </c>
     </row>
     <row r="62">
@@ -6028,7 +6030,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6037,45 +6039,45 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H62" t="n">
-        <v>6988.83</v>
+        <v>6965.7</v>
       </c>
       <c r="I62" t="n">
-        <v>6950.25</v>
+        <v>6936.76</v>
       </c>
       <c r="J62" t="n">
-        <v>6988.83</v>
+        <v>6936.76</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N62" t="n">
-        <v>105000</v>
+        <v>100000</v>
       </c>
       <c r="O62" t="n">
-        <v>103950</v>
+        <v>103932.5</v>
       </c>
     </row>
     <row r="63">
@@ -6085,7 +6087,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6094,12 +6096,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -6109,30 +6111,27 @@
         <v>6982.4</v>
       </c>
       <c r="H63" t="n">
-        <v>6992.85</v>
+        <v>6988.83</v>
       </c>
       <c r="I63" t="n">
-        <v>6930.15</v>
-      </c>
-      <c r="J63" t="n">
-        <v>6930.15</v>
+        <v>6966.32</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>5</v>
-      </c>
-      <c r="M63" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
+      </c>
+      <c r="M63" s="5" t="n">
+        <v>-1.573</v>
       </c>
       <c r="N63" t="n">
-        <v>103950</v>
+        <v>103932.5</v>
       </c>
       <c r="O63" t="n">
-        <v>109147.5</v>
+        <v>102297.64</v>
       </c>
     </row>
     <row r="64">
@@ -6142,7 +6141,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -6151,12 +6150,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -6166,27 +6165,30 @@
         <v>6982.4</v>
       </c>
       <c r="H64" t="n">
-        <v>6991.93</v>
+        <v>6992.85</v>
       </c>
       <c r="I64" t="n">
-        <v>6934.75</v>
+        <v>6956.27</v>
+      </c>
+      <c r="J64" t="n">
+        <v>6956.27</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N64" t="n">
-        <v>109147.5</v>
+        <v>102297.64</v>
       </c>
       <c r="O64" t="n">
-        <v>108056.02</v>
+        <v>106320.5</v>
       </c>
     </row>
     <row r="65">
@@ -6196,7 +6198,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -6205,12 +6207,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -6220,10 +6222,10 @@
         <v>6982.4</v>
       </c>
       <c r="H65" t="n">
-        <v>6986.84</v>
+        <v>6991.93</v>
       </c>
       <c r="I65" t="n">
-        <v>6960.2</v>
+        <v>6958.57</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -6234,13 +6236,13 @@
         <v>-1</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N65" t="n">
-        <v>108056.02</v>
+        <v>106320.5</v>
       </c>
       <c r="O65" t="n">
-        <v>106975.46</v>
+        <v>104648.08</v>
       </c>
     </row>
     <row r="66">
@@ -6250,94 +6252,91 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H66" t="n">
-        <v>6770.77</v>
+        <v>6986.84</v>
       </c>
       <c r="I66" t="n">
-        <v>6912.55</v>
-      </c>
-      <c r="J66" t="n">
-        <v>6770.77</v>
+        <v>6971.3</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L66" t="n">
         <v>-1</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N66" t="n">
-        <v>106975.46</v>
+        <v>104648.08</v>
       </c>
       <c r="O66" t="n">
-        <v>105905.71</v>
+        <v>103001.96</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>86.081</v>
+        <v>6794.4</v>
       </c>
       <c r="H67" t="n">
-        <v>88.001</v>
+        <v>6770.77</v>
       </c>
       <c r="I67" t="n">
-        <v>76.48099999999999</v>
+        <v>6853.48</v>
       </c>
       <c r="J67" t="n">
-        <v>88.001</v>
+        <v>6770.77</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -6348,13 +6347,13 @@
         <v>-1</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N67" t="n">
-        <v>100000</v>
+        <v>103001.96</v>
       </c>
       <c r="O67" t="n">
-        <v>99000</v>
+        <v>101381.74</v>
       </c>
     </row>
     <row r="68">
@@ -6364,37 +6363,37 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>73.84399999999999</v>
+        <v>86.081</v>
       </c>
       <c r="H68" t="n">
-        <v>71.999</v>
+        <v>88.001</v>
       </c>
       <c r="I68" t="n">
-        <v>83.069</v>
+        <v>81.28100000000001</v>
       </c>
       <c r="J68" t="n">
-        <v>71.999</v>
+        <v>88.001</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6405,53 +6404,53 @@
         <v>-1</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N68" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="O68" t="n">
-        <v>98010</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G69" t="n">
-        <v>15</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>15.26</v>
+        <v>71.999</v>
       </c>
       <c r="I69" t="n">
-        <v>13.7</v>
+        <v>78.456</v>
       </c>
       <c r="J69" t="n">
-        <v>15.26</v>
+        <v>71.999</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6462,19 +6461,19 @@
         <v>-1</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N69" t="n">
-        <v>100000</v>
+        <v>98427</v>
       </c>
       <c r="O69" t="n">
-        <v>99000</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -6487,28 +6486,28 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70" t="n">
-        <v>20.89</v>
+        <v>15</v>
       </c>
       <c r="H70" t="n">
-        <v>21.07</v>
+        <v>15.26</v>
       </c>
       <c r="I70" t="n">
-        <v>19.99</v>
+        <v>14.35</v>
       </c>
       <c r="J70" t="n">
-        <v>21.07</v>
+        <v>15.26</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6519,19 +6518,19 @@
         <v>-1</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N70" t="n">
         <v>100000</v>
       </c>
       <c r="O70" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -6544,28 +6543,28 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.8614000000000001</v>
+        <v>20.89</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8637</v>
+        <v>21.07</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8499</v>
+        <v>20.44</v>
       </c>
       <c r="J71" t="n">
-        <v>0.8637</v>
+        <v>21.07</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6576,13 +6575,13 @@
         <v>-1</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N71" t="n">
         <v>100000</v>
       </c>
       <c r="O71" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="72">
@@ -6592,7 +6591,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -6601,12 +6600,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -6616,13 +6615,13 @@
         <v>0.8614000000000001</v>
       </c>
       <c r="H72" t="n">
-        <v>0.8658</v>
+        <v>0.8637</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8418</v>
+        <v>0.8557</v>
       </c>
       <c r="J72" t="n">
-        <v>0.8658</v>
+        <v>0.8637</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6633,13 +6632,13 @@
         <v>-1</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N72" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="O72" t="n">
-        <v>98010</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="73">
@@ -6649,111 +6648,111 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.8467</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>0.8436</v>
+        <v>0.8658</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8622</v>
+        <v>0.8504</v>
       </c>
       <c r="J73" t="n">
-        <v>0.8498</v>
+        <v>0.8658</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
-      </c>
-      <c r="M73" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
+      </c>
+      <c r="M73" s="5" t="n">
+        <v>-1.573</v>
       </c>
       <c r="N73" t="n">
-        <v>98010</v>
+        <v>98427</v>
       </c>
       <c r="O73" t="n">
-        <v>98990.10000000001</v>
+        <v>96878.74000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>116.5</v>
+        <v>0.8467</v>
       </c>
       <c r="H74" t="n">
-        <v>116.79</v>
+        <v>0.8436</v>
       </c>
       <c r="I74" t="n">
-        <v>115.05</v>
+        <v>0.8544</v>
       </c>
       <c r="J74" t="n">
-        <v>116.79</v>
+        <v>0.8498</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v>-1</v>
+        <v>1</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>1.573</v>
       </c>
       <c r="N74" t="n">
-        <v>100000</v>
+        <v>96878.74000000001</v>
       </c>
       <c r="O74" t="n">
-        <v>99000</v>
+        <v>98402.64999999999</v>
       </c>
     </row>
     <row r="75">
@@ -6763,7 +6762,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -6772,28 +6771,28 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>118.02</v>
+        <v>116.5</v>
       </c>
       <c r="H75" t="n">
-        <v>118.16</v>
+        <v>116.79</v>
       </c>
       <c r="I75" t="n">
-        <v>117.32</v>
+        <v>115.77</v>
       </c>
       <c r="J75" t="n">
-        <v>118.16</v>
+        <v>116.79</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6804,70 +6803,70 @@
         <v>-1</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N75" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="O75" t="n">
-        <v>98010</v>
+        <v>98427</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G76" t="n">
-        <v>97.81399999999999</v>
+        <v>118.02</v>
       </c>
       <c r="H76" t="n">
-        <v>97.569</v>
+        <v>118.16</v>
       </c>
       <c r="I76" t="n">
-        <v>98.976</v>
+        <v>117.67</v>
       </c>
       <c r="J76" t="n">
-        <v>97.569</v>
+        <v>117.67</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M76" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N76" t="n">
-        <v>100000</v>
+        <v>98427</v>
       </c>
       <c r="O76" t="n">
-        <v>99000</v>
+        <v>102297.64</v>
       </c>
     </row>
     <row r="77">
@@ -6877,54 +6876,54 @@
         </is>
       </c>
       <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
         <v>2</v>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>11</v>
-      </c>
       <c r="G77" t="n">
-        <v>99.376</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>99.571</v>
+        <v>97.569</v>
       </c>
       <c r="I77" t="n">
-        <v>98.401</v>
+        <v>98.42700000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>99.571</v>
+        <v>98.42700000000001</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M77" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N77" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="O77" t="n">
-        <v>98010</v>
+        <v>103932.5</v>
       </c>
     </row>
     <row r="78">
@@ -6934,54 +6933,54 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="n">
-        <v>100.066</v>
+        <v>97.714</v>
       </c>
       <c r="H78" t="n">
-        <v>100.201</v>
+        <v>97.46899999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>99.39100000000001</v>
+        <v>98.327</v>
       </c>
       <c r="J78" t="n">
-        <v>100.201</v>
+        <v>98.327</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M78" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N78" t="n">
-        <v>98010</v>
+        <v>103932.5</v>
       </c>
       <c r="O78" t="n">
-        <v>97029.89999999999</v>
+        <v>108019.65</v>
       </c>
     </row>
     <row r="79">
@@ -6991,7 +6990,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -7000,45 +6999,45 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G79" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H79" t="n">
-        <v>100.361</v>
+        <v>99.571</v>
       </c>
       <c r="I79" t="n">
-        <v>99.004</v>
+        <v>98.889</v>
       </c>
       <c r="J79" t="n">
-        <v>100.361</v>
+        <v>98.889</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M79" s="5" t="n">
-        <v>-1</v>
+        <v>2.5</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>3.9325</v>
       </c>
       <c r="N79" t="n">
-        <v>97029.89999999999</v>
+        <v>108019.65</v>
       </c>
       <c r="O79" t="n">
-        <v>96059.60000000001</v>
+        <v>112267.52</v>
       </c>
     </row>
     <row r="80">
@@ -7048,7 +7047,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -7057,28 +7056,28 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80" t="n">
-        <v>100.621</v>
+        <v>99.246</v>
       </c>
       <c r="H80" t="n">
-        <v>100.911</v>
+        <v>99.501</v>
       </c>
       <c r="I80" t="n">
-        <v>99.17100000000001</v>
+        <v>98.608</v>
       </c>
       <c r="J80" t="n">
-        <v>100.911</v>
+        <v>99.501</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -7089,13 +7088,13 @@
         <v>-1</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>-1</v>
+        <v>-1.573</v>
       </c>
       <c r="N80" t="n">
-        <v>96059.60000000001</v>
+        <v>112267.52</v>
       </c>
       <c r="O80" t="n">
-        <v>95099</v>
+        <v>110501.55</v>
       </c>
     </row>
     <row r="81">
@@ -7105,7 +7104,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -7114,28 +7113,28 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H81" t="n">
-        <v>101.526</v>
+        <v>100.201</v>
       </c>
       <c r="I81" t="n">
-        <v>100.836</v>
+        <v>99.72799999999999</v>
       </c>
       <c r="J81" t="n">
-        <v>100.836</v>
+        <v>99.72799999999999</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -7143,26 +7142,26 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N81" t="n">
-        <v>95099</v>
+        <v>110501.55</v>
       </c>
       <c r="O81" t="n">
-        <v>99853.96000000001</v>
+        <v>114847.02</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -7171,28 +7170,28 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>121.72</v>
+        <v>100.066</v>
       </c>
       <c r="H82" t="n">
-        <v>123.03</v>
+        <v>100.316</v>
       </c>
       <c r="I82" t="n">
-        <v>115.17</v>
+        <v>99.441</v>
       </c>
       <c r="J82" t="n">
-        <v>115.17</v>
+        <v>99.441</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -7200,73 +7199,301 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>5</v>
+        <v>3.9325</v>
       </c>
       <c r="N82" t="n">
-        <v>100000</v>
+        <v>114847.02</v>
       </c>
       <c r="O82" t="n">
-        <v>105000</v>
+        <v>119363.38</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>7</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="n">
+        <v>100.066</v>
+      </c>
+      <c r="H83" t="n">
+        <v>100.361</v>
+      </c>
+      <c r="I83" t="n">
+        <v>99.328</v>
+      </c>
+      <c r="J83" t="n">
+        <v>100.361</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>-1.573</v>
+      </c>
+      <c r="N83" t="n">
+        <v>119363.38</v>
+      </c>
+      <c r="O83" t="n">
+        <v>117485.8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>8</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>2</v>
+      </c>
+      <c r="G84" t="n">
+        <v>100.621</v>
+      </c>
+      <c r="H84" t="n">
+        <v>100.911</v>
+      </c>
+      <c r="I84" t="n">
+        <v>99.896</v>
+      </c>
+      <c r="J84" t="n">
+        <v>100.911</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M84" s="5" t="n">
+        <v>-1.573</v>
+      </c>
+      <c r="N84" t="n">
+        <v>117485.8</v>
+      </c>
+      <c r="O84" t="n">
+        <v>115637.75</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>9</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H85" t="n">
+        <v>101.526</v>
+      </c>
+      <c r="I85" t="n">
+        <v>101.123</v>
+      </c>
+      <c r="J85" t="n">
+        <v>101.123</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>3.9325</v>
+      </c>
+      <c r="N85" t="n">
+        <v>115637.75</v>
+      </c>
+      <c r="O85" t="n">
+        <v>120185.2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B83" t="n">
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H86" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="I86" t="n">
+        <v>118.44</v>
+      </c>
+      <c r="J86" t="n">
+        <v>118.44</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>3.9325</v>
+      </c>
+      <c r="N86" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O86" t="n">
+        <v>103932.5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
         <v>2</v>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" t="n">
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
         <v>130.16</v>
       </c>
-      <c r="H83" t="n">
+      <c r="H87" t="n">
         <v>130.94</v>
       </c>
-      <c r="I83" t="n">
-        <v>126.26</v>
-      </c>
-      <c r="J83" t="n">
-        <v>126.26</v>
-      </c>
-      <c r="K83" t="inlineStr">
+      <c r="I87" t="n">
+        <v>128.21</v>
+      </c>
+      <c r="J87" t="n">
+        <v>128.21</v>
+      </c>
+      <c r="K87" t="inlineStr">
         <is>
           <t>target_r</t>
         </is>
       </c>
-      <c r="L83" t="n">
-        <v>5</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N83" t="n">
-        <v>105000</v>
-      </c>
-      <c r="O83" t="n">
-        <v>110250</v>
+      <c r="L87" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>3.9325</v>
+      </c>
+      <c r="N87" t="n">
+        <v>103932.5</v>
+      </c>
+      <c r="O87" t="n">
+        <v>108019.65</v>
       </c>
     </row>
   </sheetData>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 2.5R, or an opposite reversal nearer than 2.5R), starting capital 100,000, risk 1.573%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 06:17 UTC.</t>
+          <t>quickfix daily (target = 2.5R, or an opposite reversal nearer than 2.5R), starting capital 100,000, risk 1.573%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 08:10 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -582,10 +582,10 @@
         <v>77.8</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>26.91</v>
+        <v>30.61</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>126907.74</v>
+        <v>130607.61</v>
       </c>
     </row>
     <row r="3">
@@ -630,16 +630,16 @@
         <v>66.7</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>20.19</v>
+        <v>14.83</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>120185.2</v>
+        <v>114826.51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -657,10 +657,10 @@
         <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -672,28 +672,28 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>14.85</v>
+        <v>14.57</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>114847.02</v>
+        <v>114574.29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -702,46 +702,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10.5</v>
+        <v>11.75</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>110501.55</v>
+        <v>111748.11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -750,19 +750,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -771,25 +771,25 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8.02</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>108019.65</v>
+        <v>108964.11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>Bitcoin_Per_USD_CME</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -822,16 +822,16 @@
         <v>100</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8.02</v>
+        <v>8.66</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>108019.65</v>
+        <v>108661.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -852,34 +852,34 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6.32</v>
+        <v>6.22</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>106320.5</v>
+        <v>106218.27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>German_Long_Bund</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -894,13 +894,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -918,22 +918,22 @@
         <v>100</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3.93</v>
+        <v>6</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>103932.5</v>
+        <v>106000.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -945,10 +945,10 @@
         <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -966,16 +966,16 @@
         <v>100</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3.93</v>
+        <v>5.97</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>103932.5</v>
+        <v>105968.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>German_Long_Bund</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1011,19 +1011,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>102297.64</v>
+        <v>102937.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1041,13 +1041,13 @@
         <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1059,25 +1059,25 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>102297.64</v>
+        <v>102939.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1086,16 +1086,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1107,19 +1107,19 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>102297.64</v>
+        <v>102937.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1137,7 +1137,7 @@
         <v>64</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -1146,34 +1146,34 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.73</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>100688.5</v>
+        <v>101727.98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CME_SOFR_Futures_3M</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1202,17 +1202,20 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="4" t="n">
-        <v>0</v>
+      <c r="L15" t="n">
+        <v>50</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>1.73</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>100000</v>
+        <v>101727.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Global_X_Uranium_ETF</t>
+          <t>CME_SOFR_Futures_3M</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1227,7 +1230,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1257,7 +1260,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Japanese_10_Year_Bond_Futures</t>
+          <t>Global_X_Uranium_ETF</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1272,7 +1275,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1302,7 +1305,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NY_Crude_Oil_Futures</t>
+          <t>Japanese_10_Year_Bond_Futures</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1317,7 +1320,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1347,13 +1350,13 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Proshares_VIX_Short_Term_Futures_ETF</t>
+          <t>NY_Crude_Oil_Futures</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1362,7 +1365,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1392,13 +1395,13 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>US_10_Year_T_Note_Futures</t>
+          <t>Proshares_VIX_Short_Term_Futures_ETF</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1407,7 +1410,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1437,13 +1440,13 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>US_10_Year_T_Note_Futures</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1452,16 +1455,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1472,26 +1475,23 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
-        <v>25</v>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v>-0.9</v>
+      <c r="M21" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>99104.67</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1500,16 +1500,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1521,19 +1521,19 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-1.57</v>
+        <v>-0.59</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>98427</v>
+        <v>99405.25999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1572,10 +1572,10 @@
         <v>0</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-1.57</v>
+        <v>-1.18</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
     </row>
     <row r="24">
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>-1.57</v>
+        <v>-1.18</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
     </row>
     <row r="25">
@@ -1668,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-3.12</v>
+        <v>-2.34</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>96878.74000000001</v>
+        <v>97663.81</v>
       </c>
     </row>
     <row r="26">
@@ -1716,16 +1716,16 @@
         <v>0</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>-4.65</v>
+        <v>-3.48</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>95354.84</v>
+        <v>96516.25999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index</t>
+          <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1744,13 +1744,13 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>0</v>
@@ -1768,16 +1768,16 @@
         <v>100</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>12.27</v>
+        <v>16.15</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>112267.52</v>
+        <v>116148.92</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>EURO_STOXX_50_Index</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1796,13 +1796,13 @@
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0</v>
@@ -1820,16 +1820,16 @@
         <v>100</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>8.02</v>
+        <v>9.07</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>108019.65</v>
+        <v>109073.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance</t>
+          <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1839,16 +1839,16 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>3</v>
@@ -1872,16 +1872,16 @@
         <v>66.7</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>6.32</v>
+        <v>5.74</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>106320.5</v>
+        <v>105741.78</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance</t>
+          <t>Ethereum_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1900,16 +1900,16 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
@@ -1921,19 +1921,19 @@
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="N30" s="8" t="n">
-        <v>104648.08</v>
+        <v>104716.24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures</t>
+          <t>Bitcoin_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1943,25 +1943,25 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="F31" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G31" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="H31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
@@ -1976,10 +1976,10 @@
         <v>50</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>2.3</v>
+        <v>4.21</v>
       </c>
       <c r="N31" s="8" t="n">
-        <v>102297.64</v>
+        <v>104207.25</v>
       </c>
     </row>
     <row r="32">
@@ -2013,10 +2013,10 @@
         <v>2</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>0</v>
@@ -2028,16 +2028,16 @@
         <v>33.3</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>1.38</v>
+        <v>2.6</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>101381.74</v>
+        <v>102599.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures</t>
+          <t>Coffee_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -2059,7 +2059,7 @@
         <v>73</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>1</v>
@@ -2068,7 +2068,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
         <v>0</v>
@@ -2077,13 +2077,13 @@
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.73</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>100688.5</v>
+        <v>101727.98</v>
       </c>
     </row>
     <row r="34">
@@ -2439,7 +2439,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -2458,40 +2458,40 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="M41" s="10" t="n">
-        <v>-1.57</v>
+        <v>-1.19</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>98427</v>
+        <v>98811.36</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2510,40 +2510,40 @@
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="M42" s="10" t="n">
-        <v>-1.6</v>
+        <v>-1.24</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>98402.64999999999</v>
+        <v>98759.72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 2.5R, or an opposite reversal nearer than 2.5R), starting capital 100,000, risk 1.573%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 08:10 UTC.</t>
+          <t>quickfix daily (target = 2.5R, or an opposite reversal nearer than 2.5R), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 09:49 UTC.</t>
         </is>
       </c>
     </row>
@@ -2703,13 +2703,13 @@
         <v>-1</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N2" t="n">
         <v>100000</v>
       </c>
       <c r="O2" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
     </row>
     <row r="3">
@@ -2749,7 +2749,7 @@
         <v>69020</v>
       </c>
       <c r="J3" t="n">
-        <v>69020</v>
+        <v>70581</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -2757,16 +2757,16 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.5</v>
+        <v>3.1107</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3.9325</v>
+        <v>3.6551</v>
       </c>
       <c r="N3" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
       <c r="O3" t="n">
-        <v>102297.64</v>
+        <v>102437.15</v>
       </c>
     </row>
     <row r="4">
@@ -2817,13 +2817,13 @@
         <v>2.5</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N4" t="n">
-        <v>102297.64</v>
+        <v>102437.15</v>
       </c>
       <c r="O4" t="n">
-        <v>106320.5</v>
+        <v>105446.24</v>
       </c>
     </row>
     <row r="5">
@@ -2874,13 +2874,13 @@
         <v>-1</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N5" t="n">
-        <v>106320.5</v>
+        <v>105446.24</v>
       </c>
       <c r="O5" t="n">
-        <v>104648.08</v>
+        <v>104207.25</v>
       </c>
     </row>
     <row r="6">
@@ -2920,7 +2920,7 @@
         <v>78525</v>
       </c>
       <c r="J6" t="n">
-        <v>78525</v>
+        <v>77440</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2928,16 +2928,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>4.7325</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3.9325</v>
+        <v>5.5607</v>
       </c>
       <c r="N6" t="n">
         <v>100000</v>
       </c>
       <c r="O6" t="n">
-        <v>103932.5</v>
+        <v>105560.7</v>
       </c>
     </row>
     <row r="7">
@@ -2988,13 +2988,13 @@
         <v>2.5</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N7" t="n">
-        <v>103932.5</v>
+        <v>105560.7</v>
       </c>
       <c r="O7" t="n">
-        <v>108019.65</v>
+        <v>108661.55</v>
       </c>
     </row>
     <row r="8">
@@ -3045,13 +3045,13 @@
         <v>2.5</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N8" t="n">
         <v>100000</v>
       </c>
       <c r="O8" t="n">
-        <v>103932.5</v>
+        <v>102937.5</v>
       </c>
     </row>
     <row r="9">
@@ -3091,7 +3091,7 @@
         <v>662.7</v>
       </c>
       <c r="J9" t="n">
-        <v>662.7</v>
+        <v>658.2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3099,16 +3099,16 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>3.1233</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3.9325</v>
+        <v>3.6699</v>
       </c>
       <c r="N9" t="n">
-        <v>103932.5</v>
+        <v>102937.5</v>
       </c>
       <c r="O9" t="n">
-        <v>108019.65</v>
+        <v>106715.17</v>
       </c>
     </row>
     <row r="10">
@@ -3159,13 +3159,13 @@
         <v>2.5</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N10" t="n">
-        <v>108019.65</v>
+        <v>106715.17</v>
       </c>
       <c r="O10" t="n">
-        <v>112267.52</v>
+        <v>109849.92</v>
       </c>
     </row>
     <row r="11">
@@ -3216,13 +3216,13 @@
         <v>2.5</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N11" t="n">
-        <v>112267.52</v>
+        <v>109849.92</v>
       </c>
       <c r="O11" t="n">
-        <v>116682.44</v>
+        <v>113076.76</v>
       </c>
     </row>
     <row r="12">
@@ -3273,13 +3273,13 @@
         <v>-1</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N12" t="n">
-        <v>116682.44</v>
+        <v>113076.76</v>
       </c>
       <c r="O12" t="n">
-        <v>114847.02</v>
+        <v>111748.11</v>
       </c>
     </row>
     <row r="13">
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>114847.02</v>
+        <v>111748.11</v>
       </c>
       <c r="O13" t="n">
-        <v>114847.02</v>
+        <v>111748.11</v>
       </c>
     </row>
     <row r="14">
@@ -3358,22 +3358,25 @@
       <c r="I14" t="n">
         <v>5214</v>
       </c>
+      <c r="J14" t="n">
+        <v>5253</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>-1.573</v>
+        <v>3.3191</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
         <v>100000</v>
       </c>
       <c r="O14" t="n">
-        <v>98427</v>
+        <v>103900</v>
       </c>
     </row>
     <row r="15">
@@ -3424,13 +3427,13 @@
         <v>-1</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N15" t="n">
-        <v>98427</v>
+        <v>103900</v>
       </c>
       <c r="O15" t="n">
-        <v>96878.74000000001</v>
+        <v>102679.17</v>
       </c>
     </row>
     <row r="16">
@@ -3470,7 +3473,7 @@
         <v>3088</v>
       </c>
       <c r="J16" t="n">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -3478,16 +3481,16 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5</v>
+        <v>2.5385</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9827</v>
       </c>
       <c r="N16" t="n">
-        <v>96878.74000000001</v>
+        <v>102679.17</v>
       </c>
       <c r="O16" t="n">
-        <v>100688.5</v>
+        <v>105741.78</v>
       </c>
     </row>
     <row r="17">
@@ -3538,13 +3541,13 @@
         <v>-1</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N17" t="n">
         <v>100000</v>
       </c>
       <c r="O17" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
     </row>
     <row r="18">
@@ -3595,13 +3598,13 @@
         <v>2.5</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N18" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
       <c r="O18" t="n">
-        <v>102297.64</v>
+        <v>101727.98</v>
       </c>
     </row>
     <row r="19">
@@ -3649,13 +3652,13 @@
         <v>-1</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N19" t="n">
         <v>100000</v>
       </c>
       <c r="O19" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
     </row>
     <row r="20">
@@ -3695,7 +3698,7 @@
         <v>483.6</v>
       </c>
       <c r="J20" t="n">
-        <v>483.6</v>
+        <v>478.2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -3703,16 +3706,16 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>7.4545</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3.9325</v>
+        <v>8.7591</v>
       </c>
       <c r="N20" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
       <c r="O20" t="n">
-        <v>102297.64</v>
+        <v>107481.17</v>
       </c>
     </row>
     <row r="21">
@@ -3763,13 +3766,13 @@
         <v>-1</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N21" t="n">
-        <v>102297.64</v>
+        <v>107481.17</v>
       </c>
       <c r="O21" t="n">
-        <v>100688.5</v>
+        <v>106218.27</v>
       </c>
     </row>
     <row r="22">
@@ -3806,10 +3809,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>100688.5</v>
+        <v>106218.27</v>
       </c>
       <c r="O22" t="n">
-        <v>100688.5</v>
+        <v>106218.27</v>
       </c>
     </row>
     <row r="23">
@@ -3849,7 +3852,7 @@
         <v>49598</v>
       </c>
       <c r="J23" t="n">
-        <v>49598</v>
+        <v>49495</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3857,16 +3860,16 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.5</v>
+        <v>4.1803</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3.9325</v>
+        <v>4.9119</v>
       </c>
       <c r="N23" t="n">
         <v>100000</v>
       </c>
       <c r="O23" t="n">
-        <v>103932.5</v>
+        <v>104911.89</v>
       </c>
     </row>
     <row r="24">
@@ -3906,7 +3909,7 @@
         <v>51479</v>
       </c>
       <c r="J24" t="n">
-        <v>51479</v>
+        <v>50796</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3914,16 +3917,16 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.5</v>
+        <v>8.9434</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3.9325</v>
+        <v>10.5085</v>
       </c>
       <c r="N24" t="n">
-        <v>103932.5</v>
+        <v>104911.89</v>
       </c>
       <c r="O24" t="n">
-        <v>108019.65</v>
+        <v>115936.54</v>
       </c>
     </row>
     <row r="25">
@@ -3974,13 +3977,13 @@
         <v>-1</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N25" t="n">
-        <v>108019.65</v>
+        <v>115936.54</v>
       </c>
       <c r="O25" t="n">
-        <v>106320.5</v>
+        <v>114574.29</v>
       </c>
     </row>
     <row r="26">
@@ -4019,22 +4022,25 @@
       <c r="I26" t="n">
         <v>1.1744</v>
       </c>
+      <c r="J26" t="n">
+        <v>1.17435</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>-1.573</v>
+        <v>2.5321</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>2.9752</v>
       </c>
       <c r="N26" t="n">
         <v>100000</v>
       </c>
       <c r="O26" t="n">
-        <v>98427</v>
+        <v>102975.16</v>
       </c>
     </row>
     <row r="27">
@@ -4085,13 +4091,13 @@
         <v>2.5</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N27" t="n">
-        <v>98427</v>
+        <v>102975.16</v>
       </c>
       <c r="O27" t="n">
-        <v>102297.64</v>
+        <v>106000.06</v>
       </c>
     </row>
     <row r="28">
@@ -4142,13 +4148,13 @@
         <v>2.5</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N28" t="n">
         <v>100000</v>
       </c>
       <c r="O28" t="n">
-        <v>103932.5</v>
+        <v>102937.5</v>
       </c>
     </row>
     <row r="29">
@@ -4199,13 +4205,13 @@
         <v>2.5</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N29" t="n">
-        <v>103932.5</v>
+        <v>102937.5</v>
       </c>
       <c r="O29" t="n">
-        <v>108019.65</v>
+        <v>105961.29</v>
       </c>
     </row>
     <row r="30">
@@ -4256,13 +4262,13 @@
         <v>2.5</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N30" t="n">
-        <v>108019.65</v>
+        <v>105961.29</v>
       </c>
       <c r="O30" t="n">
-        <v>112267.52</v>
+        <v>109073.9</v>
       </c>
     </row>
     <row r="31">
@@ -4313,13 +4319,13 @@
         <v>-1</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N31" t="n">
         <v>100000</v>
       </c>
       <c r="O31" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
     </row>
     <row r="32">
@@ -4370,13 +4376,13 @@
         <v>2.5</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N32" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
       <c r="O32" t="n">
-        <v>102297.64</v>
+        <v>101727.98</v>
       </c>
     </row>
     <row r="33">
@@ -4427,13 +4433,13 @@
         <v>2.5</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N33" t="n">
-        <v>102297.64</v>
+        <v>101727.98</v>
       </c>
       <c r="O33" t="n">
-        <v>106320.5</v>
+        <v>104716.24</v>
       </c>
     </row>
     <row r="34">
@@ -4484,13 +4490,13 @@
         <v>2.5</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N34" t="n">
         <v>100000</v>
       </c>
       <c r="O34" t="n">
-        <v>103932.5</v>
+        <v>102937.5</v>
       </c>
     </row>
     <row r="35">
@@ -4530,7 +4536,7 @@
         <v>4351.5</v>
       </c>
       <c r="J35" t="n">
-        <v>4351.5</v>
+        <v>4258.5</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4538,16 +4544,16 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.5</v>
+        <v>8.102399999999999</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3.9325</v>
+        <v>9.520300000000001</v>
       </c>
       <c r="N35" t="n">
         <v>100000</v>
       </c>
       <c r="O35" t="n">
-        <v>103932.5</v>
+        <v>109520.33</v>
       </c>
     </row>
     <row r="36">
@@ -4598,13 +4604,13 @@
         <v>2.5</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N36" t="n">
-        <v>103932.5</v>
+        <v>109520.33</v>
       </c>
       <c r="O36" t="n">
-        <v>108019.65</v>
+        <v>112737.49</v>
       </c>
     </row>
     <row r="37">
@@ -4655,13 +4661,13 @@
         <v>2.5</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N37" t="n">
-        <v>108019.65</v>
+        <v>112737.49</v>
       </c>
       <c r="O37" t="n">
-        <v>112267.52</v>
+        <v>116049.15</v>
       </c>
     </row>
     <row r="38">
@@ -4701,7 +4707,7 @@
         <v>4407</v>
       </c>
       <c r="J38" t="n">
-        <v>4407</v>
+        <v>4473.5</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4709,16 +4715,16 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.5</v>
+        <v>4.809</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3.9325</v>
+        <v>5.6506</v>
       </c>
       <c r="N38" t="n">
-        <v>112267.52</v>
+        <v>116049.15</v>
       </c>
       <c r="O38" t="n">
-        <v>116682.44</v>
+        <v>122606.64</v>
       </c>
     </row>
     <row r="39">
@@ -4766,13 +4772,13 @@
         <v>-1</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N39" t="n">
-        <v>116682.44</v>
+        <v>122606.64</v>
       </c>
       <c r="O39" t="n">
-        <v>114847.02</v>
+        <v>121166.01</v>
       </c>
     </row>
     <row r="40">
@@ -4823,13 +4829,13 @@
         <v>-1</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N40" t="n">
-        <v>114847.02</v>
+        <v>121166.01</v>
       </c>
       <c r="O40" t="n">
-        <v>113040.48</v>
+        <v>119742.31</v>
       </c>
     </row>
     <row r="41">
@@ -4880,13 +4886,13 @@
         <v>2.5</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N41" t="n">
-        <v>113040.48</v>
+        <v>119742.31</v>
       </c>
       <c r="O41" t="n">
-        <v>117485.8</v>
+        <v>123259.74</v>
       </c>
     </row>
     <row r="42">
@@ -4937,13 +4943,13 @@
         <v>2.5</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N42" t="n">
-        <v>117485.8</v>
+        <v>123259.74</v>
       </c>
       <c r="O42" t="n">
-        <v>122105.93</v>
+        <v>126880.49</v>
       </c>
     </row>
     <row r="43">
@@ -4994,13 +5000,13 @@
         <v>2.5</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N43" t="n">
-        <v>122105.93</v>
+        <v>126880.49</v>
       </c>
       <c r="O43" t="n">
-        <v>126907.74</v>
+        <v>130607.61</v>
       </c>
     </row>
     <row r="44">
@@ -5051,13 +5057,13 @@
         <v>-1</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N44" t="n">
         <v>100000</v>
       </c>
       <c r="O44" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
     </row>
     <row r="45">
@@ -5105,13 +5111,13 @@
         <v>-1</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N45" t="n">
         <v>100000</v>
       </c>
       <c r="O45" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
     </row>
     <row r="46">
@@ -5162,13 +5168,13 @@
         <v>2.5</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N46" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
       <c r="O46" t="n">
-        <v>102297.64</v>
+        <v>101727.98</v>
       </c>
     </row>
     <row r="47">
@@ -5219,13 +5225,13 @@
         <v>2.5</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N47" t="n">
-        <v>102297.64</v>
+        <v>101727.98</v>
       </c>
       <c r="O47" t="n">
-        <v>106320.5</v>
+        <v>104716.24</v>
       </c>
     </row>
     <row r="48">
@@ -5265,7 +5271,7 @@
         <v>237.3</v>
       </c>
       <c r="J48" t="n">
-        <v>237.3</v>
+        <v>238.1</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -5273,16 +5279,16 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.5</v>
+        <v>3.4524</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3.9325</v>
+        <v>4.0565</v>
       </c>
       <c r="N48" t="n">
-        <v>106320.5</v>
+        <v>104716.24</v>
       </c>
       <c r="O48" t="n">
-        <v>110501.55</v>
+        <v>108964.11</v>
       </c>
     </row>
     <row r="49">
@@ -5333,13 +5339,13 @@
         <v>-1</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N49" t="n">
         <v>100000</v>
       </c>
       <c r="O49" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
     </row>
     <row r="50">
@@ -5390,13 +5396,13 @@
         <v>-1</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N50" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
       <c r="O50" t="n">
-        <v>96878.74000000001</v>
+        <v>97663.81</v>
       </c>
     </row>
     <row r="51">
@@ -5436,7 +5442,7 @@
         <v>5.4818</v>
       </c>
       <c r="J51" t="n">
-        <v>5.4818</v>
+        <v>5.485</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -5444,16 +5450,16 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.5</v>
+        <v>2.5475</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9933</v>
       </c>
       <c r="N51" t="n">
-        <v>96878.74000000001</v>
+        <v>97663.81</v>
       </c>
       <c r="O51" t="n">
-        <v>100688.5</v>
+        <v>100587.16</v>
       </c>
     </row>
     <row r="52">
@@ -5504,13 +5510,13 @@
         <v>-1</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N52" t="n">
-        <v>100688.5</v>
+        <v>100587.16</v>
       </c>
       <c r="O52" t="n">
-        <v>99104.67</v>
+        <v>99405.25999999999</v>
       </c>
     </row>
     <row r="53">
@@ -5561,13 +5567,13 @@
         <v>-1</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N53" t="n">
         <v>100000</v>
       </c>
       <c r="O53" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
     </row>
     <row r="54">
@@ -5618,13 +5624,13 @@
         <v>2.5</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N54" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
       <c r="O54" t="n">
-        <v>102297.64</v>
+        <v>101727.98</v>
       </c>
     </row>
     <row r="55">
@@ -5664,7 +5670,7 @@
         <v>1402.9</v>
       </c>
       <c r="J55" t="n">
-        <v>1402.9</v>
+        <v>1403</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -5672,16 +5678,16 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.5</v>
+        <v>2.5059</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9444</v>
       </c>
       <c r="N55" t="n">
         <v>100000</v>
       </c>
       <c r="O55" t="n">
-        <v>103932.5</v>
+        <v>102944.41</v>
       </c>
     </row>
     <row r="56">
@@ -5732,13 +5738,13 @@
         <v>2.5</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N56" t="n">
-        <v>103932.5</v>
+        <v>102944.41</v>
       </c>
       <c r="O56" t="n">
-        <v>108019.65</v>
+        <v>105968.4</v>
       </c>
     </row>
     <row r="57">
@@ -5789,13 +5795,13 @@
         <v>-1</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N57" t="n">
         <v>100000</v>
       </c>
       <c r="O57" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
     </row>
     <row r="58">
@@ -5846,13 +5852,13 @@
         <v>-1</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N58" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
       <c r="O58" t="n">
-        <v>96878.74000000001</v>
+        <v>97663.81</v>
       </c>
     </row>
     <row r="59">
@@ -5903,13 +5909,13 @@
         <v>-1</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N59" t="n">
-        <v>96878.74000000001</v>
+        <v>97663.81</v>
       </c>
       <c r="O59" t="n">
-        <v>95354.84</v>
+        <v>96516.25999999999</v>
       </c>
     </row>
     <row r="60">
@@ -5948,22 +5954,25 @@
       <c r="I60" t="n">
         <v>27760.1</v>
       </c>
+      <c r="J60" t="n">
+        <v>27760</v>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>-1.573</v>
+        <v>2.5017</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>2.9395</v>
       </c>
       <c r="N60" t="n">
         <v>100000</v>
       </c>
       <c r="O60" t="n">
-        <v>98427</v>
+        <v>102939.5</v>
       </c>
     </row>
     <row r="61">
@@ -6014,13 +6023,13 @@
         <v>2.5</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N61" t="n">
         <v>100000</v>
       </c>
       <c r="O61" t="n">
-        <v>103932.5</v>
+        <v>102937.5</v>
       </c>
     </row>
     <row r="62">
@@ -6060,7 +6069,7 @@
         <v>6936.76</v>
       </c>
       <c r="J62" t="n">
-        <v>6936.76</v>
+        <v>6914.11</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -6068,16 +6077,16 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.5</v>
+        <v>5.2382</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3.9325</v>
+        <v>6.1549</v>
       </c>
       <c r="N62" t="n">
         <v>100000</v>
       </c>
       <c r="O62" t="n">
-        <v>103932.5</v>
+        <v>106154.9</v>
       </c>
     </row>
     <row r="63">
@@ -6116,22 +6125,25 @@
       <c r="I63" t="n">
         <v>6966.32</v>
       </c>
+      <c r="J63" t="n">
+        <v>7002</v>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>-1.573</v>
+        <v>-3.5816</v>
       </c>
       <c r="N63" t="n">
-        <v>103932.5</v>
+        <v>106154.9</v>
       </c>
       <c r="O63" t="n">
-        <v>102297.64</v>
+        <v>102352.8</v>
       </c>
     </row>
     <row r="64">
@@ -6171,7 +6183,7 @@
         <v>6956.27</v>
       </c>
       <c r="J64" t="n">
-        <v>6956.27</v>
+        <v>6947.27</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6179,16 +6191,16 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.5</v>
+        <v>3.3617</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3.9325</v>
+        <v>3.95</v>
       </c>
       <c r="N64" t="n">
-        <v>102297.64</v>
+        <v>102352.8</v>
       </c>
       <c r="O64" t="n">
-        <v>106320.5</v>
+        <v>106395.76</v>
       </c>
     </row>
     <row r="65">
@@ -6236,13 +6248,13 @@
         <v>-1</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N65" t="n">
-        <v>106320.5</v>
+        <v>106395.76</v>
       </c>
       <c r="O65" t="n">
-        <v>104648.08</v>
+        <v>105145.61</v>
       </c>
     </row>
     <row r="66">
@@ -6290,13 +6302,13 @@
         <v>-1</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N66" t="n">
-        <v>104648.08</v>
+        <v>105145.61</v>
       </c>
       <c r="O66" t="n">
-        <v>103001.96</v>
+        <v>103910.15</v>
       </c>
     </row>
     <row r="67">
@@ -6336,7 +6348,7 @@
         <v>6853.48</v>
       </c>
       <c r="J67" t="n">
-        <v>6770.77</v>
+        <v>6769.03</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -6344,16 +6356,16 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-1</v>
+        <v>-1.0736</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.2615</v>
       </c>
       <c r="N67" t="n">
-        <v>103001.96</v>
+        <v>103910.15</v>
       </c>
       <c r="O67" t="n">
-        <v>101381.74</v>
+        <v>102599.3</v>
       </c>
     </row>
     <row r="68">
@@ -6404,13 +6416,13 @@
         <v>-1</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N68" t="n">
         <v>100000</v>
       </c>
       <c r="O68" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
     </row>
     <row r="69">
@@ -6461,13 +6473,13 @@
         <v>-1</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N69" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
       <c r="O69" t="n">
-        <v>96878.74000000001</v>
+        <v>97663.81</v>
       </c>
     </row>
     <row r="70">
@@ -6518,13 +6530,13 @@
         <v>-1</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N70" t="n">
         <v>100000</v>
       </c>
       <c r="O70" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
     </row>
     <row r="71">
@@ -6564,7 +6576,7 @@
         <v>20.44</v>
       </c>
       <c r="J71" t="n">
-        <v>21.07</v>
+        <v>21.08</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6572,16 +6584,16 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.2403</v>
       </c>
       <c r="N71" t="n">
         <v>100000</v>
       </c>
       <c r="O71" t="n">
-        <v>98427</v>
+        <v>98759.72</v>
       </c>
     </row>
     <row r="72">
@@ -6632,13 +6644,13 @@
         <v>-1</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N72" t="n">
         <v>100000</v>
       </c>
       <c r="O72" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
     </row>
     <row r="73">
@@ -6689,13 +6701,13 @@
         <v>-1</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N73" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
       <c r="O73" t="n">
-        <v>96878.74000000001</v>
+        <v>97663.81</v>
       </c>
     </row>
     <row r="74">
@@ -6746,13 +6758,13 @@
         <v>1</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1.573</v>
+        <v>1.175</v>
       </c>
       <c r="N74" t="n">
-        <v>96878.74000000001</v>
+        <v>97663.81</v>
       </c>
       <c r="O74" t="n">
-        <v>98402.64999999999</v>
+        <v>98811.36</v>
       </c>
     </row>
     <row r="75">
@@ -6803,13 +6815,13 @@
         <v>-1</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N75" t="n">
         <v>100000</v>
       </c>
       <c r="O75" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
     </row>
     <row r="76">
@@ -6860,13 +6872,13 @@
         <v>2.5</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N76" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
       <c r="O76" t="n">
-        <v>102297.64</v>
+        <v>101727.98</v>
       </c>
     </row>
     <row r="77">
@@ -6917,13 +6929,13 @@
         <v>2.5</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N77" t="n">
         <v>100000</v>
       </c>
       <c r="O77" t="n">
-        <v>103932.5</v>
+        <v>102937.5</v>
       </c>
     </row>
     <row r="78">
@@ -6974,13 +6986,13 @@
         <v>2.5</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N78" t="n">
-        <v>103932.5</v>
+        <v>102937.5</v>
       </c>
       <c r="O78" t="n">
-        <v>108019.65</v>
+        <v>105961.29</v>
       </c>
     </row>
     <row r="79">
@@ -7031,13 +7043,13 @@
         <v>2.5</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N79" t="n">
-        <v>108019.65</v>
+        <v>105961.29</v>
       </c>
       <c r="O79" t="n">
-        <v>112267.52</v>
+        <v>109073.9</v>
       </c>
     </row>
     <row r="80">
@@ -7088,13 +7100,13 @@
         <v>-1</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N80" t="n">
-        <v>112267.52</v>
+        <v>109073.9</v>
       </c>
       <c r="O80" t="n">
-        <v>110501.55</v>
+        <v>107792.28</v>
       </c>
     </row>
     <row r="81">
@@ -7145,13 +7157,13 @@
         <v>2.5</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N81" t="n">
-        <v>110501.55</v>
+        <v>107792.28</v>
       </c>
       <c r="O81" t="n">
-        <v>114847.02</v>
+        <v>110958.68</v>
       </c>
     </row>
     <row r="82">
@@ -7202,13 +7214,13 @@
         <v>2.5</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N82" t="n">
-        <v>114847.02</v>
+        <v>110958.68</v>
       </c>
       <c r="O82" t="n">
-        <v>119363.38</v>
+        <v>114218.09</v>
       </c>
     </row>
     <row r="83">
@@ -7259,13 +7271,13 @@
         <v>-1</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N83" t="n">
-        <v>119363.38</v>
+        <v>114218.09</v>
       </c>
       <c r="O83" t="n">
-        <v>117485.8</v>
+        <v>112876.03</v>
       </c>
     </row>
     <row r="84">
@@ -7316,13 +7328,13 @@
         <v>-1</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>-1.573</v>
+        <v>-1.175</v>
       </c>
       <c r="N84" t="n">
-        <v>117485.8</v>
+        <v>112876.03</v>
       </c>
       <c r="O84" t="n">
-        <v>115637.75</v>
+        <v>111549.74</v>
       </c>
     </row>
     <row r="85">
@@ -7373,13 +7385,13 @@
         <v>2.5</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3.9325</v>
+        <v>2.9375</v>
       </c>
       <c r="N85" t="n">
-        <v>115637.75</v>
+        <v>111549.74</v>
       </c>
       <c r="O85" t="n">
-        <v>120185.2</v>
+        <v>114826.51</v>
       </c>
     </row>
     <row r="86">
@@ -7419,7 +7431,7 @@
         <v>118.44</v>
       </c>
       <c r="J86" t="n">
-        <v>118.44</v>
+        <v>113.29</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7427,16 +7439,16 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.5</v>
+        <v>6.4351</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3.9325</v>
+        <v>7.5613</v>
       </c>
       <c r="N86" t="n">
         <v>100000</v>
       </c>
       <c r="O86" t="n">
-        <v>103932.5</v>
+        <v>107561.26</v>
       </c>
     </row>
     <row r="87">
@@ -7476,7 +7488,7 @@
         <v>128.21</v>
       </c>
       <c r="J87" t="n">
-        <v>128.21</v>
+        <v>124.86</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7484,16 +7496,16 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.5</v>
+        <v>6.7949</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>3.9325</v>
+        <v>7.984</v>
       </c>
       <c r="N87" t="n">
-        <v>103932.5</v>
+        <v>107561.26</v>
       </c>
       <c r="O87" t="n">
-        <v>108019.65</v>
+        <v>116148.92</v>
       </c>
     </row>
   </sheetData>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 2.5R, or an opposite reversal nearer than 2.5R), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 09:49 UTC.</t>
+          <t>quickfix daily (target = 2.5R, or an opposite reversal nearer than 2.5R), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 19:13 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -639,7 +639,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -657,10 +657,10 @@
         <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -672,28 +672,28 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>14.57</v>
+        <v>10.96</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>114574.29</v>
+        <v>110958.68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -702,46 +702,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>11.75</v>
+        <v>7.79</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>111748.11</v>
+        <v>107792.28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -750,19 +750,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -771,25 +771,25 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8.960000000000001</v>
+        <v>6.72</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>108964.11</v>
+        <v>106724.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -822,16 +822,16 @@
         <v>100</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8.66</v>
+        <v>6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>108661.55</v>
+        <v>106000.06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -849,43 +849,43 @@
         <v>64</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6.22</v>
+        <v>5.97</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>106218.27</v>
+        <v>105968.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>Bitcoin_Per_USD_CME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -918,16 +918,16 @@
         <v>100</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6</v>
+        <v>5.96</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>106000.06</v>
+        <v>105961.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>German_Long_Bund</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -966,16 +966,16 @@
         <v>100</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5.97</v>
+        <v>2.94</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>105968.4</v>
+        <v>102937.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>German_Long_Bund</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -1017,19 +1017,19 @@
         <v>2.94</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>102937.5</v>
+        <v>102939.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1065,19 +1065,19 @@
         <v>2.94</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>102939.5</v>
+        <v>102937.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1089,13 +1089,13 @@
         <v>64</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1107,25 +1107,25 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2.94</v>
+        <v>1.73</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>102937.5</v>
+        <v>101727.98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
@@ -1167,13 +1167,13 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1194,22 +1194,22 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1.73</v>
+        <v>0.53</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>101727.98</v>
+        <v>100532.68</v>
       </c>
     </row>
     <row r="16">
@@ -1768,10 +1768,10 @@
         <v>100</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>16.15</v>
+        <v>10.72</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>116148.92</v>
+        <v>110720.87</v>
       </c>
     </row>
     <row r="28">
@@ -1829,7 +1829,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures</t>
+          <t>Ethereum_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1839,16 +1839,16 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>3</v>
@@ -1872,16 +1872,16 @@
         <v>66.7</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>5.74</v>
+        <v>4.72</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>105741.78</v>
+        <v>104716.24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance</t>
+          <t>Bitcoin_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1900,16 +1900,16 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
@@ -1921,19 +1921,19 @@
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>4.72</v>
+        <v>3.49</v>
       </c>
       <c r="N30" s="8" t="n">
-        <v>104716.24</v>
+        <v>103485.83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance</t>
+          <t>Coffee_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1943,25 +1943,25 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
@@ -1976,16 +1976,16 @@
         <v>50</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>4.21</v>
+        <v>1.73</v>
       </c>
       <c r="N31" s="8" t="n">
-        <v>104207.25</v>
+        <v>101727.98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -2007,16 +2007,16 @@
         <v>73</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>0</v>
@@ -2028,16 +2028,16 @@
         <v>33.3</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>2.6</v>
+        <v>0.58</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>102599.3</v>
+        <v>100576.82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures</t>
+          <t>iShares_Silver_Trust</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -2059,13 +2059,13 @@
         <v>73</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
@@ -2076,20 +2076,18 @@
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M33" s="7" t="n">
-        <v>1.73</v>
+      <c r="L33" s="6" t="n"/>
+      <c r="M33" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>101727.98</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>iShares_Silver_Trust</t>
+          <t>JPY_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -2099,7 +2097,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -2108,7 +2106,7 @@
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>0</v>
@@ -2139,7 +2137,7 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>JPY_EUR_Cross_Rate</t>
+          <t>NASDAQ_100_Index</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -2149,7 +2147,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -2158,7 +2156,7 @@
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>0</v>
@@ -2189,7 +2187,7 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>NASDAQ_100_Index</t>
+          <t>NIKKEI_225_Index</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2199,7 +2197,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -2239,7 +2237,7 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>NIKKEI_225_Index</t>
+          <t>ProShares_UltraPro_Dow</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -2249,7 +2247,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -2258,7 +2256,7 @@
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>0</v>
@@ -2289,7 +2287,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>ProShares_UltraPro_Dow</t>
+          <t>SPDR_Gold_Shares</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2308,7 +2306,7 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>0</v>
@@ -2339,7 +2337,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>SPDR_Gold_Shares</t>
+          <t>United_States_Natural_Gas_Fund_LP</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -2349,7 +2347,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -2389,7 +2387,7 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>United_States_Natural_Gas_Fund_LP</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -2399,7 +2397,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -2411,16 +2409,16 @@
         <v>73</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J40" s="6" t="n">
         <v>0</v>
@@ -2428,12 +2426,14 @@
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="6" t="n"/>
-      <c r="M40" s="9" t="n">
-        <v>0</v>
+      <c r="L40" s="6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="M40" s="10" t="n">
+        <v>-0.51</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>100000</v>
+        <v>99489.67</v>
       </c>
     </row>
     <row r="41">
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 2.5R, or an opposite reversal nearer than 2.5R), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 19:13 UTC.</t>
+          <t>quickfix daily (target = 2.5R, or an opposite reversal nearer than 2.5R), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 20:58 UTC.</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
         <v>69020</v>
       </c>
       <c r="J3" t="n">
-        <v>70581</v>
+        <v>69020</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -2757,16 +2757,16 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.1107</v>
+        <v>2.5</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3.6551</v>
+        <v>2.9375</v>
       </c>
       <c r="N3" t="n">
         <v>98825</v>
       </c>
       <c r="O3" t="n">
-        <v>102437.15</v>
+        <v>101727.98</v>
       </c>
     </row>
     <row r="4">
@@ -2820,10 +2820,10 @@
         <v>2.9375</v>
       </c>
       <c r="N4" t="n">
-        <v>102437.15</v>
+        <v>101727.98</v>
       </c>
       <c r="O4" t="n">
-        <v>105446.24</v>
+        <v>104716.24</v>
       </c>
     </row>
     <row r="5">
@@ -2877,10 +2877,10 @@
         <v>-1.175</v>
       </c>
       <c r="N5" t="n">
-        <v>105446.24</v>
+        <v>104716.24</v>
       </c>
       <c r="O5" t="n">
-        <v>104207.25</v>
+        <v>103485.83</v>
       </c>
     </row>
     <row r="6">
@@ -2920,7 +2920,7 @@
         <v>78525</v>
       </c>
       <c r="J6" t="n">
-        <v>77440</v>
+        <v>78525</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2928,16 +2928,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.7325</v>
+        <v>2.5</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5.5607</v>
+        <v>2.9375</v>
       </c>
       <c r="N6" t="n">
         <v>100000</v>
       </c>
       <c r="O6" t="n">
-        <v>105560.7</v>
+        <v>102937.5</v>
       </c>
     </row>
     <row r="7">
@@ -2991,10 +2991,10 @@
         <v>2.9375</v>
       </c>
       <c r="N7" t="n">
-        <v>105560.7</v>
+        <v>102937.5</v>
       </c>
       <c r="O7" t="n">
-        <v>108661.55</v>
+        <v>105961.29</v>
       </c>
     </row>
     <row r="8">
@@ -3091,7 +3091,7 @@
         <v>662.7</v>
       </c>
       <c r="J9" t="n">
-        <v>658.2</v>
+        <v>662.7</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3099,16 +3099,16 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.1233</v>
+        <v>2.5</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3.6699</v>
+        <v>2.9375</v>
       </c>
       <c r="N9" t="n">
         <v>102937.5</v>
       </c>
       <c r="O9" t="n">
-        <v>106715.17</v>
+        <v>105961.29</v>
       </c>
     </row>
     <row r="10">
@@ -3162,10 +3162,10 @@
         <v>2.9375</v>
       </c>
       <c r="N10" t="n">
-        <v>106715.17</v>
+        <v>105961.29</v>
       </c>
       <c r="O10" t="n">
-        <v>109849.92</v>
+        <v>109073.9</v>
       </c>
     </row>
     <row r="11">
@@ -3219,10 +3219,10 @@
         <v>2.9375</v>
       </c>
       <c r="N11" t="n">
-        <v>109849.92</v>
+        <v>109073.9</v>
       </c>
       <c r="O11" t="n">
-        <v>113076.76</v>
+        <v>112277.95</v>
       </c>
     </row>
     <row r="12">
@@ -3276,10 +3276,10 @@
         <v>-1.175</v>
       </c>
       <c r="N12" t="n">
-        <v>113076.76</v>
+        <v>112277.95</v>
       </c>
       <c r="O12" t="n">
-        <v>111748.11</v>
+        <v>110958.68</v>
       </c>
     </row>
     <row r="13">
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>111748.11</v>
+        <v>110958.68</v>
       </c>
       <c r="O13" t="n">
-        <v>111748.11</v>
+        <v>110958.68</v>
       </c>
     </row>
     <row r="14">
@@ -3358,25 +3358,22 @@
       <c r="I14" t="n">
         <v>5214</v>
       </c>
-      <c r="J14" t="n">
-        <v>5253</v>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.3191</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>3.9</v>
+        <v>-1</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>-1.175</v>
       </c>
       <c r="N14" t="n">
         <v>100000</v>
       </c>
       <c r="O14" t="n">
-        <v>103900</v>
+        <v>98825</v>
       </c>
     </row>
     <row r="15">
@@ -3430,10 +3427,10 @@
         <v>-1.175</v>
       </c>
       <c r="N15" t="n">
-        <v>103900</v>
+        <v>98825</v>
       </c>
       <c r="O15" t="n">
-        <v>102679.17</v>
+        <v>97663.81</v>
       </c>
     </row>
     <row r="16">
@@ -3487,10 +3484,10 @@
         <v>2.9827</v>
       </c>
       <c r="N16" t="n">
-        <v>102679.17</v>
+        <v>97663.81</v>
       </c>
       <c r="O16" t="n">
-        <v>105741.78</v>
+        <v>100576.82</v>
       </c>
     </row>
     <row r="17">
@@ -3698,7 +3695,7 @@
         <v>483.6</v>
       </c>
       <c r="J20" t="n">
-        <v>478.2</v>
+        <v>483.6</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -3706,16 +3703,16 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.4545</v>
+        <v>2.5</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8.7591</v>
+        <v>2.9375</v>
       </c>
       <c r="N20" t="n">
         <v>98825</v>
       </c>
       <c r="O20" t="n">
-        <v>107481.17</v>
+        <v>101727.98</v>
       </c>
     </row>
     <row r="21">
@@ -3769,10 +3766,10 @@
         <v>-1.175</v>
       </c>
       <c r="N21" t="n">
-        <v>107481.17</v>
+        <v>101727.98</v>
       </c>
       <c r="O21" t="n">
-        <v>106218.27</v>
+        <v>100532.68</v>
       </c>
     </row>
     <row r="22">
@@ -3809,10 +3806,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>106218.27</v>
+        <v>100532.68</v>
       </c>
       <c r="O22" t="n">
-        <v>106218.27</v>
+        <v>100532.68</v>
       </c>
     </row>
     <row r="23">
@@ -3909,7 +3906,7 @@
         <v>51479</v>
       </c>
       <c r="J24" t="n">
-        <v>50796</v>
+        <v>51479</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3917,16 +3914,16 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>8.9434</v>
+        <v>2.5</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>10.5085</v>
+        <v>2.9375</v>
       </c>
       <c r="N24" t="n">
         <v>104911.89</v>
       </c>
       <c r="O24" t="n">
-        <v>115936.54</v>
+        <v>107993.67</v>
       </c>
     </row>
     <row r="25">
@@ -3980,10 +3977,10 @@
         <v>-1.175</v>
       </c>
       <c r="N25" t="n">
-        <v>115936.54</v>
+        <v>107993.67</v>
       </c>
       <c r="O25" t="n">
-        <v>114574.29</v>
+        <v>106724.75</v>
       </c>
     </row>
     <row r="26">
@@ -5271,7 +5268,7 @@
         <v>237.3</v>
       </c>
       <c r="J48" t="n">
-        <v>238.1</v>
+        <v>237.3</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -5279,16 +5276,16 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.4524</v>
+        <v>2.5</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4.0565</v>
+        <v>2.9375</v>
       </c>
       <c r="N48" t="n">
         <v>104716.24</v>
       </c>
       <c r="O48" t="n">
-        <v>108964.11</v>
+        <v>107792.28</v>
       </c>
     </row>
     <row r="49">
@@ -6069,7 +6066,7 @@
         <v>6936.76</v>
       </c>
       <c r="J62" t="n">
-        <v>6914.11</v>
+        <v>6936.76</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -6077,16 +6074,16 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>5.2382</v>
+        <v>2.5</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>6.1549</v>
+        <v>2.9375</v>
       </c>
       <c r="N62" t="n">
         <v>100000</v>
       </c>
       <c r="O62" t="n">
-        <v>106154.9</v>
+        <v>102937.5</v>
       </c>
     </row>
     <row r="63">
@@ -6140,10 +6137,10 @@
         <v>-3.5816</v>
       </c>
       <c r="N63" t="n">
-        <v>106154.9</v>
+        <v>102937.5</v>
       </c>
       <c r="O63" t="n">
-        <v>102352.8</v>
+        <v>99250.64</v>
       </c>
     </row>
     <row r="64">
@@ -6197,10 +6194,10 @@
         <v>3.95</v>
       </c>
       <c r="N64" t="n">
-        <v>102352.8</v>
+        <v>99250.64</v>
       </c>
       <c r="O64" t="n">
-        <v>106395.76</v>
+        <v>103171.06</v>
       </c>
     </row>
     <row r="65">
@@ -6251,10 +6248,10 @@
         <v>-1.175</v>
       </c>
       <c r="N65" t="n">
-        <v>106395.76</v>
+        <v>103171.06</v>
       </c>
       <c r="O65" t="n">
-        <v>105145.61</v>
+        <v>101958.8</v>
       </c>
     </row>
     <row r="66">
@@ -6305,10 +6302,10 @@
         <v>-1.175</v>
       </c>
       <c r="N66" t="n">
-        <v>105145.61</v>
+        <v>101958.8</v>
       </c>
       <c r="O66" t="n">
-        <v>103910.15</v>
+        <v>100760.79</v>
       </c>
     </row>
     <row r="67">
@@ -6362,10 +6359,10 @@
         <v>-1.2615</v>
       </c>
       <c r="N67" t="n">
-        <v>103910.15</v>
+        <v>100760.79</v>
       </c>
       <c r="O67" t="n">
-        <v>102599.3</v>
+        <v>99489.67</v>
       </c>
     </row>
     <row r="68">
@@ -7488,7 +7485,7 @@
         <v>128.21</v>
       </c>
       <c r="J87" t="n">
-        <v>124.86</v>
+        <v>128.21</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7496,16 +7493,16 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>6.7949</v>
+        <v>2.5</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>7.984</v>
+        <v>2.9375</v>
       </c>
       <c r="N87" t="n">
         <v>107561.26</v>
       </c>
       <c r="O87" t="n">
-        <v>116148.92</v>
+        <v>110720.87</v>
       </c>
     </row>
   </sheetData>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 2.5R, or an opposite reversal nearer than 2.5R), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 20:58 UTC.</t>
+          <t>quickfix daily (target = 2.5R, or an opposite reversal nearer than 2.5R), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 23:07 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -582,16 +582,16 @@
         <v>77.8</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>30.61</v>
+        <v>27.26</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>130607.61</v>
+        <v>127258.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -624,22 +624,22 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>14.83</v>
+        <v>13.92</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>114826.51</v>
+        <v>113921.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -672,28 +672,28 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10.96</v>
+        <v>12.92</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>110958.68</v>
+        <v>112916.93</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -702,19 +702,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -723,25 +723,25 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7.79</v>
+        <v>7.1</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>107792.28</v>
+        <v>107095.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -750,19 +750,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -771,19 +771,19 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6.72</v>
+        <v>6.63</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>106724.75</v>
+        <v>106631.02</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -801,13 +801,13 @@
         <v>64</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -819,19 +819,19 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6</v>
+        <v>6.63</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>106000.06</v>
+        <v>106631.02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -870,22 +870,22 @@
         <v>100</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5.97</v>
+        <v>6.25</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>105968.4</v>
+        <v>106253.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -918,22 +918,22 @@
         <v>100</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5.96</v>
+        <v>6.22</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>105961.29</v>
+        <v>106216.17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>German_Long_Bund</t>
+          <t>Bitcoin_Per_USD_CME</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -966,16 +966,16 @@
         <v>100</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2.94</v>
+        <v>5.38</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>102937.5</v>
+        <v>105381.31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -993,43 +993,43 @@
         <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2.94</v>
+        <v>4.62</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>102939.5</v>
+        <v>104620.42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>German_Long_Bund</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1062,22 +1062,22 @@
         <v>100</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2.94</v>
+        <v>2.64</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>102937.5</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1089,13 +1089,13 @@
         <v>64</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1107,25 +1107,25 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1.73</v>
+        <v>2.64</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>101727.98</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
@@ -1158,22 +1158,22 @@
         <v>50</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1.73</v>
+        <v>1.21</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>101727.98</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1194,22 +1194,22 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.53</v>
+        <v>1.21</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>100532.68</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="16">
@@ -1485,7 +1485,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1500,19 +1500,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1521,13 +1521,13 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-0.59</v>
+        <v>-0.19</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>99405.25999999999</v>
+        <v>99807.41</v>
       </c>
     </row>
     <row r="23">
@@ -1572,16 +1572,16 @@
         <v>0</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-1.18</v>
+        <v>-1.39</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>98825</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1620,22 +1620,22 @@
         <v>0</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>-1.18</v>
+        <v>-1.39</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>98825</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1668,22 +1668,22 @@
         <v>0</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-2.34</v>
+        <v>-1.39</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>97663.81</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1692,13 +1692,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>3</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>-3.48</v>
+        <v>-1.58</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>96516.25999999999</v>
+        <v>98420.09</v>
       </c>
     </row>
     <row r="27">
@@ -1768,10 +1768,10 @@
         <v>100</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>10.72</v>
+        <v>11.82</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>110720.87</v>
+        <v>111822.04</v>
       </c>
     </row>
     <row r="28">
@@ -1820,16 +1820,16 @@
         <v>100</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>9.07</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>109073.9</v>
+        <v>108134.09</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance</t>
+          <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1839,29 +1839,29 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="F29" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="J29" s="6" t="n">
         <v>0</v>
       </c>
@@ -1869,19 +1869,19 @@
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>4.72</v>
+        <v>5.15</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>104716.24</v>
+        <v>105148.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance</t>
+          <t>Ethereum_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1900,16 +1900,16 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
@@ -1921,19 +1921,19 @@
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>3.49</v>
+        <v>3.89</v>
       </c>
       <c r="N30" s="8" t="n">
-        <v>103485.83</v>
+        <v>103887.36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures</t>
+          <t>Bitcoin_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1943,25 +1943,25 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="F31" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G31" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="H31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
@@ -1976,16 +1976,16 @@
         <v>50</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>1.73</v>
+        <v>2.44</v>
       </c>
       <c r="N31" s="8" t="n">
-        <v>101727.98</v>
+        <v>102443.33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures</t>
+          <t>Coffee_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -2007,7 +2007,7 @@
         <v>73</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>1</v>
@@ -2016,7 +2016,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>0</v>
@@ -2025,13 +2025,13 @@
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.58</v>
+        <v>1.21</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>100576.82</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="33">
@@ -2387,7 +2387,7 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
@@ -2430,16 +2430,16 @@
         <v>33.3</v>
       </c>
       <c r="M40" s="10" t="n">
-        <v>-0.51</v>
+        <v>-1.41</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>99489.67</v>
+        <v>98590.95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -2458,22 +2458,22 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="6" t="n">
         <v>2</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0</v>
@@ -2482,10 +2482,10 @@
         <v>33.3</v>
       </c>
       <c r="M41" s="10" t="n">
-        <v>-1.19</v>
+        <v>-1.45</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>98811.36</v>
+        <v>98551.73</v>
       </c>
     </row>
     <row r="42">
@@ -2534,16 +2534,16 @@
         <v>0</v>
       </c>
       <c r="M42" s="10" t="n">
-        <v>-1.24</v>
+        <v>-1.47</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>98759.72</v>
+        <v>98532.78</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 2.5R, or an opposite reversal nearer than 2.5R), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 23:07 UTC.</t>
+          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-28 00:45 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O87"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2689,7 +2689,7 @@
         <v>74618</v>
       </c>
       <c r="I2" t="n">
-        <v>81233</v>
+        <v>80099</v>
       </c>
       <c r="J2" t="n">
         <v>74618</v>
@@ -2703,13 +2703,13 @@
         <v>-1</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>-1.175</v>
+        <v>-1.39</v>
       </c>
       <c r="N2" t="n">
         <v>100000</v>
       </c>
       <c r="O2" t="n">
-        <v>98825</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="3">
@@ -2746,10 +2746,10 @@
         <v>60074</v>
       </c>
       <c r="I3" t="n">
-        <v>69020</v>
+        <v>67486</v>
       </c>
       <c r="J3" t="n">
-        <v>69020</v>
+        <v>67486</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -2757,16 +2757,16 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N3" t="n">
-        <v>98825</v>
+        <v>98610</v>
       </c>
       <c r="O3" t="n">
-        <v>101727.98</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="4">
@@ -2803,10 +2803,10 @@
         <v>76101</v>
       </c>
       <c r="I4" t="n">
-        <v>73780</v>
+        <v>74178</v>
       </c>
       <c r="J4" t="n">
-        <v>73780</v>
+        <v>74178</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -2814,16 +2814,16 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N4" t="n">
-        <v>101727.98</v>
+        <v>101214.29</v>
       </c>
       <c r="O4" t="n">
-        <v>104716.24</v>
+        <v>103887.36</v>
       </c>
     </row>
     <row r="5">
@@ -2860,7 +2860,7 @@
         <v>76040</v>
       </c>
       <c r="I5" t="n">
-        <v>72050</v>
+        <v>72734</v>
       </c>
       <c r="J5" t="n">
         <v>76040</v>
@@ -2874,13 +2874,13 @@
         <v>-1</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>-1.175</v>
+        <v>-1.39</v>
       </c>
       <c r="N5" t="n">
-        <v>104716.24</v>
+        <v>103887.36</v>
       </c>
       <c r="O5" t="n">
-        <v>103485.83</v>
+        <v>102443.33</v>
       </c>
     </row>
     <row r="6">
@@ -2917,10 +2917,10 @@
         <v>80226</v>
       </c>
       <c r="I6" t="n">
-        <v>78525</v>
+        <v>78817</v>
       </c>
       <c r="J6" t="n">
-        <v>78525</v>
+        <v>78817</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2928,16 +2928,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N6" t="n">
         <v>100000</v>
       </c>
       <c r="O6" t="n">
-        <v>102937.5</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="7">
@@ -2974,10 +2974,10 @@
         <v>83601</v>
       </c>
       <c r="I7" t="n">
-        <v>81658</v>
+        <v>81992</v>
       </c>
       <c r="J7" t="n">
-        <v>81658</v>
+        <v>81980</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2985,16 +2985,16 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>1.9207</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.6698</v>
       </c>
       <c r="N7" t="n">
-        <v>102937.5</v>
+        <v>102641</v>
       </c>
       <c r="O7" t="n">
-        <v>105961.29</v>
+        <v>105381.31</v>
       </c>
     </row>
     <row r="8">
@@ -3031,10 +3031,10 @@
         <v>671.5</v>
       </c>
       <c r="I8" t="n">
-        <v>640.4</v>
+        <v>645.7</v>
       </c>
       <c r="J8" t="n">
-        <v>640.4</v>
+        <v>645.7</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3042,16 +3042,16 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N8" t="n">
         <v>100000</v>
       </c>
       <c r="O8" t="n">
-        <v>102937.5</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="9">
@@ -3088,10 +3088,10 @@
         <v>688.3</v>
       </c>
       <c r="I9" t="n">
-        <v>662.7</v>
+        <v>667.1</v>
       </c>
       <c r="J9" t="n">
-        <v>662.7</v>
+        <v>667.1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3099,16 +3099,16 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N9" t="n">
-        <v>102937.5</v>
+        <v>102641</v>
       </c>
       <c r="O9" t="n">
-        <v>105961.29</v>
+        <v>105351.75</v>
       </c>
     </row>
     <row r="10">
@@ -3145,10 +3145,10 @@
         <v>570.9</v>
       </c>
       <c r="I10" t="n">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="J10" t="n">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3156,16 +3156,16 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N10" t="n">
-        <v>105961.29</v>
+        <v>105351.75</v>
       </c>
       <c r="O10" t="n">
-        <v>109073.9</v>
+        <v>108134.09</v>
       </c>
     </row>
     <row r="11">
@@ -3202,10 +3202,10 @@
         <v>573.9</v>
       </c>
       <c r="I11" t="n">
-        <v>588.2</v>
+        <v>585.8</v>
       </c>
       <c r="J11" t="n">
-        <v>588.2</v>
+        <v>585.8</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -3213,16 +3213,16 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N11" t="n">
-        <v>109073.9</v>
+        <v>108134.09</v>
       </c>
       <c r="O11" t="n">
-        <v>112277.95</v>
+        <v>110989.91</v>
       </c>
     </row>
     <row r="12">
@@ -3246,11 +3246,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>645</v>
@@ -3259,27 +3259,27 @@
         <v>653.1</v>
       </c>
       <c r="I12" t="n">
-        <v>624.8</v>
+        <v>629.6</v>
       </c>
       <c r="J12" t="n">
-        <v>653.1</v>
+        <v>629.6</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>-1.175</v>
+        <v>1.9</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N12" t="n">
-        <v>112277.95</v>
+        <v>110989.91</v>
       </c>
       <c r="O12" t="n">
-        <v>110958.68</v>
+        <v>113921.15</v>
       </c>
     </row>
     <row r="13">
@@ -3308,7 +3308,7 @@
         <v>711.3</v>
       </c>
       <c r="I13" t="n">
-        <v>692.7</v>
+        <v>695.9</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>110958.68</v>
+        <v>113921.15</v>
       </c>
       <c r="O13" t="n">
-        <v>110958.68</v>
+        <v>113921.15</v>
       </c>
     </row>
     <row r="14">
@@ -3356,7 +3356,7 @@
         <v>5050</v>
       </c>
       <c r="I14" t="n">
-        <v>5214</v>
+        <v>5186</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -3367,13 +3367,13 @@
         <v>-1</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>-1.175</v>
+        <v>-1.39</v>
       </c>
       <c r="N14" t="n">
         <v>100000</v>
       </c>
       <c r="O14" t="n">
-        <v>98825</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="15">
@@ -3397,11 +3397,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>4082</v>
@@ -3410,27 +3410,27 @@
         <v>3930</v>
       </c>
       <c r="I15" t="n">
-        <v>4462</v>
+        <v>4371</v>
       </c>
       <c r="J15" t="n">
-        <v>3930</v>
+        <v>4371</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>-1.175</v>
+        <v>1.9</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N15" t="n">
-        <v>98825</v>
+        <v>98610</v>
       </c>
       <c r="O15" t="n">
-        <v>97663.81</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="16">
@@ -3449,28 +3449,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>2990</v>
+        <v>4082</v>
       </c>
       <c r="H16" t="n">
-        <v>2951</v>
+        <v>4016</v>
       </c>
       <c r="I16" t="n">
-        <v>3088</v>
+        <v>4207</v>
       </c>
       <c r="J16" t="n">
-        <v>3089</v>
+        <v>4207</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -3478,83 +3478,80 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.5385</v>
+        <v>1.9</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2.9827</v>
+        <v>2.641</v>
       </c>
       <c r="N16" t="n">
-        <v>97663.81</v>
+        <v>101214.29</v>
       </c>
       <c r="O16" t="n">
-        <v>100576.82</v>
+        <v>103887.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures</t>
+          <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>377.8</v>
+        <v>4082</v>
       </c>
       <c r="H17" t="n">
-        <v>382.86</v>
+        <v>4049</v>
       </c>
       <c r="I17" t="n">
-        <v>365.15</v>
-      </c>
-      <c r="J17" t="n">
-        <v>382.86</v>
+        <v>4145</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L17" t="n">
         <v>-1</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>-1.175</v>
+        <v>-1.39</v>
       </c>
       <c r="N17" t="n">
-        <v>100000</v>
+        <v>103887.36</v>
       </c>
       <c r="O17" t="n">
-        <v>98825</v>
+        <v>102443.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures</t>
+          <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3563,28 +3560,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>345.1</v>
+        <v>2990</v>
       </c>
       <c r="H18" t="n">
-        <v>341.79</v>
+        <v>2951</v>
       </c>
       <c r="I18" t="n">
-        <v>353.38</v>
+        <v>3064</v>
       </c>
       <c r="J18" t="n">
-        <v>353.38</v>
+        <v>3064</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -3592,22 +3589,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N18" t="n">
-        <v>98825</v>
+        <v>102443.33</v>
       </c>
       <c r="O18" t="n">
-        <v>101727.98</v>
+        <v>105148.85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures</t>
+          <t>Coffee_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -3620,48 +3617,51 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>478.2</v>
+        <v>377.8</v>
       </c>
       <c r="H19" t="n">
-        <v>480.1</v>
+        <v>382.86</v>
       </c>
       <c r="I19" t="n">
-        <v>473.4</v>
+        <v>368.19</v>
+      </c>
+      <c r="J19" t="n">
+        <v>382.86</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>-1</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>-1.175</v>
+        <v>-1.39</v>
       </c>
       <c r="N19" t="n">
         <v>100000</v>
       </c>
       <c r="O19" t="n">
-        <v>98825</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures</t>
+          <t>Coffee_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -3669,33 +3669,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>486.4</v>
+        <v>345.1</v>
       </c>
       <c r="H20" t="n">
-        <v>487.5</v>
+        <v>341.79</v>
       </c>
       <c r="I20" t="n">
-        <v>483.6</v>
+        <v>351.39</v>
       </c>
       <c r="J20" t="n">
-        <v>483.6</v>
+        <v>351.39</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N20" t="n">
-        <v>98825</v>
+        <v>98610</v>
       </c>
       <c r="O20" t="n">
-        <v>101727.98</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="21">
@@ -3722,54 +3722,54 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>411</v>
+        <v>478.2</v>
       </c>
       <c r="H21" t="n">
-        <v>408.3</v>
+        <v>480.1</v>
       </c>
       <c r="I21" t="n">
-        <v>417.8</v>
+        <v>474.6</v>
       </c>
       <c r="J21" t="n">
-        <v>408.3</v>
+        <v>473.6</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v>-1.175</v>
+        <v>2.4211</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>3.3653</v>
       </c>
       <c r="N21" t="n">
-        <v>101727.98</v>
+        <v>100000</v>
       </c>
       <c r="O21" t="n">
-        <v>100532.68</v>
+        <v>103365.26</v>
       </c>
     </row>
     <row r="22">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3788,95 +3788,109 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>488.1</v>
+        <v>486.4</v>
       </c>
       <c r="H22" t="n">
-        <v>492.1</v>
+        <v>487.5</v>
       </c>
       <c r="I22" t="n">
-        <v>478.1</v>
+        <v>484.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>484.3</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N22" t="n">
-        <v>100532.68</v>
+        <v>103365.26</v>
       </c>
       <c r="O22" t="n">
-        <v>100532.68</v>
+        <v>106095.14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>49750</v>
+        <v>411</v>
       </c>
       <c r="H23" t="n">
-        <v>49811</v>
+        <v>408.3</v>
       </c>
       <c r="I23" t="n">
-        <v>49598</v>
-      </c>
-      <c r="J23" t="n">
-        <v>49495</v>
+        <v>416.1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.1803</v>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>4.9119</v>
+        <v>-1</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N23" t="n">
-        <v>100000</v>
+        <v>106095.14</v>
       </c>
       <c r="O23" t="n">
-        <v>104911.89</v>
+        <v>104620.42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3885,45 +3899,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
+          <t>2026-07-24</t>
+        </is>
       </c>
       <c r="G24" t="n">
-        <v>51744</v>
+        <v>488.1</v>
       </c>
       <c r="H24" t="n">
-        <v>51850</v>
+        <v>492.1</v>
       </c>
       <c r="I24" t="n">
-        <v>51479</v>
-      </c>
-      <c r="J24" t="n">
-        <v>51479</v>
+        <v>480.5</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>target_r</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>2.9375</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N24" t="n">
-        <v>104911.89</v>
+        <v>104620.42</v>
       </c>
       <c r="O24" t="n">
-        <v>107993.67</v>
+        <v>104620.42</v>
       </c>
     </row>
     <row r="25">
@@ -3933,7 +3930,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3942,55 +3939,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>52734</v>
+        <v>49750</v>
       </c>
       <c r="H25" t="n">
-        <v>53106</v>
+        <v>49811</v>
       </c>
       <c r="I25" t="n">
-        <v>51804</v>
+        <v>49634</v>
       </c>
       <c r="J25" t="n">
-        <v>53106</v>
+        <v>49495</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M25" s="5" t="n">
-        <v>-1.175</v>
+        <v>4.1803</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>5.8107</v>
       </c>
       <c r="N25" t="n">
-        <v>107993.67</v>
+        <v>100000</v>
       </c>
       <c r="O25" t="n">
-        <v>106724.75</v>
+        <v>105810.66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3999,28 +3996,28 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1.1783</v>
+        <v>51744</v>
       </c>
       <c r="H26" t="n">
-        <v>1.17986</v>
+        <v>51850</v>
       </c>
       <c r="I26" t="n">
-        <v>1.1744</v>
+        <v>51543</v>
       </c>
       <c r="J26" t="n">
-        <v>1.17435</v>
+        <v>51543</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -4028,79 +4025,79 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.5321</v>
+        <v>1.9</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2.9752</v>
+        <v>2.641</v>
       </c>
       <c r="N26" t="n">
-        <v>100000</v>
+        <v>105810.66</v>
       </c>
       <c r="O26" t="n">
-        <v>102975.16</v>
+        <v>108605.12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1.1391</v>
+        <v>52734</v>
       </c>
       <c r="H27" t="n">
-        <v>1.13634</v>
+        <v>53106</v>
       </c>
       <c r="I27" t="n">
-        <v>1.146</v>
+        <v>52027</v>
       </c>
       <c r="J27" t="n">
-        <v>1.146</v>
+        <v>53106</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>2.9375</v>
+        <v>-1</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N27" t="n">
-        <v>102975.16</v>
+        <v>108605.12</v>
       </c>
       <c r="O27" t="n">
-        <v>106000.06</v>
+        <v>107095.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -4113,28 +4110,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>6043.4</v>
+        <v>1.1783</v>
       </c>
       <c r="H28" t="n">
-        <v>6073.35</v>
+        <v>1.17986</v>
       </c>
       <c r="I28" t="n">
-        <v>5968.52</v>
+        <v>1.17534</v>
       </c>
       <c r="J28" t="n">
-        <v>5968.52</v>
+        <v>1.17435</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4142,22 +4139,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>2.5321</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2.9375</v>
+        <v>3.5196</v>
       </c>
       <c r="N28" t="n">
         <v>100000</v>
       </c>
       <c r="O28" t="n">
-        <v>102937.5</v>
+        <v>103519.55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -4165,33 +4162,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>6060.23</v>
+        <v>1.1391</v>
       </c>
       <c r="H29" t="n">
-        <v>6078.29</v>
+        <v>1.13634</v>
       </c>
       <c r="I29" t="n">
-        <v>6015.08</v>
+        <v>1.14434</v>
       </c>
       <c r="J29" t="n">
-        <v>6015.08</v>
+        <v>1.14434</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4199,16 +4196,16 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N29" t="n">
-        <v>102937.5</v>
+        <v>103519.55</v>
       </c>
       <c r="O29" t="n">
-        <v>105961.29</v>
+        <v>106253.5</v>
       </c>
     </row>
     <row r="30">
@@ -4218,7 +4215,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4227,28 +4224,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>6060.23</v>
+        <v>6043.4</v>
       </c>
       <c r="H30" t="n">
-        <v>6099.08</v>
+        <v>6073.35</v>
       </c>
       <c r="I30" t="n">
-        <v>5963.1</v>
+        <v>5986.49</v>
       </c>
       <c r="J30" t="n">
-        <v>5963.1</v>
+        <v>5986.49</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4256,113 +4253,113 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N30" t="n">
-        <v>105961.29</v>
+        <v>100000</v>
       </c>
       <c r="O30" t="n">
-        <v>109073.9</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance</t>
+          <t>EURO_STOXX_50_Index</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>2812</v>
+        <v>6060.23</v>
       </c>
       <c r="H31" t="n">
-        <v>2754</v>
+        <v>6078.29</v>
       </c>
       <c r="I31" t="n">
-        <v>2957</v>
+        <v>6025.92</v>
       </c>
       <c r="J31" t="n">
-        <v>2754</v>
+        <v>6025.92</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M31" s="5" t="n">
-        <v>-1.175</v>
+        <v>1.9</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N31" t="n">
-        <v>100000</v>
+        <v>102641</v>
       </c>
       <c r="O31" t="n">
-        <v>98825</v>
+        <v>105351.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance</t>
+          <t>EURO_STOXX_50_Index</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>1818</v>
+        <v>6060.23</v>
       </c>
       <c r="H32" t="n">
-        <v>1799</v>
+        <v>6099.08</v>
       </c>
       <c r="I32" t="n">
-        <v>1866</v>
+        <v>5986.41</v>
       </c>
       <c r="J32" t="n">
-        <v>1866</v>
+        <v>5986.41</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4370,16 +4367,16 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N32" t="n">
-        <v>98825</v>
+        <v>105351.75</v>
       </c>
       <c r="O32" t="n">
-        <v>101727.98</v>
+        <v>108134.09</v>
       </c>
     </row>
     <row r="33">
@@ -4389,94 +4386,94 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>2370</v>
+        <v>2812</v>
       </c>
       <c r="H33" t="n">
-        <v>2386</v>
+        <v>2754</v>
       </c>
       <c r="I33" t="n">
-        <v>2330</v>
+        <v>2922</v>
       </c>
       <c r="J33" t="n">
-        <v>2330</v>
+        <v>2754</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>2.9375</v>
+        <v>-1</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N33" t="n">
-        <v>101727.98</v>
+        <v>100000</v>
       </c>
       <c r="O33" t="n">
-        <v>104716.24</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>German_Long_Bund</t>
+          <t>Ethereum_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>127.47</v>
+        <v>1818</v>
       </c>
       <c r="H34" t="n">
-        <v>127.7</v>
+        <v>1799</v>
       </c>
       <c r="I34" t="n">
-        <v>126.89</v>
+        <v>1854</v>
       </c>
       <c r="J34" t="n">
-        <v>126.89</v>
+        <v>1854</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4484,26 +4481,26 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N34" t="n">
-        <v>100000</v>
+        <v>98610</v>
       </c>
       <c r="O34" t="n">
-        <v>102937.5</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>Ethereum_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4512,28 +4509,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>4393</v>
+        <v>2370</v>
       </c>
       <c r="H35" t="n">
-        <v>4409.6</v>
+        <v>2386</v>
       </c>
       <c r="I35" t="n">
-        <v>4351.5</v>
+        <v>2340</v>
       </c>
       <c r="J35" t="n">
-        <v>4258.5</v>
+        <v>2340</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4541,26 +4538,26 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>8.102399999999999</v>
+        <v>1.9</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>9.520300000000001</v>
+        <v>2.641</v>
       </c>
       <c r="N35" t="n">
-        <v>100000</v>
+        <v>101214.29</v>
       </c>
       <c r="O35" t="n">
-        <v>109520.33</v>
+        <v>103887.36</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>German_Long_Bund</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4569,28 +4566,28 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>4393</v>
+        <v>127.47</v>
       </c>
       <c r="H36" t="n">
-        <v>4420.6</v>
+        <v>127.7</v>
       </c>
       <c r="I36" t="n">
-        <v>4324</v>
+        <v>127.03</v>
       </c>
       <c r="J36" t="n">
-        <v>4324</v>
+        <v>127.03</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4598,16 +4595,16 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N36" t="n">
-        <v>109520.33</v>
+        <v>100000</v>
       </c>
       <c r="O36" t="n">
-        <v>112737.49</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="37">
@@ -4617,7 +4614,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4626,28 +4623,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>5358.1</v>
+        <v>4393</v>
       </c>
       <c r="H37" t="n">
-        <v>5434.2</v>
+        <v>4409.6</v>
       </c>
       <c r="I37" t="n">
-        <v>5167.8</v>
+        <v>4361.5</v>
       </c>
       <c r="J37" t="n">
-        <v>5167.8</v>
+        <v>4258.5</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4655,16 +4652,16 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.5</v>
+        <v>8.102399999999999</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2.9375</v>
+        <v>11.2623</v>
       </c>
       <c r="N37" t="n">
-        <v>112737.49</v>
+        <v>100000</v>
       </c>
       <c r="O37" t="n">
-        <v>116049.15</v>
+        <v>111262.35</v>
       </c>
     </row>
     <row r="38">
@@ -4674,37 +4671,37 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>4335</v>
+        <v>4393</v>
       </c>
       <c r="H38" t="n">
-        <v>4306.2</v>
+        <v>4420.6</v>
       </c>
       <c r="I38" t="n">
-        <v>4407</v>
+        <v>4340.6</v>
       </c>
       <c r="J38" t="n">
-        <v>4473.5</v>
+        <v>4340</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4712,16 +4709,16 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.809</v>
+        <v>1.9203</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5.6506</v>
+        <v>2.6692</v>
       </c>
       <c r="N38" t="n">
-        <v>116049.15</v>
+        <v>111262.35</v>
       </c>
       <c r="O38" t="n">
-        <v>122606.64</v>
+        <v>114232.17</v>
       </c>
     </row>
     <row r="39">
@@ -4731,7 +4728,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4740,42 +4737,45 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>4746</v>
+        <v>5358.1</v>
       </c>
       <c r="H39" t="n">
-        <v>4758.5</v>
+        <v>5434.2</v>
       </c>
       <c r="I39" t="n">
-        <v>4714.8</v>
+        <v>5213.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5213.5</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M39" s="5" t="n">
-        <v>-1.175</v>
+        <v>1.9</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N39" t="n">
-        <v>122606.64</v>
+        <v>114232.17</v>
       </c>
       <c r="O39" t="n">
-        <v>121166.01</v>
+        <v>117249.04</v>
       </c>
     </row>
     <row r="40">
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4794,45 +4794,45 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>4347</v>
+        <v>4335</v>
       </c>
       <c r="H40" t="n">
-        <v>4292.9</v>
+        <v>4306.2</v>
       </c>
       <c r="I40" t="n">
-        <v>4482.3</v>
+        <v>4389.7</v>
       </c>
       <c r="J40" t="n">
-        <v>4292.9</v>
+        <v>4389.7</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v>-1.175</v>
+        <v>1.9</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N40" t="n">
-        <v>121166.01</v>
+        <v>117249.04</v>
       </c>
       <c r="O40" t="n">
-        <v>119742.31</v>
+        <v>120345.59</v>
       </c>
     </row>
     <row r="41">
@@ -4842,54 +4842,51 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>4103</v>
+        <v>4746</v>
       </c>
       <c r="H41" t="n">
-        <v>4046.1</v>
+        <v>4758.5</v>
       </c>
       <c r="I41" t="n">
-        <v>4245.2</v>
-      </c>
-      <c r="J41" t="n">
-        <v>4245.2</v>
+        <v>4722.2</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M41" s="2" t="n">
-        <v>2.9375</v>
+        <v>-1</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N41" t="n">
-        <v>119742.31</v>
+        <v>120345.59</v>
       </c>
       <c r="O41" t="n">
-        <v>123259.74</v>
+        <v>118672.78</v>
       </c>
     </row>
     <row r="42">
@@ -4899,7 +4896,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4908,45 +4905,45 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>3984</v>
+        <v>4347</v>
       </c>
       <c r="H42" t="n">
-        <v>3955.3</v>
+        <v>4292.9</v>
       </c>
       <c r="I42" t="n">
-        <v>4055.7</v>
+        <v>4449.8</v>
       </c>
       <c r="J42" t="n">
-        <v>4055.7</v>
+        <v>4292.9</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M42" s="2" t="n">
-        <v>2.9375</v>
+        <v>-1</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N42" t="n">
-        <v>123259.74</v>
+        <v>118672.78</v>
       </c>
       <c r="O42" t="n">
-        <v>126880.49</v>
+        <v>117023.23</v>
       </c>
     </row>
     <row r="43">
@@ -4956,7 +4953,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4965,28 +4962,28 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>3984</v>
+        <v>4103</v>
       </c>
       <c r="H43" t="n">
-        <v>3962.9</v>
+        <v>4046.1</v>
       </c>
       <c r="I43" t="n">
-        <v>4036.8</v>
+        <v>4211.1</v>
       </c>
       <c r="J43" t="n">
-        <v>4036.8</v>
+        <v>4234.9</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -4994,137 +4991,140 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.5</v>
+        <v>2.3181</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2.9375</v>
+        <v>3.2222</v>
       </c>
       <c r="N43" t="n">
-        <v>126880.49</v>
+        <v>117023.23</v>
       </c>
       <c r="O43" t="n">
-        <v>130607.61</v>
+        <v>120793.91</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>0.006417</v>
+        <v>3984</v>
       </c>
       <c r="H44" t="n">
-        <v>0.006454</v>
+        <v>3955.3</v>
       </c>
       <c r="I44" t="n">
-        <v>0.006324</v>
+        <v>4038.5</v>
       </c>
       <c r="J44" t="n">
-        <v>0.006454</v>
+        <v>4038.5</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v>-1.175</v>
+        <v>1.9</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N44" t="n">
-        <v>100000</v>
+        <v>120793.91</v>
       </c>
       <c r="O44" t="n">
-        <v>98825</v>
+        <v>123984.08</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>239.06</v>
+        <v>3984</v>
       </c>
       <c r="H45" t="n">
-        <v>239.73</v>
+        <v>3962.9</v>
       </c>
       <c r="I45" t="n">
-        <v>237.39</v>
+        <v>4024.1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>4024.1</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v>-1.175</v>
+        <v>1.9</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N45" t="n">
-        <v>100000</v>
+        <v>123984.08</v>
       </c>
       <c r="O45" t="n">
-        <v>98825</v>
+        <v>127258.49</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5133,45 +5133,45 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G46" t="n">
-        <v>251.58</v>
+        <v>0.006417</v>
       </c>
       <c r="H46" t="n">
-        <v>251.91</v>
+        <v>0.006454</v>
       </c>
       <c r="I46" t="n">
-        <v>250.76</v>
+        <v>0.006347</v>
       </c>
       <c r="J46" t="n">
-        <v>250.76</v>
+        <v>0.006454</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>2.9375</v>
+        <v>-1</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N46" t="n">
-        <v>98825</v>
+        <v>100000</v>
       </c>
       <c r="O46" t="n">
-        <v>101727.98</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="47">
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5190,45 +5190,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>255.38</v>
+        <v>239.06</v>
       </c>
       <c r="H47" t="n">
-        <v>256.63</v>
+        <v>239.73</v>
       </c>
       <c r="I47" t="n">
-        <v>252.25</v>
-      </c>
-      <c r="J47" t="n">
-        <v>252.25</v>
+        <v>237.79</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>2.9375</v>
+        <v>-1</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N47" t="n">
-        <v>101727.98</v>
+        <v>100000</v>
       </c>
       <c r="O47" t="n">
-        <v>104716.24</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="48">
@@ -5238,37 +5235,37 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>235.2</v>
+        <v>251.58</v>
       </c>
       <c r="H48" t="n">
-        <v>234.36</v>
+        <v>251.91</v>
       </c>
       <c r="I48" t="n">
-        <v>237.3</v>
+        <v>250.95</v>
       </c>
       <c r="J48" t="n">
-        <v>237.3</v>
+        <v>250.95</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -5276,83 +5273,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N48" t="n">
-        <v>104716.24</v>
+        <v>98610</v>
       </c>
       <c r="O48" t="n">
-        <v>107792.28</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>5.7714</v>
+        <v>255.38</v>
       </c>
       <c r="H49" t="n">
-        <v>5.6849</v>
+        <v>256.63</v>
       </c>
       <c r="I49" t="n">
-        <v>5.9877</v>
+        <v>253</v>
       </c>
       <c r="J49" t="n">
-        <v>5.6849</v>
+        <v>253</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M49" s="5" t="n">
-        <v>-1.175</v>
+        <v>1.9</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N49" t="n">
-        <v>100000</v>
+        <v>101214.29</v>
       </c>
       <c r="O49" t="n">
-        <v>98825</v>
+        <v>103887.36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5361,45 +5358,45 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>5.7714</v>
+        <v>235.2</v>
       </c>
       <c r="H50" t="n">
-        <v>5.6774</v>
+        <v>234.36</v>
       </c>
       <c r="I50" t="n">
-        <v>6.0064</v>
+        <v>236.8</v>
       </c>
       <c r="J50" t="n">
-        <v>5.6774</v>
+        <v>236.8</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v>-1.175</v>
+        <v>1.9</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N50" t="n">
-        <v>98825</v>
+        <v>103887.36</v>
       </c>
       <c r="O50" t="n">
-        <v>97663.81</v>
+        <v>106631.02</v>
       </c>
     </row>
     <row r="51">
@@ -5409,7 +5406,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5418,45 +5415,45 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>5.3133</v>
+        <v>5.7714</v>
       </c>
       <c r="H51" t="n">
-        <v>5.2459</v>
+        <v>5.6849</v>
       </c>
       <c r="I51" t="n">
-        <v>5.4818</v>
+        <v>5.9357</v>
       </c>
       <c r="J51" t="n">
-        <v>5.485</v>
+        <v>5.6849</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.5475</v>
-      </c>
-      <c r="M51" s="2" t="n">
-        <v>2.9933</v>
+        <v>-1</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N51" t="n">
-        <v>97663.81</v>
+        <v>100000</v>
       </c>
       <c r="O51" t="n">
-        <v>100587.16</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="52">
@@ -5466,37 +5463,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>6.0956</v>
+        <v>5.7714</v>
       </c>
       <c r="H52" t="n">
-        <v>6.1481</v>
+        <v>5.6774</v>
       </c>
       <c r="I52" t="n">
-        <v>5.9644</v>
+        <v>5.95</v>
       </c>
       <c r="J52" t="n">
-        <v>6.1481</v>
+        <v>5.6774</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -5507,80 +5504,80 @@
         <v>-1</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>-1.175</v>
+        <v>-1.39</v>
       </c>
       <c r="N52" t="n">
-        <v>100587.16</v>
+        <v>98610</v>
       </c>
       <c r="O52" t="n">
-        <v>99405.25999999999</v>
+        <v>97239.32000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>3.305</v>
+        <v>5.3133</v>
       </c>
       <c r="H53" t="n">
-        <v>3.354</v>
+        <v>5.2459</v>
       </c>
       <c r="I53" t="n">
-        <v>3.183</v>
+        <v>5.4414</v>
       </c>
       <c r="J53" t="n">
-        <v>3.354</v>
+        <v>5.4414</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M53" s="5" t="n">
-        <v>-1.175</v>
+        <v>1.9</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N53" t="n">
-        <v>100000</v>
+        <v>97239.32000000001</v>
       </c>
       <c r="O53" t="n">
-        <v>98825</v>
+        <v>99807.41</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -5589,51 +5586,51 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54" t="n">
-        <v>3.305</v>
+        <v>6.0956</v>
       </c>
       <c r="H54" t="n">
-        <v>3.356</v>
+        <v>6.1481</v>
       </c>
       <c r="I54" t="n">
-        <v>3.178</v>
+        <v>5.9959</v>
       </c>
       <c r="J54" t="n">
-        <v>3.178</v>
+        <v>6.1481</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M54" s="2" t="n">
-        <v>2.9375</v>
+        <v>-1</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N54" t="n">
-        <v>98825</v>
+        <v>99807.41</v>
       </c>
       <c r="O54" t="n">
-        <v>101727.98</v>
+        <v>98420.09</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -5641,56 +5638,56 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1360.4</v>
+        <v>3.305</v>
       </c>
       <c r="H55" t="n">
-        <v>1343.4</v>
+        <v>3.354</v>
       </c>
       <c r="I55" t="n">
-        <v>1402.9</v>
+        <v>3.212</v>
       </c>
       <c r="J55" t="n">
-        <v>1403</v>
+        <v>3.354</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.5059</v>
-      </c>
-      <c r="M55" s="2" t="n">
-        <v>2.9444</v>
+        <v>-1</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N55" t="n">
         <v>100000</v>
       </c>
       <c r="O55" t="n">
-        <v>102944.41</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -5698,33 +5695,33 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>1167</v>
+        <v>3.305</v>
       </c>
       <c r="H56" t="n">
-        <v>1159.4</v>
+        <v>3.356</v>
       </c>
       <c r="I56" t="n">
-        <v>1186</v>
+        <v>3.208</v>
       </c>
       <c r="J56" t="n">
-        <v>1186</v>
+        <v>3.208</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -5732,22 +5729,22 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N56" t="n">
-        <v>102944.41</v>
+        <v>98610</v>
       </c>
       <c r="O56" t="n">
-        <v>105968.4</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -5755,56 +5752,56 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>2084.6</v>
+        <v>1360.4</v>
       </c>
       <c r="H57" t="n">
-        <v>2113.7</v>
+        <v>1343.4</v>
       </c>
       <c r="I57" t="n">
-        <v>2011.9</v>
+        <v>1392.7</v>
       </c>
       <c r="J57" t="n">
-        <v>2113.7</v>
+        <v>1403</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M57" s="5" t="n">
-        <v>-1.175</v>
+        <v>2.5059</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>3.4832</v>
       </c>
       <c r="N57" t="n">
         <v>100000</v>
       </c>
       <c r="O57" t="n">
-        <v>98825</v>
+        <v>103483.18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -5817,45 +5814,45 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1641.5</v>
+        <v>1167</v>
       </c>
       <c r="H58" t="n">
-        <v>1621</v>
+        <v>1159.4</v>
       </c>
       <c r="I58" t="n">
-        <v>1692.8</v>
+        <v>1181.4</v>
       </c>
       <c r="J58" t="n">
-        <v>1621</v>
+        <v>1181.4</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v>-1.175</v>
+        <v>1.9</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N58" t="n">
-        <v>98825</v>
+        <v>103483.18</v>
       </c>
       <c r="O58" t="n">
-        <v>97663.81</v>
+        <v>106216.17</v>
       </c>
     </row>
     <row r="59">
@@ -5865,151 +5862,151 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>1581.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H59" t="n">
-        <v>1547.6</v>
+        <v>2113.7</v>
       </c>
       <c r="I59" t="n">
-        <v>1666.2</v>
+        <v>2029.3</v>
       </c>
       <c r="J59" t="n">
-        <v>1547.6</v>
+        <v>2029.3</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v>-1.175</v>
+        <v>1.9</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N59" t="n">
-        <v>97663.81</v>
+        <v>100000</v>
       </c>
       <c r="O59" t="n">
-        <v>96516.25999999999</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>27907</v>
+        <v>1641.5</v>
       </c>
       <c r="H60" t="n">
-        <v>27965.76</v>
+        <v>1621</v>
       </c>
       <c r="I60" t="n">
-        <v>27760.1</v>
+        <v>1680.5</v>
       </c>
       <c r="J60" t="n">
-        <v>27760</v>
+        <v>1621</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.5017</v>
-      </c>
-      <c r="M60" s="2" t="n">
-        <v>2.9395</v>
+        <v>-1</v>
+      </c>
+      <c r="M60" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N60" t="n">
-        <v>100000</v>
+        <v>102641</v>
       </c>
       <c r="O60" t="n">
-        <v>102939.5</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>7206.55</v>
+        <v>1581.5</v>
       </c>
       <c r="H61" t="n">
-        <v>7223.26</v>
+        <v>1547.6</v>
       </c>
       <c r="I61" t="n">
-        <v>7164.77</v>
+        <v>1645.9</v>
       </c>
       <c r="J61" t="n">
-        <v>7164.77</v>
+        <v>1645.9</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -6017,56 +6014,56 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N61" t="n">
-        <v>100000</v>
+        <v>101214.29</v>
       </c>
       <c r="O61" t="n">
-        <v>102937.5</v>
+        <v>103887.36</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>6957.43</v>
+        <v>1559</v>
       </c>
       <c r="H62" t="n">
-        <v>6965.7</v>
+        <v>1539.5</v>
       </c>
       <c r="I62" t="n">
-        <v>6936.76</v>
+        <v>1596</v>
       </c>
       <c r="J62" t="n">
-        <v>6936.76</v>
+        <v>1596</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -6074,26 +6071,26 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N62" t="n">
-        <v>100000</v>
+        <v>103887.36</v>
       </c>
       <c r="O62" t="n">
-        <v>102937.5</v>
+        <v>106631.02</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6102,55 +6099,52 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>6982.4</v>
+        <v>27907</v>
       </c>
       <c r="H63" t="n">
-        <v>6988.83</v>
+        <v>27965.76</v>
       </c>
       <c r="I63" t="n">
-        <v>6966.32</v>
-      </c>
-      <c r="J63" t="n">
-        <v>7002</v>
+        <v>27795.36</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-3.0482</v>
+        <v>-1</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>-3.5816</v>
+        <v>-1.39</v>
       </c>
       <c r="N63" t="n">
-        <v>102937.5</v>
+        <v>100000</v>
       </c>
       <c r="O63" t="n">
-        <v>99250.64</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -6159,28 +6153,28 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>6982.4</v>
+        <v>7206.55</v>
       </c>
       <c r="H64" t="n">
-        <v>6992.85</v>
+        <v>7223.26</v>
       </c>
       <c r="I64" t="n">
-        <v>6956.27</v>
+        <v>7174.8</v>
       </c>
       <c r="J64" t="n">
-        <v>6947.27</v>
+        <v>7174.8</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6188,16 +6182,16 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.3617</v>
+        <v>1.9</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3.95</v>
+        <v>2.641</v>
       </c>
       <c r="N64" t="n">
-        <v>99250.64</v>
+        <v>100000</v>
       </c>
       <c r="O64" t="n">
-        <v>103171.06</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="65">
@@ -6207,7 +6201,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -6216,42 +6210,45 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H65" t="n">
-        <v>6991.93</v>
+        <v>6965.7</v>
       </c>
       <c r="I65" t="n">
-        <v>6958.57</v>
+        <v>6941.72</v>
+      </c>
+      <c r="J65" t="n">
+        <v>6941.72</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M65" s="5" t="n">
-        <v>-1.175</v>
+        <v>1.9</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N65" t="n">
-        <v>103171.06</v>
+        <v>100000</v>
       </c>
       <c r="O65" t="n">
-        <v>101958.8</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="66">
@@ -6261,7 +6258,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -6270,12 +6267,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -6285,27 +6282,30 @@
         <v>6982.4</v>
       </c>
       <c r="H66" t="n">
-        <v>6986.84</v>
+        <v>6988.83</v>
       </c>
       <c r="I66" t="n">
-        <v>6971.3</v>
+        <v>6970.18</v>
+      </c>
+      <c r="J66" t="n">
+        <v>7002</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>-1.175</v>
+        <v>-4.237</v>
       </c>
       <c r="N66" t="n">
-        <v>101958.8</v>
+        <v>102641</v>
       </c>
       <c r="O66" t="n">
-        <v>100760.79</v>
+        <v>98292.09</v>
       </c>
     </row>
     <row r="67">
@@ -6315,64 +6315,64 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H67" t="n">
-        <v>6770.77</v>
+        <v>6992.85</v>
       </c>
       <c r="I67" t="n">
-        <v>6853.48</v>
+        <v>6962.54</v>
       </c>
       <c r="J67" t="n">
-        <v>6769.03</v>
+        <v>6947.27</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-1.0736</v>
-      </c>
-      <c r="M67" s="5" t="n">
-        <v>-1.2615</v>
+        <v>3.3617</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>4.6728</v>
       </c>
       <c r="N67" t="n">
-        <v>100760.79</v>
+        <v>98292.09</v>
       </c>
       <c r="O67" t="n">
-        <v>99489.67</v>
+        <v>102885.07</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -6381,142 +6381,136 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H68" t="n">
-        <v>88.001</v>
+        <v>6991.93</v>
       </c>
       <c r="I68" t="n">
-        <v>81.28100000000001</v>
-      </c>
-      <c r="J68" t="n">
-        <v>88.001</v>
+        <v>6964.29</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L68" t="n">
         <v>-1</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>-1.175</v>
+        <v>-1.39</v>
       </c>
       <c r="N68" t="n">
-        <v>100000</v>
+        <v>102885.07</v>
       </c>
       <c r="O68" t="n">
-        <v>98825</v>
+        <v>101454.97</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>73.84399999999999</v>
+        <v>6982.4</v>
       </c>
       <c r="H69" t="n">
-        <v>71.999</v>
+        <v>6986.84</v>
       </c>
       <c r="I69" t="n">
-        <v>78.456</v>
-      </c>
-      <c r="J69" t="n">
-        <v>71.999</v>
+        <v>6973.96</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L69" t="n">
         <v>-1</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>-1.175</v>
+        <v>-1.39</v>
       </c>
       <c r="N69" t="n">
-        <v>98825</v>
+        <v>101454.97</v>
       </c>
       <c r="O69" t="n">
-        <v>97663.81</v>
+        <v>100044.75</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>15</v>
+        <v>6794.4</v>
       </c>
       <c r="H70" t="n">
-        <v>15.26</v>
+        <v>6770.77</v>
       </c>
       <c r="I70" t="n">
-        <v>14.35</v>
+        <v>6839.3</v>
       </c>
       <c r="J70" t="n">
-        <v>15.26</v>
+        <v>6769.03</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6524,22 +6518,22 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-1</v>
+        <v>-1.0736</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>-1.175</v>
+        <v>-1.4924</v>
       </c>
       <c r="N70" t="n">
-        <v>100000</v>
+        <v>100044.75</v>
       </c>
       <c r="O70" t="n">
-        <v>98825</v>
+        <v>98551.73</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -6552,28 +6546,28 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>20.89</v>
+        <v>86.081</v>
       </c>
       <c r="H71" t="n">
-        <v>21.07</v>
+        <v>88.001</v>
       </c>
       <c r="I71" t="n">
-        <v>20.44</v>
+        <v>82.43300000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>21.08</v>
+        <v>88.001</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6581,113 +6575,113 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-1.0556</v>
+        <v>-1</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>-1.2403</v>
+        <v>-1.39</v>
       </c>
       <c r="N71" t="n">
         <v>100000</v>
       </c>
       <c r="O71" t="n">
-        <v>98759.72</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G72" t="n">
-        <v>0.8614000000000001</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>0.8637</v>
+        <v>71.999</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8557</v>
+        <v>77.349</v>
       </c>
       <c r="J72" t="n">
-        <v>0.8637</v>
+        <v>77.349</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M72" s="5" t="n">
-        <v>-1.175</v>
+        <v>1.9</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N72" t="n">
-        <v>100000</v>
+        <v>98610</v>
       </c>
       <c r="O72" t="n">
-        <v>98825</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
         <v>2</v>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
       <c r="G73" t="n">
-        <v>0.8614000000000001</v>
+        <v>15</v>
       </c>
       <c r="H73" t="n">
-        <v>0.8658</v>
+        <v>15.26</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8504</v>
+        <v>14.51</v>
       </c>
       <c r="J73" t="n">
-        <v>0.8658</v>
+        <v>15.26</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6698,76 +6692,76 @@
         <v>-1</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>-1.175</v>
+        <v>-1.39</v>
       </c>
       <c r="N73" t="n">
-        <v>98825</v>
+        <v>100000</v>
       </c>
       <c r="O73" t="n">
-        <v>97663.81</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.8467</v>
+        <v>20.89</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8436</v>
+        <v>21.07</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8544</v>
+        <v>20.55</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8498</v>
+        <v>21.08</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
-      </c>
-      <c r="M74" s="2" t="n">
-        <v>1.175</v>
+        <v>-1.0556</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>-1.4672</v>
       </c>
       <c r="N74" t="n">
-        <v>97663.81</v>
+        <v>100000</v>
       </c>
       <c r="O74" t="n">
-        <v>98811.36</v>
+        <v>98532.78</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -6780,28 +6774,28 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>116.5</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H75" t="n">
-        <v>116.79</v>
+        <v>0.8637</v>
       </c>
       <c r="I75" t="n">
-        <v>115.77</v>
+        <v>0.857</v>
       </c>
       <c r="J75" t="n">
-        <v>116.79</v>
+        <v>0.8637</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6812,19 +6806,19 @@
         <v>-1</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>-1.175</v>
+        <v>-1.39</v>
       </c>
       <c r="N75" t="n">
         <v>100000</v>
       </c>
       <c r="O75" t="n">
-        <v>98825</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -6837,55 +6831,55 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>118.02</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>118.16</v>
+        <v>0.8658</v>
       </c>
       <c r="I76" t="n">
-        <v>117.67</v>
+        <v>0.853</v>
       </c>
       <c r="J76" t="n">
-        <v>117.67</v>
+        <v>0.8658</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M76" s="2" t="n">
-        <v>2.9375</v>
+        <v>-1</v>
+      </c>
+      <c r="M76" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N76" t="n">
-        <v>98825</v>
+        <v>98610</v>
       </c>
       <c r="O76" t="n">
-        <v>101727.98</v>
+        <v>97239.32000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -6894,112 +6888,112 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>97.81399999999999</v>
+        <v>0.8467</v>
       </c>
       <c r="H77" t="n">
-        <v>97.569</v>
+        <v>0.8436</v>
       </c>
       <c r="I77" t="n">
-        <v>98.42700000000001</v>
+        <v>0.8526</v>
       </c>
       <c r="J77" t="n">
-        <v>98.42700000000001</v>
+        <v>0.8498</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2.9375</v>
+        <v>1.39</v>
       </c>
       <c r="N77" t="n">
-        <v>100000</v>
+        <v>97239.32000000001</v>
       </c>
       <c r="O77" t="n">
-        <v>102937.5</v>
+        <v>98590.95</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>97.714</v>
+        <v>116.5</v>
       </c>
       <c r="H78" t="n">
-        <v>97.46899999999999</v>
+        <v>116.79</v>
       </c>
       <c r="I78" t="n">
-        <v>98.327</v>
+        <v>115.95</v>
       </c>
       <c r="J78" t="n">
-        <v>98.327</v>
+        <v>116.79</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M78" s="2" t="n">
-        <v>2.9375</v>
+        <v>-1</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N78" t="n">
-        <v>102937.5</v>
+        <v>100000</v>
       </c>
       <c r="O78" t="n">
-        <v>105961.29</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -7008,28 +7002,28 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>99.376</v>
+        <v>118.02</v>
       </c>
       <c r="H79" t="n">
-        <v>99.571</v>
+        <v>118.16</v>
       </c>
       <c r="I79" t="n">
-        <v>98.889</v>
+        <v>117.75</v>
       </c>
       <c r="J79" t="n">
-        <v>98.889</v>
+        <v>117.75</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -7037,26 +7031,26 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N79" t="n">
-        <v>105961.29</v>
+        <v>98610</v>
       </c>
       <c r="O79" t="n">
-        <v>109073.9</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -7065,45 +7059,42 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>99.246</v>
+        <v>118.08</v>
       </c>
       <c r="H80" t="n">
-        <v>99.501</v>
+        <v>118.16</v>
       </c>
       <c r="I80" t="n">
-        <v>98.608</v>
-      </c>
-      <c r="J80" t="n">
-        <v>99.501</v>
+        <v>117.93</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L80" t="n">
         <v>-1</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>-1.175</v>
+        <v>-1.39</v>
       </c>
       <c r="N80" t="n">
-        <v>109073.9</v>
+        <v>101214.29</v>
       </c>
       <c r="O80" t="n">
-        <v>107792.28</v>
+        <v>99807.41</v>
       </c>
     </row>
     <row r="81">
@@ -7113,37 +7104,37 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>100.066</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>100.201</v>
+        <v>97.569</v>
       </c>
       <c r="I81" t="n">
-        <v>99.72799999999999</v>
+        <v>98.279</v>
       </c>
       <c r="J81" t="n">
-        <v>99.72799999999999</v>
+        <v>98.279</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -7151,16 +7142,16 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N81" t="n">
-        <v>107792.28</v>
+        <v>100000</v>
       </c>
       <c r="O81" t="n">
-        <v>110958.68</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="82">
@@ -7170,37 +7161,37 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G82" t="n">
-        <v>100.066</v>
+        <v>97.714</v>
       </c>
       <c r="H82" t="n">
-        <v>100.316</v>
+        <v>97.46899999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>99.441</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>99.441</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -7208,16 +7199,16 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N82" t="n">
-        <v>110958.68</v>
+        <v>102641</v>
       </c>
       <c r="O82" t="n">
-        <v>114218.09</v>
+        <v>105351.75</v>
       </c>
     </row>
     <row r="83">
@@ -7227,7 +7218,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -7236,45 +7227,45 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G83" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H83" t="n">
-        <v>100.361</v>
+        <v>99.571</v>
       </c>
       <c r="I83" t="n">
-        <v>99.328</v>
+        <v>99.006</v>
       </c>
       <c r="J83" t="n">
-        <v>100.361</v>
+        <v>99.006</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M83" s="5" t="n">
-        <v>-1.175</v>
+        <v>1.9</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N83" t="n">
-        <v>114218.09</v>
+        <v>105351.75</v>
       </c>
       <c r="O83" t="n">
-        <v>112876.03</v>
+        <v>108134.09</v>
       </c>
     </row>
     <row r="84">
@@ -7284,7 +7275,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -7293,28 +7284,28 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G84" t="n">
-        <v>100.621</v>
+        <v>99.246</v>
       </c>
       <c r="H84" t="n">
-        <v>100.911</v>
+        <v>99.501</v>
       </c>
       <c r="I84" t="n">
-        <v>99.896</v>
+        <v>98.761</v>
       </c>
       <c r="J84" t="n">
-        <v>100.911</v>
+        <v>99.501</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7325,13 +7316,13 @@
         <v>-1</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>-1.175</v>
+        <v>-1.39</v>
       </c>
       <c r="N84" t="n">
-        <v>112876.03</v>
+        <v>108134.09</v>
       </c>
       <c r="O84" t="n">
-        <v>111549.74</v>
+        <v>106631.02</v>
       </c>
     </row>
     <row r="85">
@@ -7341,7 +7332,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -7350,28 +7341,28 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H85" t="n">
-        <v>101.526</v>
+        <v>100.201</v>
       </c>
       <c r="I85" t="n">
-        <v>101.123</v>
+        <v>99.809</v>
       </c>
       <c r="J85" t="n">
-        <v>101.123</v>
+        <v>99.809</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7379,26 +7370,26 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2.9375</v>
+        <v>2.641</v>
       </c>
       <c r="N85" t="n">
-        <v>111549.74</v>
+        <v>106631.02</v>
       </c>
       <c r="O85" t="n">
-        <v>114826.51</v>
+        <v>109447.15</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -7407,28 +7398,28 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>121.72</v>
+        <v>100.066</v>
       </c>
       <c r="H86" t="n">
-        <v>123.03</v>
+        <v>100.316</v>
       </c>
       <c r="I86" t="n">
-        <v>118.44</v>
+        <v>99.59099999999999</v>
       </c>
       <c r="J86" t="n">
-        <v>113.29</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7436,73 +7427,301 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>6.4351</v>
+        <v>2.424</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>7.5613</v>
+        <v>3.3694</v>
       </c>
       <c r="N86" t="n">
-        <v>100000</v>
+        <v>109447.15</v>
       </c>
       <c r="O86" t="n">
-        <v>107561.26</v>
+        <v>113134.82</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>7</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>100.066</v>
+      </c>
+      <c r="H87" t="n">
+        <v>100.361</v>
+      </c>
+      <c r="I87" t="n">
+        <v>99.505</v>
+      </c>
+      <c r="J87" t="n">
+        <v>100.361</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M87" s="5" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="N87" t="n">
+        <v>113134.82</v>
+      </c>
+      <c r="O87" t="n">
+        <v>111562.24</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>8</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>2</v>
+      </c>
+      <c r="G88" t="n">
+        <v>100.621</v>
+      </c>
+      <c r="H88" t="n">
+        <v>100.911</v>
+      </c>
+      <c r="I88" t="n">
+        <v>100.07</v>
+      </c>
+      <c r="J88" t="n">
+        <v>100.911</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M88" s="5" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="N88" t="n">
+        <v>111562.24</v>
+      </c>
+      <c r="O88" t="n">
+        <v>110011.53</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>9</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H89" t="n">
+        <v>101.526</v>
+      </c>
+      <c r="I89" t="n">
+        <v>101.192</v>
+      </c>
+      <c r="J89" t="n">
+        <v>101.192</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="N89" t="n">
+        <v>110011.53</v>
+      </c>
+      <c r="O89" t="n">
+        <v>112916.93</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B87" t="n">
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H90" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="I90" t="n">
+        <v>119.23</v>
+      </c>
+      <c r="J90" t="n">
+        <v>113.29</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>6.4351</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>8.944800000000001</v>
+      </c>
+      <c r="N90" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O90" t="n">
+        <v>108944.81</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
         <v>2</v>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="F87" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" t="n">
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
         <v>130.16</v>
       </c>
-      <c r="H87" t="n">
+      <c r="H91" t="n">
         <v>130.94</v>
       </c>
-      <c r="I87" t="n">
-        <v>128.21</v>
-      </c>
-      <c r="J87" t="n">
-        <v>128.21</v>
-      </c>
-      <c r="K87" t="inlineStr">
+      <c r="I91" t="n">
+        <v>128.68</v>
+      </c>
+      <c r="J91" t="n">
+        <v>128.68</v>
+      </c>
+      <c r="K91" t="inlineStr">
         <is>
           <t>target_r</t>
         </is>
       </c>
-      <c r="L87" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M87" s="2" t="n">
-        <v>2.9375</v>
-      </c>
-      <c r="N87" t="n">
-        <v>107561.26</v>
-      </c>
-      <c r="O87" t="n">
-        <v>110720.87</v>
+      <c r="L91" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="N91" t="n">
+        <v>108944.81</v>
+      </c>
+      <c r="O91" t="n">
+        <v>111822.04</v>
       </c>
     </row>
   </sheetData>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-28 00:45 UTC.</t>
+          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-28 05:43 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -602,17 +602,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -624,16 +624,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>100</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>13.92</v>
+        <v>16.93</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>113921.15</v>
+        <v>116929.81</v>
       </c>
     </row>
     <row r="4">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F4" t="n">
         <v>9</v>
@@ -687,7 +687,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -698,23 +698,23 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -723,46 +723,46 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7.1</v>
+        <v>7.38</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>107095.5</v>
+        <v>107383.44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -771,34 +771,34 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6.63</v>
+        <v>7.1</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>106631.02</v>
+        <v>107095.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -807,10 +807,10 @@
         <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -831,7 +831,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -842,20 +842,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -867,19 +867,19 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6.25</v>
+        <v>6.63</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>106253.5</v>
+        <v>106631.02</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -918,31 +918,31 @@
         <v>100</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6.22</v>
+        <v>6.25</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>106216.17</v>
+        <v>106253.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -966,34 +966,34 @@
         <v>100</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5.38</v>
+        <v>6.22</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>105381.31</v>
+        <v>106216.17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures</t>
+          <t>Bitcoin_Per_USD_CME</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -1002,22 +1002,22 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4.62</v>
+        <v>5.38</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>104620.42</v>
+        <v>105381.31</v>
       </c>
     </row>
     <row r="12">
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1271,11 +1271,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1316,11 +1316,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1361,11 +1361,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1406,11 +1406,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1451,11 +1451,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-28 05:43 UTC.</t>
+          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-28 16:18 UTC.</t>
         </is>
       </c>
     </row>
@@ -3301,6 +3301,14 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
       <c r="G13" t="n">
         <v>706</v>
       </c>
@@ -3310,16 +3318,25 @@
       <c r="I13" t="n">
         <v>695.9</v>
       </c>
+      <c r="J13" t="n">
+        <v>695.9</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N13" t="n">
         <v>113921.15</v>
       </c>
       <c r="O13" t="n">
-        <v>113921.15</v>
+        <v>116929.81</v>
       </c>
     </row>
     <row r="14">
@@ -3902,6 +3919,14 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
       <c r="G24" t="n">
         <v>488.1</v>
       </c>
@@ -3911,16 +3936,25 @@
       <c r="I24" t="n">
         <v>480.5</v>
       </c>
+      <c r="J24" t="n">
+        <v>480.5</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N24" t="n">
         <v>104620.42</v>
       </c>
       <c r="O24" t="n">
-        <v>104620.42</v>
+        <v>107383.44</v>
       </c>
     </row>
     <row r="25">

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-28 16:18 UTC.</t>
+          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-28 17:14 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-28 17:14 UTC.</t>
+          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-28 22:50 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-28 22:50 UTC.</t>
+          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-29 02:46 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -650,17 +650,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -675,13 +675,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>66.7</v>
+        <v>70</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12.92</v>
+        <v>15.9</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>112916.93</v>
+        <v>115899.07</v>
       </c>
     </row>
     <row r="5">
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>50</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1271,11 +1271,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1316,11 +1316,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1361,11 +1361,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1406,11 +1406,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1451,11 +1451,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-29 02:46 UTC.</t>
+          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-29); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-30 20:33 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5778,11 +5778,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -5791,45 +5791,28 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>1</v>
+          <t>2026-07-29</t>
+        </is>
       </c>
       <c r="G57" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H57" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="I57" t="n">
-        <v>1392.7</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1403</v>
+        <v>2.737</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>target_r</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>2.5059</v>
-      </c>
-      <c r="M57" s="2" t="n">
-        <v>3.4832</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N57" t="n">
-        <v>100000</v>
+        <v>101214.29</v>
       </c>
       <c r="O57" t="n">
-        <v>103483.18</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="58">
@@ -5839,7 +5822,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -5848,28 +5831,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H58" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="I58" t="n">
-        <v>1181.4</v>
+        <v>1392.7</v>
       </c>
       <c r="J58" t="n">
-        <v>1181.4</v>
+        <v>1403</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5877,56 +5860,56 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.9</v>
+        <v>2.5059</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2.641</v>
+        <v>3.4832</v>
       </c>
       <c r="N58" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O58" t="n">
         <v>103483.18</v>
-      </c>
-      <c r="O58" t="n">
-        <v>106216.17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H59" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="I59" t="n">
-        <v>2029.3</v>
+        <v>1181.4</v>
       </c>
       <c r="J59" t="n">
-        <v>2029.3</v>
+        <v>1181.4</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5940,10 +5923,10 @@
         <v>2.641</v>
       </c>
       <c r="N59" t="n">
-        <v>100000</v>
+        <v>103483.18</v>
       </c>
       <c r="O59" t="n">
-        <v>102641</v>
+        <v>106216.17</v>
       </c>
     </row>
     <row r="60">
@@ -5953,54 +5936,54 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>1641.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H60" t="n">
-        <v>1621</v>
+        <v>2113.7</v>
       </c>
       <c r="I60" t="n">
-        <v>1680.5</v>
+        <v>2029.3</v>
       </c>
       <c r="J60" t="n">
-        <v>1621</v>
+        <v>2029.3</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>-1.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N60" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O60" t="n">
         <v>102641</v>
-      </c>
-      <c r="O60" t="n">
-        <v>101214.29</v>
       </c>
     </row>
     <row r="61">
@@ -6010,7 +5993,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6019,45 +6002,45 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>1581.5</v>
+        <v>1641.5</v>
       </c>
       <c r="H61" t="n">
-        <v>1547.6</v>
+        <v>1621</v>
       </c>
       <c r="I61" t="n">
-        <v>1645.9</v>
+        <v>1680.5</v>
       </c>
       <c r="J61" t="n">
-        <v>1645.9</v>
+        <v>1621</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M61" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M61" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N61" t="n">
+        <v>102641</v>
+      </c>
+      <c r="O61" t="n">
         <v>101214.29</v>
-      </c>
-      <c r="O61" t="n">
-        <v>103887.36</v>
       </c>
     </row>
     <row r="62">
@@ -6067,7 +6050,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6076,28 +6059,28 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>1559</v>
+        <v>1581.5</v>
       </c>
       <c r="H62" t="n">
-        <v>1539.5</v>
+        <v>1547.6</v>
       </c>
       <c r="I62" t="n">
-        <v>1596</v>
+        <v>1645.9</v>
       </c>
       <c r="J62" t="n">
-        <v>1596</v>
+        <v>1645.9</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -6111,70 +6094,73 @@
         <v>2.641</v>
       </c>
       <c r="N62" t="n">
+        <v>101214.29</v>
+      </c>
+      <c r="O62" t="n">
         <v>103887.36</v>
-      </c>
-      <c r="O62" t="n">
-        <v>106631.02</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>27907</v>
+        <v>1559</v>
       </c>
       <c r="H63" t="n">
-        <v>27965.76</v>
+        <v>1539.5</v>
       </c>
       <c r="I63" t="n">
-        <v>27795.36</v>
+        <v>1596</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1596</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M63" s="5" t="n">
-        <v>-1.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N63" t="n">
-        <v>100000</v>
+        <v>103887.36</v>
       </c>
       <c r="O63" t="n">
-        <v>98610</v>
+        <v>106631.02</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -6187,51 +6173,48 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>7206.55</v>
+        <v>27907</v>
       </c>
       <c r="H64" t="n">
-        <v>7223.26</v>
+        <v>27965.76</v>
       </c>
       <c r="I64" t="n">
-        <v>7174.8</v>
-      </c>
-      <c r="J64" t="n">
-        <v>7174.8</v>
+        <v>27795.36</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M64" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N64" t="n">
         <v>100000</v>
       </c>
       <c r="O64" t="n">
-        <v>102641</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -6244,28 +6227,28 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>6957.43</v>
+        <v>7206.55</v>
       </c>
       <c r="H65" t="n">
-        <v>6965.7</v>
+        <v>7223.26</v>
       </c>
       <c r="I65" t="n">
-        <v>6941.72</v>
+        <v>7174.8</v>
       </c>
       <c r="J65" t="n">
-        <v>6941.72</v>
+        <v>7174.8</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -6292,7 +6275,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -6301,45 +6284,45 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H66" t="n">
-        <v>6988.83</v>
+        <v>6965.7</v>
       </c>
       <c r="I66" t="n">
-        <v>6970.18</v>
+        <v>6941.72</v>
       </c>
       <c r="J66" t="n">
-        <v>7002</v>
+        <v>6941.72</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-3.0482</v>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v>-4.237</v>
+        <v>1.9</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N66" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O66" t="n">
         <v>102641</v>
-      </c>
-      <c r="O66" t="n">
-        <v>98292.09</v>
       </c>
     </row>
     <row r="67">
@@ -6349,7 +6332,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -6358,12 +6341,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -6373,30 +6356,30 @@
         <v>6982.4</v>
       </c>
       <c r="H67" t="n">
-        <v>6992.85</v>
+        <v>6988.83</v>
       </c>
       <c r="I67" t="n">
-        <v>6962.54</v>
+        <v>6970.18</v>
       </c>
       <c r="J67" t="n">
-        <v>6947.27</v>
+        <v>7002</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.3617</v>
-      </c>
-      <c r="M67" s="2" t="n">
-        <v>4.6728</v>
+        <v>-3.0482</v>
+      </c>
+      <c r="M67" s="5" t="n">
+        <v>-4.237</v>
       </c>
       <c r="N67" t="n">
+        <v>102641</v>
+      </c>
+      <c r="O67" t="n">
         <v>98292.09</v>
-      </c>
-      <c r="O67" t="n">
-        <v>102885.07</v>
       </c>
     </row>
     <row r="68">
@@ -6406,7 +6389,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -6415,12 +6398,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -6430,27 +6413,30 @@
         <v>6982.4</v>
       </c>
       <c r="H68" t="n">
-        <v>6991.93</v>
+        <v>6992.85</v>
       </c>
       <c r="I68" t="n">
-        <v>6964.29</v>
+        <v>6962.54</v>
+      </c>
+      <c r="J68" t="n">
+        <v>6947.27</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v>-1.39</v>
+        <v>3.3617</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>4.6728</v>
       </c>
       <c r="N68" t="n">
+        <v>98292.09</v>
+      </c>
+      <c r="O68" t="n">
         <v>102885.07</v>
-      </c>
-      <c r="O68" t="n">
-        <v>101454.97</v>
       </c>
     </row>
     <row r="69">
@@ -6460,7 +6446,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -6469,12 +6455,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -6484,10 +6470,10 @@
         <v>6982.4</v>
       </c>
       <c r="H69" t="n">
-        <v>6986.84</v>
+        <v>6991.93</v>
       </c>
       <c r="I69" t="n">
-        <v>6973.96</v>
+        <v>6964.29</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6501,10 +6487,10 @@
         <v>-1.39</v>
       </c>
       <c r="N69" t="n">
+        <v>102885.07</v>
+      </c>
+      <c r="O69" t="n">
         <v>101454.97</v>
-      </c>
-      <c r="O69" t="n">
-        <v>100044.75</v>
       </c>
     </row>
     <row r="70">
@@ -6514,94 +6500,91 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H70" t="n">
-        <v>6770.77</v>
+        <v>6986.84</v>
       </c>
       <c r="I70" t="n">
-        <v>6839.3</v>
-      </c>
-      <c r="J70" t="n">
-        <v>6769.03</v>
+        <v>6973.96</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-1.0736</v>
+        <v>-1</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>-1.4924</v>
+        <v>-1.39</v>
       </c>
       <c r="N70" t="n">
+        <v>101454.97</v>
+      </c>
+      <c r="O70" t="n">
         <v>100044.75</v>
-      </c>
-      <c r="O70" t="n">
-        <v>98551.73</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>86.081</v>
+        <v>6794.4</v>
       </c>
       <c r="H71" t="n">
-        <v>88.001</v>
+        <v>6770.77</v>
       </c>
       <c r="I71" t="n">
-        <v>82.43300000000001</v>
+        <v>6839.3</v>
       </c>
       <c r="J71" t="n">
-        <v>88.001</v>
+        <v>6769.03</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6609,16 +6592,16 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-1</v>
+        <v>-1.0736</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>-1.39</v>
+        <v>-1.4924</v>
       </c>
       <c r="N71" t="n">
-        <v>100000</v>
+        <v>100044.75</v>
       </c>
       <c r="O71" t="n">
-        <v>98610</v>
+        <v>98551.73</v>
       </c>
     </row>
     <row r="72">
@@ -6628,117 +6611,117 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>73.84399999999999</v>
+        <v>86.081</v>
       </c>
       <c r="H72" t="n">
-        <v>71.999</v>
+        <v>88.001</v>
       </c>
       <c r="I72" t="n">
-        <v>77.349</v>
+        <v>82.43300000000001</v>
       </c>
       <c r="J72" t="n">
-        <v>77.349</v>
+        <v>88.001</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M72" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N72" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O72" t="n">
         <v>98610</v>
-      </c>
-      <c r="O72" t="n">
-        <v>101214.29</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>2</v>
       </c>
       <c r="G73" t="n">
-        <v>15</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H73" t="n">
-        <v>15.26</v>
+        <v>71.999</v>
       </c>
       <c r="I73" t="n">
-        <v>14.51</v>
+        <v>77.349</v>
       </c>
       <c r="J73" t="n">
-        <v>15.26</v>
+        <v>77.349</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M73" s="5" t="n">
-        <v>-1.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N73" t="n">
-        <v>100000</v>
+        <v>98610</v>
       </c>
       <c r="O73" t="n">
-        <v>98610</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -6751,28 +6734,28 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" t="n">
-        <v>20.89</v>
+        <v>15</v>
       </c>
       <c r="H74" t="n">
-        <v>21.07</v>
+        <v>15.26</v>
       </c>
       <c r="I74" t="n">
-        <v>20.55</v>
+        <v>14.51</v>
       </c>
       <c r="J74" t="n">
-        <v>21.08</v>
+        <v>15.26</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6780,22 +6763,22 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-1.0556</v>
+        <v>-1</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>-1.4672</v>
+        <v>-1.39</v>
       </c>
       <c r="N74" t="n">
         <v>100000</v>
       </c>
       <c r="O74" t="n">
-        <v>98532.78</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -6808,28 +6791,28 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.8614000000000001</v>
+        <v>20.89</v>
       </c>
       <c r="H75" t="n">
-        <v>0.8637</v>
+        <v>21.07</v>
       </c>
       <c r="I75" t="n">
-        <v>0.857</v>
+        <v>20.55</v>
       </c>
       <c r="J75" t="n">
-        <v>0.8637</v>
+        <v>21.08</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6837,16 +6820,16 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>-1.39</v>
+        <v>-1.4672</v>
       </c>
       <c r="N75" t="n">
         <v>100000</v>
       </c>
       <c r="O75" t="n">
-        <v>98610</v>
+        <v>98532.78</v>
       </c>
     </row>
     <row r="76">
@@ -6856,7 +6839,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -6865,12 +6848,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -6880,13 +6863,13 @@
         <v>0.8614000000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8658</v>
+        <v>0.8637</v>
       </c>
       <c r="I76" t="n">
-        <v>0.853</v>
+        <v>0.857</v>
       </c>
       <c r="J76" t="n">
-        <v>0.8658</v>
+        <v>0.8637</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6900,10 +6883,10 @@
         <v>-1.39</v>
       </c>
       <c r="N76" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O76" t="n">
         <v>98610</v>
-      </c>
-      <c r="O76" t="n">
-        <v>97239.32000000001</v>
       </c>
     </row>
     <row r="77">
@@ -6913,111 +6896,111 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.8467</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>0.8436</v>
+        <v>0.8658</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8526</v>
+        <v>0.853</v>
       </c>
       <c r="J77" t="n">
-        <v>0.8498</v>
+        <v>0.8658</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
-      </c>
-      <c r="M77" s="2" t="n">
-        <v>1.39</v>
+        <v>-1</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N77" t="n">
+        <v>98610</v>
+      </c>
+      <c r="O77" t="n">
         <v>97239.32000000001</v>
-      </c>
-      <c r="O77" t="n">
-        <v>98590.95</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>116.5</v>
+        <v>0.8467</v>
       </c>
       <c r="H78" t="n">
-        <v>116.79</v>
+        <v>0.8436</v>
       </c>
       <c r="I78" t="n">
-        <v>115.95</v>
+        <v>0.8526</v>
       </c>
       <c r="J78" t="n">
-        <v>116.79</v>
+        <v>0.8498</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M78" s="5" t="n">
-        <v>-1.39</v>
+        <v>1</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>1.39</v>
       </c>
       <c r="N78" t="n">
-        <v>100000</v>
+        <v>97239.32000000001</v>
       </c>
       <c r="O78" t="n">
-        <v>98610</v>
+        <v>98590.95</v>
       </c>
     </row>
     <row r="79">
@@ -7027,7 +7010,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -7036,45 +7019,45 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>118.02</v>
+        <v>116.5</v>
       </c>
       <c r="H79" t="n">
-        <v>118.16</v>
+        <v>116.79</v>
       </c>
       <c r="I79" t="n">
-        <v>117.75</v>
+        <v>115.95</v>
       </c>
       <c r="J79" t="n">
-        <v>117.75</v>
+        <v>116.79</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M79" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M79" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N79" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O79" t="n">
         <v>98610</v>
-      </c>
-      <c r="O79" t="n">
-        <v>101214.29</v>
       </c>
     </row>
     <row r="80">
@@ -7084,7 +7067,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -7093,99 +7076,99 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>118.08</v>
+        <v>118.02</v>
       </c>
       <c r="H80" t="n">
         <v>118.16</v>
       </c>
       <c r="I80" t="n">
-        <v>117.93</v>
+        <v>117.75</v>
+      </c>
+      <c r="J80" t="n">
+        <v>117.75</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M80" s="5" t="n">
-        <v>-1.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N80" t="n">
+        <v>98610</v>
+      </c>
+      <c r="O80" t="n">
         <v>101214.29</v>
-      </c>
-      <c r="O80" t="n">
-        <v>99807.41</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>97.81399999999999</v>
+        <v>118.08</v>
       </c>
       <c r="H81" t="n">
-        <v>97.569</v>
+        <v>118.16</v>
       </c>
       <c r="I81" t="n">
-        <v>98.279</v>
-      </c>
-      <c r="J81" t="n">
-        <v>98.279</v>
+        <v>117.93</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M81" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M81" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N81" t="n">
-        <v>100000</v>
+        <v>101214.29</v>
       </c>
       <c r="O81" t="n">
-        <v>102641</v>
+        <v>99807.41</v>
       </c>
     </row>
     <row r="82">
@@ -7195,7 +7178,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -7204,28 +7187,28 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>97.714</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>97.46899999999999</v>
+        <v>97.569</v>
       </c>
       <c r="I82" t="n">
-        <v>98.18000000000001</v>
+        <v>98.279</v>
       </c>
       <c r="J82" t="n">
-        <v>98.18000000000001</v>
+        <v>98.279</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -7239,10 +7222,10 @@
         <v>2.641</v>
       </c>
       <c r="N82" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O82" t="n">
         <v>102641</v>
-      </c>
-      <c r="O82" t="n">
-        <v>105351.75</v>
       </c>
     </row>
     <row r="83">
@@ -7252,37 +7235,37 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G83" t="n">
-        <v>99.376</v>
+        <v>97.714</v>
       </c>
       <c r="H83" t="n">
-        <v>99.571</v>
+        <v>97.46899999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>99.006</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>99.006</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7296,10 +7279,10 @@
         <v>2.641</v>
       </c>
       <c r="N83" t="n">
+        <v>102641</v>
+      </c>
+      <c r="O83" t="n">
         <v>105351.75</v>
-      </c>
-      <c r="O83" t="n">
-        <v>108134.09</v>
       </c>
     </row>
     <row r="84">
@@ -7309,7 +7292,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -7318,45 +7301,45 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>3</v>
       </c>
       <c r="G84" t="n">
-        <v>99.246</v>
+        <v>99.376</v>
       </c>
       <c r="H84" t="n">
-        <v>99.501</v>
+        <v>99.571</v>
       </c>
       <c r="I84" t="n">
-        <v>98.761</v>
+        <v>99.006</v>
       </c>
       <c r="J84" t="n">
-        <v>99.501</v>
+        <v>99.006</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M84" s="5" t="n">
-        <v>-1.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N84" t="n">
+        <v>105351.75</v>
+      </c>
+      <c r="O84" t="n">
         <v>108134.09</v>
-      </c>
-      <c r="O84" t="n">
-        <v>106631.02</v>
       </c>
     </row>
     <row r="85">
@@ -7366,7 +7349,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -7375,45 +7358,45 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G85" t="n">
-        <v>100.066</v>
+        <v>99.246</v>
       </c>
       <c r="H85" t="n">
-        <v>100.201</v>
+        <v>99.501</v>
       </c>
       <c r="I85" t="n">
-        <v>99.809</v>
+        <v>98.761</v>
       </c>
       <c r="J85" t="n">
-        <v>99.809</v>
+        <v>99.501</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M85" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M85" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N85" t="n">
+        <v>108134.09</v>
+      </c>
+      <c r="O85" t="n">
         <v>106631.02</v>
-      </c>
-      <c r="O85" t="n">
-        <v>109447.15</v>
       </c>
     </row>
     <row r="86">
@@ -7423,7 +7406,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -7432,12 +7415,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -7447,13 +7430,13 @@
         <v>100.066</v>
       </c>
       <c r="H86" t="n">
-        <v>100.316</v>
+        <v>100.201</v>
       </c>
       <c r="I86" t="n">
-        <v>99.59099999999999</v>
+        <v>99.809</v>
       </c>
       <c r="J86" t="n">
-        <v>99.45999999999999</v>
+        <v>99.809</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7461,16 +7444,16 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.424</v>
+        <v>1.9</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3.3694</v>
+        <v>2.641</v>
       </c>
       <c r="N86" t="n">
+        <v>106631.02</v>
+      </c>
+      <c r="O86" t="n">
         <v>109447.15</v>
-      </c>
-      <c r="O86" t="n">
-        <v>113134.82</v>
       </c>
     </row>
     <row r="87">
@@ -7480,7 +7463,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -7489,12 +7472,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -7504,30 +7487,30 @@
         <v>100.066</v>
       </c>
       <c r="H87" t="n">
-        <v>100.361</v>
+        <v>100.316</v>
       </c>
       <c r="I87" t="n">
-        <v>99.505</v>
+        <v>99.59099999999999</v>
       </c>
       <c r="J87" t="n">
-        <v>100.361</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M87" s="5" t="n">
-        <v>-1.39</v>
+        <v>2.424</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>3.3694</v>
       </c>
       <c r="N87" t="n">
+        <v>109447.15</v>
+      </c>
+      <c r="O87" t="n">
         <v>113134.82</v>
-      </c>
-      <c r="O87" t="n">
-        <v>111562.24</v>
       </c>
     </row>
     <row r="88">
@@ -7537,7 +7520,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -7546,28 +7529,28 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>100.621</v>
+        <v>100.066</v>
       </c>
       <c r="H88" t="n">
-        <v>100.911</v>
+        <v>100.361</v>
       </c>
       <c r="I88" t="n">
-        <v>100.07</v>
+        <v>99.505</v>
       </c>
       <c r="J88" t="n">
-        <v>100.911</v>
+        <v>100.361</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7581,10 +7564,10 @@
         <v>-1.39</v>
       </c>
       <c r="N88" t="n">
+        <v>113134.82</v>
+      </c>
+      <c r="O88" t="n">
         <v>111562.24</v>
-      </c>
-      <c r="O88" t="n">
-        <v>110011.53</v>
       </c>
     </row>
     <row r="89">
@@ -7594,7 +7577,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -7603,55 +7586,55 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>101.411</v>
+        <v>100.621</v>
       </c>
       <c r="H89" t="n">
-        <v>101.526</v>
+        <v>100.911</v>
       </c>
       <c r="I89" t="n">
-        <v>101.192</v>
+        <v>100.07</v>
       </c>
       <c r="J89" t="n">
-        <v>101.192</v>
+        <v>100.911</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M89" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N89" t="n">
+        <v>111562.24</v>
+      </c>
+      <c r="O89" t="n">
         <v>110011.53</v>
-      </c>
-      <c r="O89" t="n">
-        <v>112916.93</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -7660,28 +7643,28 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>121.72</v>
+        <v>101.411</v>
       </c>
       <c r="H90" t="n">
-        <v>123.03</v>
+        <v>101.526</v>
       </c>
       <c r="I90" t="n">
-        <v>119.23</v>
+        <v>101.192</v>
       </c>
       <c r="J90" t="n">
-        <v>113.29</v>
+        <v>101.192</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7689,26 +7672,26 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>6.4351</v>
+        <v>1.9</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>8.944800000000001</v>
+        <v>2.641</v>
       </c>
       <c r="N90" t="n">
-        <v>100000</v>
+        <v>110011.53</v>
       </c>
       <c r="O90" t="n">
-        <v>108944.81</v>
+        <v>112916.93</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -7717,28 +7700,28 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>130.16</v>
+        <v>101.411</v>
       </c>
       <c r="H91" t="n">
-        <v>130.94</v>
+        <v>101.491</v>
       </c>
       <c r="I91" t="n">
-        <v>128.68</v>
+        <v>101.259</v>
       </c>
       <c r="J91" t="n">
-        <v>128.68</v>
+        <v>101.259</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7752,9 +7735,123 @@
         <v>2.641</v>
       </c>
       <c r="N91" t="n">
+        <v>112916.93</v>
+      </c>
+      <c r="O91" t="n">
+        <v>115899.07</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H92" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="I92" t="n">
+        <v>119.23</v>
+      </c>
+      <c r="J92" t="n">
+        <v>113.29</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>6.4351</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>8.944800000000001</v>
+      </c>
+      <c r="N92" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O92" t="n">
         <v>108944.81</v>
       </c>
-      <c r="O91" t="n">
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>2</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>130.16</v>
+      </c>
+      <c r="H93" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="I93" t="n">
+        <v>128.68</v>
+      </c>
+      <c r="J93" t="n">
+        <v>128.68</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="N93" t="n">
+        <v>108944.81</v>
+      </c>
+      <c r="O93" t="n">
         <v>111822.04</v>
       </c>
     </row>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -1023,7 +1023,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>German_Long_Bund</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1034,20 +1034,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1059,34 +1059,34 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2.64</v>
+        <v>3.89</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>102641</v>
+        <v>103887.36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>German_Long_Bund</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1119,31 +1119,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1152,16 +1152,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1.21</v>
+        <v>2.64</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>101214.29</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="15">
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1271,11 +1271,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1316,11 +1316,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1361,11 +1361,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1406,11 +1406,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1451,11 +1451,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-29); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-30 20:33 UTC.</t>
+          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-30); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-31 15:45 UTC.</t>
         </is>
       </c>
     </row>
@@ -5794,6 +5794,14 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
       <c r="G57" t="n">
         <v>2.69</v>
       </c>
@@ -5803,16 +5811,25 @@
       <c r="I57" t="n">
         <v>2.737</v>
       </c>
+      <c r="J57" t="n">
+        <v>2.737</v>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N57" t="n">
         <v>101214.29</v>
       </c>
       <c r="O57" t="n">
-        <v>101214.29</v>
+        <v>103887.36</v>
       </c>
     </row>
     <row r="58">

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-30); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-31 15:45 UTC.</t>
+          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-30); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-31 17:02 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1271,11 +1271,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1316,11 +1316,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1361,11 +1361,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1406,11 +1406,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1451,11 +1451,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-30); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-31 17:02 UTC.</t>
+          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 19:43 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 19:43 UTC.</t>
+          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 22:59 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 22:59 UTC.</t>
+          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-02 00:09 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1271,11 +1271,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1316,11 +1316,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1361,11 +1361,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1406,11 +1406,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1451,11 +1451,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-02 00:09 UTC.</t>
+          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-04); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-05 13:32 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>77.8</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>75</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>100</v>
@@ -1167,22 +1167,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -1191,10 +1191,10 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1215,31 +1215,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CME_SOFR_Futures_3M</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>72</v>
+        <v>153</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1250,17 +1250,20 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="4" t="n">
-        <v>0</v>
+      <c r="L16" t="n">
+        <v>50</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>1.21</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>100000</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Global_X_Uranium_ETF</t>
+          <t>CME_SOFR_Futures_3M</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1271,11 +1274,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1305,7 +1308,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Japanese_10_Year_Bond_Futures</t>
+          <t>Global_X_Uranium_ETF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1316,11 +1319,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1350,7 +1353,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NY_Crude_Oil_Futures</t>
+          <t>Japanese_10_Year_Bond_Futures</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1361,11 +1364,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1395,22 +1398,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Proshares_VIX_Short_Term_Futures_ETF</t>
+          <t>NY_Crude_Oil_Futures</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1440,22 +1443,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>US_10_Year_T_Note_Futures</t>
+          <t>Proshares_VIX_Short_Term_Futures_ETF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1485,34 +1488,34 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>US_10_Year_T_Note_Futures</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1520,47 +1523,44 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>-0.19</v>
+      <c r="M22" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>99807.41</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1569,19 +1569,19 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-1.39</v>
+        <v>-0.19</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>98610</v>
+        <v>99807.41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-04); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-05 13:32 UTC.</t>
+          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-06); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-07 13:34 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5154,11 +5154,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5167,51 +5167,34 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>3</v>
+          <t>2026-08-06</t>
+        </is>
       </c>
       <c r="G46" t="n">
-        <v>0.006417</v>
+        <v>4305.3</v>
       </c>
       <c r="H46" t="n">
-        <v>0.006454</v>
+        <v>4363.8</v>
       </c>
       <c r="I46" t="n">
-        <v>0.006347</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.006454</v>
+        <v>4194.2</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v>-1.39</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N46" t="n">
-        <v>100000</v>
+        <v>127258.49</v>
       </c>
       <c r="O46" t="n">
-        <v>98610</v>
+        <v>127258.49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -5224,29 +5207,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>239.06</v>
+        <v>0.006417</v>
       </c>
       <c r="H47" t="n">
-        <v>239.73</v>
+        <v>0.006454</v>
       </c>
       <c r="I47" t="n">
-        <v>237.79</v>
+        <v>0.006347</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.006454</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -5269,7 +5255,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5278,45 +5264,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>251.58</v>
+        <v>239.06</v>
       </c>
       <c r="H48" t="n">
-        <v>251.91</v>
+        <v>239.73</v>
       </c>
       <c r="I48" t="n">
-        <v>250.95</v>
-      </c>
-      <c r="J48" t="n">
-        <v>250.95</v>
+        <v>237.79</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N48" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O48" t="n">
         <v>98610</v>
-      </c>
-      <c r="O48" t="n">
-        <v>101214.29</v>
       </c>
     </row>
     <row r="49">
@@ -5326,7 +5309,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5335,28 +5318,28 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>255.38</v>
+        <v>251.58</v>
       </c>
       <c r="H49" t="n">
-        <v>256.63</v>
+        <v>251.91</v>
       </c>
       <c r="I49" t="n">
-        <v>253</v>
+        <v>250.95</v>
       </c>
       <c r="J49" t="n">
-        <v>253</v>
+        <v>250.95</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -5370,10 +5353,10 @@
         <v>2.641</v>
       </c>
       <c r="N49" t="n">
+        <v>98610</v>
+      </c>
+      <c r="O49" t="n">
         <v>101214.29</v>
-      </c>
-      <c r="O49" t="n">
-        <v>103887.36</v>
       </c>
     </row>
     <row r="50">
@@ -5383,37 +5366,37 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>235.2</v>
+        <v>255.38</v>
       </c>
       <c r="H50" t="n">
-        <v>234.36</v>
+        <v>256.63</v>
       </c>
       <c r="I50" t="n">
-        <v>236.8</v>
+        <v>253</v>
       </c>
       <c r="J50" t="n">
-        <v>236.8</v>
+        <v>253</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -5427,20 +5410,20 @@
         <v>2.641</v>
       </c>
       <c r="N50" t="n">
+        <v>101214.29</v>
+      </c>
+      <c r="O50" t="n">
         <v>103887.36</v>
-      </c>
-      <c r="O50" t="n">
-        <v>106631.02</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5449,45 +5432,45 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>5.7714</v>
+        <v>235.2</v>
       </c>
       <c r="H51" t="n">
-        <v>5.6849</v>
+        <v>234.36</v>
       </c>
       <c r="I51" t="n">
-        <v>5.9357</v>
+        <v>236.8</v>
       </c>
       <c r="J51" t="n">
-        <v>5.6849</v>
+        <v>236.8</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v>-1.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N51" t="n">
-        <v>100000</v>
+        <v>103887.36</v>
       </c>
       <c r="O51" t="n">
-        <v>98610</v>
+        <v>106631.02</v>
       </c>
     </row>
     <row r="52">
@@ -5497,7 +5480,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5506,12 +5489,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5521,13 +5504,13 @@
         <v>5.7714</v>
       </c>
       <c r="H52" t="n">
-        <v>5.6774</v>
+        <v>5.6849</v>
       </c>
       <c r="I52" t="n">
-        <v>5.95</v>
+        <v>5.9357</v>
       </c>
       <c r="J52" t="n">
-        <v>5.6774</v>
+        <v>5.6849</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -5541,10 +5524,10 @@
         <v>-1.39</v>
       </c>
       <c r="N52" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O52" t="n">
         <v>98610</v>
-      </c>
-      <c r="O52" t="n">
-        <v>97239.32000000001</v>
       </c>
     </row>
     <row r="53">
@@ -5554,7 +5537,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5563,45 +5546,45 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>5.3133</v>
+        <v>5.7714</v>
       </c>
       <c r="H53" t="n">
-        <v>5.2459</v>
+        <v>5.6774</v>
       </c>
       <c r="I53" t="n">
-        <v>5.4414</v>
+        <v>5.95</v>
       </c>
       <c r="J53" t="n">
-        <v>5.4414</v>
+        <v>5.6774</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M53" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N53" t="n">
+        <v>98610</v>
+      </c>
+      <c r="O53" t="n">
         <v>97239.32000000001</v>
-      </c>
-      <c r="O53" t="n">
-        <v>99807.41</v>
       </c>
     </row>
     <row r="54">
@@ -5611,64 +5594,64 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>6.0956</v>
+        <v>5.3133</v>
       </c>
       <c r="H54" t="n">
-        <v>6.1481</v>
+        <v>5.2459</v>
       </c>
       <c r="I54" t="n">
-        <v>5.9959</v>
+        <v>5.4414</v>
       </c>
       <c r="J54" t="n">
-        <v>6.1481</v>
+        <v>5.4414</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>-1.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N54" t="n">
+        <v>97239.32000000001</v>
+      </c>
+      <c r="O54" t="n">
         <v>99807.41</v>
-      </c>
-      <c r="O54" t="n">
-        <v>98420.09</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -5677,28 +5660,28 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G55" t="n">
-        <v>3.305</v>
+        <v>6.0956</v>
       </c>
       <c r="H55" t="n">
-        <v>3.354</v>
+        <v>6.1481</v>
       </c>
       <c r="I55" t="n">
-        <v>3.212</v>
+        <v>5.9959</v>
       </c>
       <c r="J55" t="n">
-        <v>3.354</v>
+        <v>6.1481</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -5712,10 +5695,10 @@
         <v>-1.39</v>
       </c>
       <c r="N55" t="n">
-        <v>100000</v>
+        <v>99807.41</v>
       </c>
       <c r="O55" t="n">
-        <v>98610</v>
+        <v>98420.09</v>
       </c>
     </row>
     <row r="56">
@@ -5725,7 +5708,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -5734,12 +5717,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -5749,30 +5732,30 @@
         <v>3.305</v>
       </c>
       <c r="H56" t="n">
-        <v>3.356</v>
+        <v>3.354</v>
       </c>
       <c r="I56" t="n">
-        <v>3.208</v>
+        <v>3.212</v>
       </c>
       <c r="J56" t="n">
-        <v>3.208</v>
+        <v>3.354</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M56" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N56" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O56" t="n">
         <v>98610</v>
-      </c>
-      <c r="O56" t="n">
-        <v>101214.29</v>
       </c>
     </row>
     <row r="57">
@@ -5782,37 +5765,37 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>2.69</v>
+        <v>3.305</v>
       </c>
       <c r="H57" t="n">
-        <v>2.665</v>
+        <v>3.356</v>
       </c>
       <c r="I57" t="n">
-        <v>2.737</v>
+        <v>3.208</v>
       </c>
       <c r="J57" t="n">
-        <v>2.737</v>
+        <v>3.208</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5826,20 +5809,20 @@
         <v>2.641</v>
       </c>
       <c r="N57" t="n">
+        <v>98610</v>
+      </c>
+      <c r="O57" t="n">
         <v>101214.29</v>
-      </c>
-      <c r="O57" t="n">
-        <v>103887.36</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -5848,28 +5831,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H58" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="I58" t="n">
-        <v>1392.7</v>
+        <v>2.737</v>
       </c>
       <c r="J58" t="n">
-        <v>1403</v>
+        <v>2.737</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5877,16 +5860,16 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.5059</v>
+        <v>1.9</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3.4832</v>
+        <v>2.641</v>
       </c>
       <c r="N58" t="n">
-        <v>100000</v>
+        <v>101214.29</v>
       </c>
       <c r="O58" t="n">
-        <v>103483.18</v>
+        <v>103887.36</v>
       </c>
     </row>
     <row r="59">
@@ -5896,7 +5879,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -5905,28 +5888,28 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H59" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="I59" t="n">
-        <v>1181.4</v>
+        <v>1392.7</v>
       </c>
       <c r="J59" t="n">
-        <v>1181.4</v>
+        <v>1403</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5934,56 +5917,56 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.9</v>
+        <v>2.5059</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2.641</v>
+        <v>3.4832</v>
       </c>
       <c r="N59" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O59" t="n">
         <v>103483.18</v>
-      </c>
-      <c r="O59" t="n">
-        <v>106216.17</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H60" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="I60" t="n">
-        <v>2029.3</v>
+        <v>1181.4</v>
       </c>
       <c r="J60" t="n">
-        <v>2029.3</v>
+        <v>1181.4</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5997,10 +5980,10 @@
         <v>2.641</v>
       </c>
       <c r="N60" t="n">
-        <v>100000</v>
+        <v>103483.18</v>
       </c>
       <c r="O60" t="n">
-        <v>102641</v>
+        <v>106216.17</v>
       </c>
     </row>
     <row r="61">
@@ -6010,54 +5993,54 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>1641.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H61" t="n">
-        <v>1621</v>
+        <v>2113.7</v>
       </c>
       <c r="I61" t="n">
-        <v>1680.5</v>
+        <v>2029.3</v>
       </c>
       <c r="J61" t="n">
-        <v>1621</v>
+        <v>2029.3</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v>-1.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N61" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O61" t="n">
         <v>102641</v>
-      </c>
-      <c r="O61" t="n">
-        <v>101214.29</v>
       </c>
     </row>
     <row r="62">
@@ -6067,7 +6050,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6076,45 +6059,45 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>1581.5</v>
+        <v>1641.5</v>
       </c>
       <c r="H62" t="n">
-        <v>1547.6</v>
+        <v>1621</v>
       </c>
       <c r="I62" t="n">
-        <v>1645.9</v>
+        <v>1680.5</v>
       </c>
       <c r="J62" t="n">
-        <v>1645.9</v>
+        <v>1621</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M62" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M62" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N62" t="n">
+        <v>102641</v>
+      </c>
+      <c r="O62" t="n">
         <v>101214.29</v>
-      </c>
-      <c r="O62" t="n">
-        <v>103887.36</v>
       </c>
     </row>
     <row r="63">
@@ -6124,7 +6107,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6133,28 +6116,28 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>1559</v>
+        <v>1581.5</v>
       </c>
       <c r="H63" t="n">
-        <v>1539.5</v>
+        <v>1547.6</v>
       </c>
       <c r="I63" t="n">
-        <v>1596</v>
+        <v>1645.9</v>
       </c>
       <c r="J63" t="n">
-        <v>1596</v>
+        <v>1645.9</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -6168,74 +6151,77 @@
         <v>2.641</v>
       </c>
       <c r="N63" t="n">
+        <v>101214.29</v>
+      </c>
+      <c r="O63" t="n">
         <v>103887.36</v>
-      </c>
-      <c r="O63" t="n">
-        <v>106631.02</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>27907</v>
+        <v>1559</v>
       </c>
       <c r="H64" t="n">
-        <v>27965.76</v>
+        <v>1539.5</v>
       </c>
       <c r="I64" t="n">
-        <v>27795.36</v>
+        <v>1596</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1596</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v>-1.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N64" t="n">
-        <v>100000</v>
+        <v>103887.36</v>
       </c>
       <c r="O64" t="n">
-        <v>98610</v>
+        <v>106631.02</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -6244,51 +6230,34 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>1</v>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="G65" t="n">
-        <v>7206.55</v>
+        <v>1769.6</v>
       </c>
       <c r="H65" t="n">
-        <v>7223.26</v>
+        <v>1798.4</v>
       </c>
       <c r="I65" t="n">
-        <v>7174.8</v>
-      </c>
-      <c r="J65" t="n">
-        <v>7174.8</v>
+        <v>1714.9</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>target_r</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M65" s="2" t="n">
-        <v>2.641</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N65" t="n">
-        <v>100000</v>
+        <v>106631.02</v>
       </c>
       <c r="O65" t="n">
-        <v>102641</v>
+        <v>106631.02</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -6301,51 +6270,48 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>6957.43</v>
+        <v>27907</v>
       </c>
       <c r="H66" t="n">
-        <v>6965.7</v>
+        <v>27965.76</v>
       </c>
       <c r="I66" t="n">
-        <v>6941.72</v>
-      </c>
-      <c r="J66" t="n">
-        <v>6941.72</v>
+        <v>27795.36</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M66" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M66" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N66" t="n">
         <v>100000</v>
       </c>
       <c r="O66" t="n">
-        <v>102641</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -6358,55 +6324,55 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>6982.4</v>
+        <v>29892.8</v>
       </c>
       <c r="H67" t="n">
-        <v>6988.83</v>
+        <v>30074.01</v>
       </c>
       <c r="I67" t="n">
-        <v>6970.18</v>
+        <v>29548.5</v>
       </c>
       <c r="J67" t="n">
-        <v>7002</v>
+        <v>29548.5</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-3.0482</v>
-      </c>
-      <c r="M67" s="5" t="n">
-        <v>-4.237</v>
+        <v>1.9</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N67" t="n">
-        <v>102641</v>
+        <v>98610</v>
       </c>
       <c r="O67" t="n">
-        <v>98292.09</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -6415,28 +6381,28 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>6982.4</v>
+        <v>7206.55</v>
       </c>
       <c r="H68" t="n">
-        <v>6992.85</v>
+        <v>7223.26</v>
       </c>
       <c r="I68" t="n">
-        <v>6962.54</v>
+        <v>7174.8</v>
       </c>
       <c r="J68" t="n">
-        <v>6947.27</v>
+        <v>7174.8</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6444,26 +6410,26 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.3617</v>
+        <v>1.9</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>4.6728</v>
+        <v>2.641</v>
       </c>
       <c r="N68" t="n">
-        <v>98292.09</v>
+        <v>100000</v>
       </c>
       <c r="O68" t="n">
-        <v>102885.07</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -6472,42 +6438,28 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>1</v>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="G69" t="n">
-        <v>6982.4</v>
+        <v>7773</v>
       </c>
       <c r="H69" t="n">
-        <v>6991.93</v>
+        <v>7820.26</v>
       </c>
       <c r="I69" t="n">
-        <v>6964.29</v>
+        <v>7683.21</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M69" s="5" t="n">
-        <v>-1.39</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N69" t="n">
-        <v>102885.07</v>
+        <v>102641</v>
       </c>
       <c r="O69" t="n">
-        <v>101454.97</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="70">
@@ -6517,7 +6469,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -6526,42 +6478,45 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H70" t="n">
-        <v>6986.84</v>
+        <v>6965.7</v>
       </c>
       <c r="I70" t="n">
-        <v>6973.96</v>
+        <v>6941.72</v>
+      </c>
+      <c r="J70" t="n">
+        <v>6941.72</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v>-1.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N70" t="n">
-        <v>101454.97</v>
+        <v>100000</v>
       </c>
       <c r="O70" t="n">
-        <v>100044.75</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="71">
@@ -6571,37 +6526,37 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H71" t="n">
-        <v>6770.77</v>
+        <v>6988.83</v>
       </c>
       <c r="I71" t="n">
-        <v>6839.3</v>
+        <v>6970.18</v>
       </c>
       <c r="J71" t="n">
-        <v>6769.03</v>
+        <v>7002</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6609,26 +6564,26 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-1.0736</v>
+        <v>-3.0482</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>-1.4924</v>
+        <v>-4.237</v>
       </c>
       <c r="N71" t="n">
-        <v>100044.75</v>
+        <v>102641</v>
       </c>
       <c r="O71" t="n">
-        <v>98551.73</v>
+        <v>98292.09</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -6637,112 +6592,109 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H72" t="n">
-        <v>88.001</v>
+        <v>6992.85</v>
       </c>
       <c r="I72" t="n">
-        <v>82.43300000000001</v>
+        <v>6962.54</v>
       </c>
       <c r="J72" t="n">
-        <v>88.001</v>
+        <v>6947.27</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M72" s="5" t="n">
-        <v>-1.39</v>
+        <v>3.3617</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>4.6728</v>
       </c>
       <c r="N72" t="n">
-        <v>100000</v>
+        <v>98292.09</v>
       </c>
       <c r="O72" t="n">
-        <v>98610</v>
+        <v>102885.07</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>73.84399999999999</v>
+        <v>6982.4</v>
       </c>
       <c r="H73" t="n">
-        <v>71.999</v>
+        <v>6991.93</v>
       </c>
       <c r="I73" t="n">
-        <v>77.349</v>
-      </c>
-      <c r="J73" t="n">
-        <v>77.349</v>
+        <v>6964.29</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M73" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M73" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N73" t="n">
-        <v>98610</v>
+        <v>102885.07</v>
       </c>
       <c r="O73" t="n">
-        <v>101214.29</v>
+        <v>101454.97</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -6751,32 +6703,29 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>15</v>
+        <v>6982.4</v>
       </c>
       <c r="H74" t="n">
-        <v>15.26</v>
+        <v>6986.84</v>
       </c>
       <c r="I74" t="n">
-        <v>14.51</v>
-      </c>
-      <c r="J74" t="n">
-        <v>15.26</v>
+        <v>6973.96</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -6786,50 +6735,50 @@
         <v>-1.39</v>
       </c>
       <c r="N74" t="n">
-        <v>100000</v>
+        <v>101454.97</v>
       </c>
       <c r="O74" t="n">
-        <v>98610</v>
+        <v>100044.75</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>20.89</v>
+        <v>6794.4</v>
       </c>
       <c r="H75" t="n">
-        <v>21.07</v>
+        <v>6770.77</v>
       </c>
       <c r="I75" t="n">
-        <v>20.55</v>
+        <v>6839.3</v>
       </c>
       <c r="J75" t="n">
-        <v>21.08</v>
+        <v>6769.03</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6837,22 +6786,22 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-1.0556</v>
+        <v>-1.0736</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>-1.4672</v>
+        <v>-1.4924</v>
       </c>
       <c r="N75" t="n">
-        <v>100000</v>
+        <v>100044.75</v>
       </c>
       <c r="O75" t="n">
-        <v>98532.78</v>
+        <v>98551.73</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -6865,28 +6814,28 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>0.8614000000000001</v>
+        <v>86.081</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8637</v>
+        <v>88.001</v>
       </c>
       <c r="I76" t="n">
-        <v>0.857</v>
+        <v>82.43300000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>0.8637</v>
+        <v>88.001</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6909,7 +6858,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -6917,113 +6866,113 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77" t="n">
-        <v>0.8614000000000001</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>0.8658</v>
+        <v>71.999</v>
       </c>
       <c r="I77" t="n">
-        <v>0.853</v>
+        <v>77.349</v>
       </c>
       <c r="J77" t="n">
-        <v>0.8658</v>
+        <v>77.349</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M77" s="5" t="n">
-        <v>-1.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N77" t="n">
         <v>98610</v>
       </c>
       <c r="O77" t="n">
-        <v>97239.32000000001</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8467</v>
+        <v>15</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8436</v>
+        <v>15.26</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8526</v>
+        <v>14.51</v>
       </c>
       <c r="J78" t="n">
-        <v>0.8498</v>
+        <v>15.26</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
-      </c>
-      <c r="M78" s="2" t="n">
-        <v>1.39</v>
+        <v>-1</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N78" t="n">
-        <v>97239.32000000001</v>
+        <v>100000</v>
       </c>
       <c r="O78" t="n">
-        <v>98590.95</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -7036,28 +6985,28 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>116.5</v>
+        <v>20.89</v>
       </c>
       <c r="H79" t="n">
-        <v>116.79</v>
+        <v>21.07</v>
       </c>
       <c r="I79" t="n">
-        <v>115.95</v>
+        <v>20.55</v>
       </c>
       <c r="J79" t="n">
-        <v>116.79</v>
+        <v>21.08</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -7065,26 +7014,26 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>-1.39</v>
+        <v>-1.4672</v>
       </c>
       <c r="N79" t="n">
         <v>100000</v>
       </c>
       <c r="O79" t="n">
-        <v>98610</v>
+        <v>98532.78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -7093,55 +7042,55 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>118.02</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>118.16</v>
+        <v>0.8637</v>
       </c>
       <c r="I80" t="n">
-        <v>117.75</v>
+        <v>0.857</v>
       </c>
       <c r="J80" t="n">
-        <v>117.75</v>
+        <v>0.8637</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M80" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N80" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O80" t="n">
         <v>98610</v>
-      </c>
-      <c r="O80" t="n">
-        <v>101214.29</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -7150,29 +7099,32 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>118.08</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>118.16</v>
+        <v>0.8658</v>
       </c>
       <c r="I81" t="n">
-        <v>117.93</v>
+        <v>0.853</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.8658</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -7182,20 +7134,20 @@
         <v>-1.39</v>
       </c>
       <c r="N81" t="n">
-        <v>101214.29</v>
+        <v>98610</v>
       </c>
       <c r="O81" t="n">
-        <v>99807.41</v>
+        <v>97239.32000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -7204,112 +7156,112 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>97.81399999999999</v>
+        <v>0.8467</v>
       </c>
       <c r="H82" t="n">
-        <v>97.569</v>
+        <v>0.8436</v>
       </c>
       <c r="I82" t="n">
-        <v>98.279</v>
+        <v>0.8526</v>
       </c>
       <c r="J82" t="n">
-        <v>98.279</v>
+        <v>0.8498</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2.641</v>
+        <v>1.39</v>
       </c>
       <c r="N82" t="n">
-        <v>100000</v>
+        <v>97239.32000000001</v>
       </c>
       <c r="O82" t="n">
-        <v>102641</v>
+        <v>98590.95</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>97.714</v>
+        <v>116.5</v>
       </c>
       <c r="H83" t="n">
-        <v>97.46899999999999</v>
+        <v>116.79</v>
       </c>
       <c r="I83" t="n">
-        <v>98.18000000000001</v>
+        <v>115.95</v>
       </c>
       <c r="J83" t="n">
-        <v>98.18000000000001</v>
+        <v>116.79</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N83" t="n">
-        <v>102641</v>
+        <v>100000</v>
       </c>
       <c r="O83" t="n">
-        <v>105351.75</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -7318,28 +7270,28 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>99.376</v>
+        <v>118.02</v>
       </c>
       <c r="H84" t="n">
-        <v>99.571</v>
+        <v>118.16</v>
       </c>
       <c r="I84" t="n">
-        <v>99.006</v>
+        <v>117.75</v>
       </c>
       <c r="J84" t="n">
-        <v>99.006</v>
+        <v>117.75</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7353,20 +7305,20 @@
         <v>2.641</v>
       </c>
       <c r="N84" t="n">
-        <v>105351.75</v>
+        <v>98610</v>
       </c>
       <c r="O84" t="n">
-        <v>108134.09</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -7375,32 +7327,29 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>99.246</v>
+        <v>118.08</v>
       </c>
       <c r="H85" t="n">
-        <v>99.501</v>
+        <v>118.16</v>
       </c>
       <c r="I85" t="n">
-        <v>98.761</v>
-      </c>
-      <c r="J85" t="n">
-        <v>99.501</v>
+        <v>117.93</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -7410,10 +7359,10 @@
         <v>-1.39</v>
       </c>
       <c r="N85" t="n">
-        <v>108134.09</v>
+        <v>101214.29</v>
       </c>
       <c r="O85" t="n">
-        <v>106631.02</v>
+        <v>99807.41</v>
       </c>
     </row>
     <row r="86">
@@ -7423,37 +7372,37 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>100.066</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>100.201</v>
+        <v>97.569</v>
       </c>
       <c r="I86" t="n">
-        <v>99.809</v>
+        <v>98.279</v>
       </c>
       <c r="J86" t="n">
-        <v>99.809</v>
+        <v>98.279</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7467,10 +7416,10 @@
         <v>2.641</v>
       </c>
       <c r="N86" t="n">
-        <v>106631.02</v>
+        <v>100000</v>
       </c>
       <c r="O86" t="n">
-        <v>109447.15</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="87">
@@ -7480,37 +7429,37 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G87" t="n">
-        <v>100.066</v>
+        <v>97.714</v>
       </c>
       <c r="H87" t="n">
-        <v>100.316</v>
+        <v>97.46899999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>99.59099999999999</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>99.45999999999999</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7518,16 +7467,16 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.424</v>
+        <v>1.9</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>3.3694</v>
+        <v>2.641</v>
       </c>
       <c r="N87" t="n">
-        <v>109447.15</v>
+        <v>102641</v>
       </c>
       <c r="O87" t="n">
-        <v>113134.82</v>
+        <v>105351.75</v>
       </c>
     </row>
     <row r="88">
@@ -7537,7 +7486,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -7546,45 +7495,45 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G88" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H88" t="n">
-        <v>100.361</v>
+        <v>99.571</v>
       </c>
       <c r="I88" t="n">
-        <v>99.505</v>
+        <v>99.006</v>
       </c>
       <c r="J88" t="n">
-        <v>100.361</v>
+        <v>99.006</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M88" s="5" t="n">
-        <v>-1.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N88" t="n">
-        <v>113134.82</v>
+        <v>105351.75</v>
       </c>
       <c r="O88" t="n">
-        <v>111562.24</v>
+        <v>108134.09</v>
       </c>
     </row>
     <row r="89">
@@ -7594,7 +7543,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -7603,28 +7552,28 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G89" t="n">
-        <v>100.621</v>
+        <v>99.246</v>
       </c>
       <c r="H89" t="n">
-        <v>100.911</v>
+        <v>99.501</v>
       </c>
       <c r="I89" t="n">
-        <v>100.07</v>
+        <v>98.761</v>
       </c>
       <c r="J89" t="n">
-        <v>100.911</v>
+        <v>99.501</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7638,10 +7587,10 @@
         <v>-1.39</v>
       </c>
       <c r="N89" t="n">
-        <v>111562.24</v>
+        <v>108134.09</v>
       </c>
       <c r="O89" t="n">
-        <v>110011.53</v>
+        <v>106631.02</v>
       </c>
     </row>
     <row r="90">
@@ -7651,7 +7600,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -7660,28 +7609,28 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H90" t="n">
-        <v>101.526</v>
+        <v>100.201</v>
       </c>
       <c r="I90" t="n">
-        <v>101.192</v>
+        <v>99.809</v>
       </c>
       <c r="J90" t="n">
-        <v>101.192</v>
+        <v>99.809</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7695,10 +7644,10 @@
         <v>2.641</v>
       </c>
       <c r="N90" t="n">
-        <v>110011.53</v>
+        <v>106631.02</v>
       </c>
       <c r="O90" t="n">
-        <v>112916.93</v>
+        <v>109447.15</v>
       </c>
     </row>
     <row r="91">
@@ -7708,7 +7657,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -7717,28 +7666,28 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H91" t="n">
-        <v>101.491</v>
+        <v>100.316</v>
       </c>
       <c r="I91" t="n">
-        <v>101.259</v>
+        <v>99.59099999999999</v>
       </c>
       <c r="J91" t="n">
-        <v>101.259</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7746,26 +7695,26 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.9</v>
+        <v>2.424</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2.641</v>
+        <v>3.3694</v>
       </c>
       <c r="N91" t="n">
-        <v>112916.93</v>
+        <v>109447.15</v>
       </c>
       <c r="O91" t="n">
-        <v>115899.07</v>
+        <v>113134.82</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -7774,101 +7723,329 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F92" t="n">
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>121.72</v>
+        <v>100.066</v>
       </c>
       <c r="H92" t="n">
-        <v>123.03</v>
+        <v>100.361</v>
       </c>
       <c r="I92" t="n">
-        <v>119.23</v>
+        <v>99.505</v>
       </c>
       <c r="J92" t="n">
-        <v>113.29</v>
+        <v>100.361</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>6.4351</v>
-      </c>
-      <c r="M92" s="2" t="n">
-        <v>8.944800000000001</v>
+        <v>-1</v>
+      </c>
+      <c r="M92" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N92" t="n">
-        <v>100000</v>
+        <v>113134.82</v>
       </c>
       <c r="O92" t="n">
-        <v>108944.81</v>
+        <v>111562.24</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>8</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" t="n">
+        <v>100.621</v>
+      </c>
+      <c r="H93" t="n">
+        <v>100.911</v>
+      </c>
+      <c r="I93" t="n">
+        <v>100.07</v>
+      </c>
+      <c r="J93" t="n">
+        <v>100.911</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M93" s="5" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="N93" t="n">
+        <v>111562.24</v>
+      </c>
+      <c r="O93" t="n">
+        <v>110011.53</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>9</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H94" t="n">
+        <v>101.526</v>
+      </c>
+      <c r="I94" t="n">
+        <v>101.192</v>
+      </c>
+      <c r="J94" t="n">
+        <v>101.192</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="N94" t="n">
+        <v>110011.53</v>
+      </c>
+      <c r="O94" t="n">
+        <v>112916.93</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>10</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H95" t="n">
+        <v>101.491</v>
+      </c>
+      <c r="I95" t="n">
+        <v>101.259</v>
+      </c>
+      <c r="J95" t="n">
+        <v>101.259</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="N95" t="n">
+        <v>112916.93</v>
+      </c>
+      <c r="O95" t="n">
+        <v>115899.07</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B93" t="n">
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H96" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="I96" t="n">
+        <v>119.23</v>
+      </c>
+      <c r="J96" t="n">
+        <v>113.29</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>6.4351</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>8.944800000000001</v>
+      </c>
+      <c r="N96" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O96" t="n">
+        <v>108944.81</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
         <v>2</v>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="F93" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" t="n">
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="n">
         <v>130.16</v>
       </c>
-      <c r="H93" t="n">
+      <c r="H97" t="n">
         <v>130.94</v>
       </c>
-      <c r="I93" t="n">
+      <c r="I97" t="n">
         <v>128.68</v>
       </c>
-      <c r="J93" t="n">
+      <c r="J97" t="n">
         <v>128.68</v>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>target_r</t>
         </is>
       </c>
-      <c r="L93" t="n">
+      <c r="L97" t="n">
         <v>1.9</v>
       </c>
-      <c r="M93" s="2" t="n">
+      <c r="M97" s="2" t="n">
         <v>2.641</v>
       </c>
-      <c r="N93" t="n">
+      <c r="N97" t="n">
         <v>108944.81</v>
       </c>
-      <c r="O93" t="n">
+      <c r="O97" t="n">
         <v>111822.04</v>
       </c>
     </row>

--- a/output/quickfix_all_markets_daily.xlsx
+++ b/output/quickfix_all_markets_daily.xlsx
@@ -554,20 +554,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
         <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -576,16 +576,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>77.8</v>
+        <v>70</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>27.26</v>
+        <v>25.49</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>127258.49</v>
+        <v>125489.6</v>
       </c>
     </row>
     <row r="3">
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>100</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
@@ -1274,11 +1274,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1319,11 +1319,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1364,11 +1364,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1409,11 +1409,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1454,11 +1454,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1499,11 +1499,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F23" t="n">
         <v>3</v>
@@ -1592,11 +1592,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>25</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-06); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-07 13:34 UTC.</t>
+          <t>quickfix daily (target = 1.9R, or an opposite reversal nearer than 1.9R), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-07); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-08 17:31 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5170,6 +5170,14 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
       <c r="G46" t="n">
         <v>4305.3</v>
       </c>
@@ -5179,16 +5187,25 @@
       <c r="I46" t="n">
         <v>4194.2</v>
       </c>
+      <c r="J46" t="n">
+        <v>4363.8</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N46" t="n">
         <v>127258.49</v>
       </c>
       <c r="O46" t="n">
-        <v>127258.49</v>
+        <v>125489.6</v>
       </c>
     </row>
     <row r="47">
@@ -5704,11 +5721,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -5717,45 +5734,28 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1</v>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G56" t="n">
-        <v>3.305</v>
+        <v>6.7286</v>
       </c>
       <c r="H56" t="n">
-        <v>3.354</v>
+        <v>6.7656</v>
       </c>
       <c r="I56" t="n">
-        <v>3.212</v>
-      </c>
-      <c r="J56" t="n">
-        <v>3.354</v>
+        <v>6.6583</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v>-1.39</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N56" t="n">
-        <v>100000</v>
+        <v>98420.09</v>
       </c>
       <c r="O56" t="n">
-        <v>98610</v>
+        <v>98420.09</v>
       </c>
     </row>
     <row r="57">
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -5774,12 +5774,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -5789,30 +5789,30 @@
         <v>3.305</v>
       </c>
       <c r="H57" t="n">
-        <v>3.356</v>
+        <v>3.354</v>
       </c>
       <c r="I57" t="n">
-        <v>3.208</v>
+        <v>3.212</v>
       </c>
       <c r="J57" t="n">
-        <v>3.208</v>
+        <v>3.354</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M57" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N57" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O57" t="n">
         <v>98610</v>
-      </c>
-      <c r="O57" t="n">
-        <v>101214.29</v>
       </c>
     </row>
     <row r="58">
@@ -5822,37 +5822,37 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>2.69</v>
+        <v>3.305</v>
       </c>
       <c r="H58" t="n">
-        <v>2.665</v>
+        <v>3.356</v>
       </c>
       <c r="I58" t="n">
-        <v>2.737</v>
+        <v>3.208</v>
       </c>
       <c r="J58" t="n">
-        <v>2.737</v>
+        <v>3.208</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5866,20 +5866,20 @@
         <v>2.641</v>
       </c>
       <c r="N58" t="n">
+        <v>98610</v>
+      </c>
+      <c r="O58" t="n">
         <v>101214.29</v>
-      </c>
-      <c r="O58" t="n">
-        <v>103887.36</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -5888,28 +5888,28 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H59" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="I59" t="n">
-        <v>1392.7</v>
+        <v>2.737</v>
       </c>
       <c r="J59" t="n">
-        <v>1403</v>
+        <v>2.737</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5917,16 +5917,16 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.5059</v>
+        <v>1.9</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3.4832</v>
+        <v>2.641</v>
       </c>
       <c r="N59" t="n">
-        <v>100000</v>
+        <v>101214.29</v>
       </c>
       <c r="O59" t="n">
-        <v>103483.18</v>
+        <v>103887.36</v>
       </c>
     </row>
     <row r="60">
@@ -5936,7 +5936,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -5945,28 +5945,28 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H60" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="I60" t="n">
-        <v>1181.4</v>
+        <v>1392.7</v>
       </c>
       <c r="J60" t="n">
-        <v>1181.4</v>
+        <v>1403</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5974,56 +5974,56 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.9</v>
+        <v>2.5059</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2.641</v>
+        <v>3.4832</v>
       </c>
       <c r="N60" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O60" t="n">
         <v>103483.18</v>
-      </c>
-      <c r="O60" t="n">
-        <v>106216.17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H61" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="I61" t="n">
-        <v>2029.3</v>
+        <v>1181.4</v>
       </c>
       <c r="J61" t="n">
-        <v>2029.3</v>
+        <v>1181.4</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -6037,67 +6037,50 @@
         <v>2.641</v>
       </c>
       <c r="N61" t="n">
-        <v>100000</v>
+        <v>103483.18</v>
       </c>
       <c r="O61" t="n">
-        <v>102641</v>
+        <v>106216.17</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>1</v>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G62" t="n">
-        <v>1641.5</v>
+        <v>1386.6</v>
       </c>
       <c r="H62" t="n">
-        <v>1621</v>
+        <v>1412.1</v>
       </c>
       <c r="I62" t="n">
-        <v>1680.5</v>
-      </c>
-      <c r="J62" t="n">
-        <v>1621</v>
+        <v>1338.1</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v>-1.39</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N62" t="n">
-        <v>102641</v>
+        <v>106216.17</v>
       </c>
       <c r="O62" t="n">
-        <v>101214.29</v>
+        <v>106216.17</v>
       </c>
     </row>
     <row r="63">
@@ -6107,37 +6090,37 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>1581.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H63" t="n">
-        <v>1547.6</v>
+        <v>2113.7</v>
       </c>
       <c r="I63" t="n">
-        <v>1645.9</v>
+        <v>2029.3</v>
       </c>
       <c r="J63" t="n">
-        <v>1645.9</v>
+        <v>2029.3</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -6151,10 +6134,10 @@
         <v>2.641</v>
       </c>
       <c r="N63" t="n">
-        <v>101214.29</v>
+        <v>100000</v>
       </c>
       <c r="O63" t="n">
-        <v>103887.36</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="64">
@@ -6164,7 +6147,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -6173,45 +6156,45 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>1559</v>
+        <v>1641.5</v>
       </c>
       <c r="H64" t="n">
-        <v>1539.5</v>
+        <v>1621</v>
       </c>
       <c r="I64" t="n">
-        <v>1596</v>
+        <v>1680.5</v>
       </c>
       <c r="J64" t="n">
-        <v>1596</v>
+        <v>1621</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M64" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N64" t="n">
-        <v>103887.36</v>
+        <v>102641</v>
       </c>
       <c r="O64" t="n">
-        <v>106631.02</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="65">
@@ -6221,101 +6204,121 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>1769.6</v>
+        <v>1581.5</v>
       </c>
       <c r="H65" t="n">
-        <v>1798.4</v>
+        <v>1547.6</v>
       </c>
       <c r="I65" t="n">
-        <v>1714.9</v>
+        <v>1645.9</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1645.9</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N65" t="n">
-        <v>106631.02</v>
+        <v>101214.29</v>
       </c>
       <c r="O65" t="n">
-        <v>106631.02</v>
+        <v>103887.36</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>27907</v>
+        <v>1559</v>
       </c>
       <c r="H66" t="n">
-        <v>27965.76</v>
+        <v>1539.5</v>
       </c>
       <c r="I66" t="n">
-        <v>27795.36</v>
+        <v>1596</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1596</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v>-1.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N66" t="n">
-        <v>100000</v>
+        <v>103887.36</v>
       </c>
       <c r="O66" t="n">
-        <v>98610</v>
+        <v>106631.02</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -6327,48 +6330,31 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
       <c r="G67" t="n">
-        <v>29892.8</v>
+        <v>1769.6</v>
       </c>
       <c r="H67" t="n">
-        <v>30074.01</v>
+        <v>1798.4</v>
       </c>
       <c r="I67" t="n">
-        <v>29548.5</v>
-      </c>
-      <c r="J67" t="n">
-        <v>29548.5</v>
+        <v>1714.9</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>target_r</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M67" s="2" t="n">
-        <v>2.641</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N67" t="n">
-        <v>98610</v>
+        <v>106631.02</v>
       </c>
       <c r="O67" t="n">
-        <v>101214.29</v>
+        <v>106631.02</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -6381,51 +6367,48 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>7206.55</v>
+        <v>27907</v>
       </c>
       <c r="H68" t="n">
-        <v>7223.26</v>
+        <v>27965.76</v>
       </c>
       <c r="I68" t="n">
-        <v>7174.8</v>
-      </c>
-      <c r="J68" t="n">
-        <v>7174.8</v>
+        <v>27795.36</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M68" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M68" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N68" t="n">
         <v>100000</v>
       </c>
       <c r="O68" t="n">
-        <v>102641</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -6441,31 +6424,48 @@
           <t>2026-08-05</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
       <c r="G69" t="n">
-        <v>7773</v>
+        <v>29892.8</v>
       </c>
       <c r="H69" t="n">
-        <v>7820.26</v>
+        <v>30074.01</v>
       </c>
       <c r="I69" t="n">
-        <v>7683.21</v>
+        <v>29548.5</v>
+      </c>
+      <c r="J69" t="n">
+        <v>29548.5</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N69" t="n">
-        <v>102641</v>
+        <v>98610</v>
       </c>
       <c r="O69" t="n">
-        <v>102641</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -6478,28 +6478,28 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>6957.43</v>
+        <v>7206.55</v>
       </c>
       <c r="H70" t="n">
-        <v>6965.7</v>
+        <v>7223.26</v>
       </c>
       <c r="I70" t="n">
-        <v>6941.72</v>
+        <v>7174.8</v>
       </c>
       <c r="J70" t="n">
-        <v>6941.72</v>
+        <v>7174.8</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -6535,45 +6535,28 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="G71" t="n">
-        <v>6982.4</v>
+        <v>7773</v>
       </c>
       <c r="H71" t="n">
-        <v>6988.83</v>
+        <v>7820.26</v>
       </c>
       <c r="I71" t="n">
-        <v>6970.18</v>
-      </c>
-      <c r="J71" t="n">
-        <v>7002</v>
+        <v>7683.21</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L71" t="n">
-        <v>-3.0482</v>
-      </c>
-      <c r="M71" s="5" t="n">
-        <v>-4.237</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N71" t="n">
         <v>102641</v>
       </c>
       <c r="O71" t="n">
-        <v>98292.09</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="72">
@@ -6583,7 +6566,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -6592,28 +6575,28 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H72" t="n">
-        <v>6992.85</v>
+        <v>6965.7</v>
       </c>
       <c r="I72" t="n">
-        <v>6962.54</v>
+        <v>6941.72</v>
       </c>
       <c r="J72" t="n">
-        <v>6947.27</v>
+        <v>6941.72</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6621,16 +6604,16 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.3617</v>
+        <v>1.9</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>4.6728</v>
+        <v>2.641</v>
       </c>
       <c r="N72" t="n">
-        <v>98292.09</v>
+        <v>100000</v>
       </c>
       <c r="O72" t="n">
-        <v>102885.07</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="73">
@@ -6640,7 +6623,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -6649,12 +6632,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -6664,27 +6647,30 @@
         <v>6982.4</v>
       </c>
       <c r="H73" t="n">
-        <v>6991.93</v>
+        <v>6988.83</v>
       </c>
       <c r="I73" t="n">
-        <v>6964.29</v>
+        <v>6970.18</v>
+      </c>
+      <c r="J73" t="n">
+        <v>7002</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>-1.39</v>
+        <v>-4.237</v>
       </c>
       <c r="N73" t="n">
-        <v>102885.07</v>
+        <v>102641</v>
       </c>
       <c r="O73" t="n">
-        <v>101454.97</v>
+        <v>98292.09</v>
       </c>
     </row>
     <row r="74">
@@ -6694,7 +6680,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -6703,12 +6689,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -6718,27 +6704,30 @@
         <v>6982.4</v>
       </c>
       <c r="H74" t="n">
-        <v>6986.84</v>
+        <v>6992.85</v>
       </c>
       <c r="I74" t="n">
-        <v>6973.96</v>
+        <v>6962.54</v>
+      </c>
+      <c r="J74" t="n">
+        <v>6947.27</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v>-1.39</v>
+        <v>3.3617</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>4.6728</v>
       </c>
       <c r="N74" t="n">
-        <v>101454.97</v>
+        <v>98292.09</v>
       </c>
       <c r="O74" t="n">
-        <v>100044.75</v>
+        <v>102885.07</v>
       </c>
     </row>
     <row r="75">
@@ -6748,64 +6737,61 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H75" t="n">
-        <v>6770.77</v>
+        <v>6991.93</v>
       </c>
       <c r="I75" t="n">
-        <v>6839.3</v>
-      </c>
-      <c r="J75" t="n">
-        <v>6769.03</v>
+        <v>6964.29</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-1.0736</v>
+        <v>-1</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>-1.4924</v>
+        <v>-1.39</v>
       </c>
       <c r="N75" t="n">
-        <v>100044.75</v>
+        <v>102885.07</v>
       </c>
       <c r="O75" t="n">
-        <v>98551.73</v>
+        <v>101454.97</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -6814,32 +6800,29 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H76" t="n">
-        <v>88.001</v>
+        <v>6986.84</v>
       </c>
       <c r="I76" t="n">
-        <v>82.43300000000001</v>
-      </c>
-      <c r="J76" t="n">
-        <v>88.001</v>
+        <v>6973.96</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -6849,20 +6832,20 @@
         <v>-1.39</v>
       </c>
       <c r="N76" t="n">
-        <v>100000</v>
+        <v>101454.97</v>
       </c>
       <c r="O76" t="n">
-        <v>98610</v>
+        <v>100044.75</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -6871,51 +6854,51 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>73.84399999999999</v>
+        <v>6794.4</v>
       </c>
       <c r="H77" t="n">
-        <v>71.999</v>
+        <v>6770.77</v>
       </c>
       <c r="I77" t="n">
-        <v>77.349</v>
+        <v>6839.3</v>
       </c>
       <c r="J77" t="n">
-        <v>77.349</v>
+        <v>6769.03</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M77" s="2" t="n">
-        <v>2.641</v>
+        <v>-1.0736</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>-1.4924</v>
       </c>
       <c r="N77" t="n">
-        <v>98610</v>
+        <v>100044.75</v>
       </c>
       <c r="O77" t="n">
-        <v>101214.29</v>
+        <v>98551.73</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -6928,28 +6911,28 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>15</v>
+        <v>86.081</v>
       </c>
       <c r="H78" t="n">
-        <v>15.26</v>
+        <v>88.001</v>
       </c>
       <c r="I78" t="n">
-        <v>14.51</v>
+        <v>82.43300000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>15.26</v>
+        <v>88.001</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6972,64 +6955,64 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" t="n">
-        <v>20.89</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>21.07</v>
+        <v>71.999</v>
       </c>
       <c r="I79" t="n">
-        <v>20.55</v>
+        <v>77.349</v>
       </c>
       <c r="J79" t="n">
-        <v>21.08</v>
+        <v>77.349</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-1.0556</v>
-      </c>
-      <c r="M79" s="5" t="n">
-        <v>-1.4672</v>
+        <v>1.9</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N79" t="n">
-        <v>100000</v>
+        <v>98610</v>
       </c>
       <c r="O79" t="n">
-        <v>98532.78</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -7042,28 +7025,28 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G80" t="n">
-        <v>0.8614000000000001</v>
+        <v>15</v>
       </c>
       <c r="H80" t="n">
-        <v>0.8637</v>
+        <v>15.26</v>
       </c>
       <c r="I80" t="n">
-        <v>0.857</v>
+        <v>14.51</v>
       </c>
       <c r="J80" t="n">
-        <v>0.8637</v>
+        <v>15.26</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -7086,11 +7069,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -7099,28 +7082,28 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.8614000000000001</v>
+        <v>20.89</v>
       </c>
       <c r="H81" t="n">
-        <v>0.8658</v>
+        <v>21.07</v>
       </c>
       <c r="I81" t="n">
-        <v>0.853</v>
+        <v>20.55</v>
       </c>
       <c r="J81" t="n">
-        <v>0.8658</v>
+        <v>21.08</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -7128,16 +7111,16 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>-1.39</v>
+        <v>-1.4672</v>
       </c>
       <c r="N81" t="n">
-        <v>98610</v>
+        <v>100000</v>
       </c>
       <c r="O81" t="n">
-        <v>97239.32000000001</v>
+        <v>98532.78</v>
       </c>
     </row>
     <row r="82">
@@ -7147,64 +7130,64 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.8467</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>0.8436</v>
+        <v>0.8637</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8526</v>
+        <v>0.857</v>
       </c>
       <c r="J82" t="n">
-        <v>0.8498</v>
+        <v>0.8637</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>1.39</v>
+        <v>-1</v>
+      </c>
+      <c r="M82" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N82" t="n">
-        <v>97239.32000000001</v>
+        <v>100000</v>
       </c>
       <c r="O82" t="n">
-        <v>98590.95</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -7213,28 +7196,28 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>116.5</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H83" t="n">
-        <v>116.79</v>
+        <v>0.8658</v>
       </c>
       <c r="I83" t="n">
-        <v>115.95</v>
+        <v>0.853</v>
       </c>
       <c r="J83" t="n">
-        <v>116.79</v>
+        <v>0.8658</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7248,67 +7231,67 @@
         <v>-1.39</v>
       </c>
       <c r="N83" t="n">
-        <v>100000</v>
+        <v>98610</v>
       </c>
       <c r="O83" t="n">
-        <v>98610</v>
+        <v>97239.32000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>118.02</v>
+        <v>0.8467</v>
       </c>
       <c r="H84" t="n">
-        <v>118.16</v>
+        <v>0.8436</v>
       </c>
       <c r="I84" t="n">
-        <v>117.75</v>
+        <v>0.8526</v>
       </c>
       <c r="J84" t="n">
-        <v>117.75</v>
+        <v>0.8498</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2.641</v>
+        <v>1.39</v>
       </c>
       <c r="N84" t="n">
-        <v>98610</v>
+        <v>97239.32000000001</v>
       </c>
       <c r="O84" t="n">
-        <v>101214.29</v>
+        <v>98590.95</v>
       </c>
     </row>
     <row r="85">
@@ -7318,7 +7301,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -7327,29 +7310,32 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>118.08</v>
+        <v>116.5</v>
       </c>
       <c r="H85" t="n">
-        <v>118.16</v>
+        <v>116.79</v>
       </c>
       <c r="I85" t="n">
-        <v>117.93</v>
+        <v>115.95</v>
+      </c>
+      <c r="J85" t="n">
+        <v>116.79</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -7359,50 +7345,50 @@
         <v>-1.39</v>
       </c>
       <c r="N85" t="n">
-        <v>101214.29</v>
+        <v>100000</v>
       </c>
       <c r="O85" t="n">
-        <v>99807.41</v>
+        <v>98610</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>97.81399999999999</v>
+        <v>118.02</v>
       </c>
       <c r="H86" t="n">
-        <v>97.569</v>
+        <v>118.16</v>
       </c>
       <c r="I86" t="n">
-        <v>98.279</v>
+        <v>117.75</v>
       </c>
       <c r="J86" t="n">
-        <v>98.279</v>
+        <v>117.75</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7416,67 +7402,64 @@
         <v>2.641</v>
       </c>
       <c r="N86" t="n">
-        <v>100000</v>
+        <v>98610</v>
       </c>
       <c r="O86" t="n">
-        <v>102641</v>
+        <v>101214.29</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>97.714</v>
+        <v>118.08</v>
       </c>
       <c r="H87" t="n">
-        <v>97.46899999999999</v>
+        <v>118.16</v>
       </c>
       <c r="I87" t="n">
-        <v>98.18000000000001</v>
-      </c>
-      <c r="J87" t="n">
-        <v>98.18000000000001</v>
+        <v>117.93</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M87" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M87" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N87" t="n">
-        <v>102641</v>
+        <v>101214.29</v>
       </c>
       <c r="O87" t="n">
-        <v>105351.75</v>
+        <v>99807.41</v>
       </c>
     </row>
     <row r="88">
@@ -7486,37 +7469,37 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>99.376</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>99.571</v>
+        <v>97.569</v>
       </c>
       <c r="I88" t="n">
-        <v>99.006</v>
+        <v>98.279</v>
       </c>
       <c r="J88" t="n">
-        <v>99.006</v>
+        <v>98.279</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7530,10 +7513,10 @@
         <v>2.641</v>
       </c>
       <c r="N88" t="n">
-        <v>105351.75</v>
+        <v>100000</v>
       </c>
       <c r="O88" t="n">
-        <v>108134.09</v>
+        <v>102641</v>
       </c>
     </row>
     <row r="89">
@@ -7543,54 +7526,54 @@
         </is>
       </c>
       <c r="B89" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
         <v>4</v>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>3</v>
-      </c>
       <c r="G89" t="n">
-        <v>99.246</v>
+        <v>97.714</v>
       </c>
       <c r="H89" t="n">
-        <v>99.501</v>
+        <v>97.46899999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>98.761</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>99.501</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M89" s="5" t="n">
-        <v>-1.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N89" t="n">
-        <v>108134.09</v>
+        <v>102641</v>
       </c>
       <c r="O89" t="n">
-        <v>106631.02</v>
+        <v>105351.75</v>
       </c>
     </row>
     <row r="90">
@@ -7600,7 +7583,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -7609,28 +7592,28 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G90" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H90" t="n">
-        <v>100.201</v>
+        <v>99.571</v>
       </c>
       <c r="I90" t="n">
-        <v>99.809</v>
+        <v>99.006</v>
       </c>
       <c r="J90" t="n">
-        <v>99.809</v>
+        <v>99.006</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7644,10 +7627,10 @@
         <v>2.641</v>
       </c>
       <c r="N90" t="n">
-        <v>106631.02</v>
+        <v>105351.75</v>
       </c>
       <c r="O90" t="n">
-        <v>109447.15</v>
+        <v>108134.09</v>
       </c>
     </row>
     <row r="91">
@@ -7657,7 +7640,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -7666,45 +7649,45 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G91" t="n">
-        <v>100.066</v>
+        <v>99.246</v>
       </c>
       <c r="H91" t="n">
-        <v>100.316</v>
+        <v>99.501</v>
       </c>
       <c r="I91" t="n">
-        <v>99.59099999999999</v>
+        <v>98.761</v>
       </c>
       <c r="J91" t="n">
-        <v>99.45999999999999</v>
+        <v>99.501</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.424</v>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>3.3694</v>
+        <v>-1</v>
+      </c>
+      <c r="M91" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N91" t="n">
-        <v>109447.15</v>
+        <v>108134.09</v>
       </c>
       <c r="O91" t="n">
-        <v>113134.82</v>
+        <v>106631.02</v>
       </c>
     </row>
     <row r="92">
@@ -7714,7 +7697,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -7723,12 +7706,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -7738,30 +7721,30 @@
         <v>100.066</v>
       </c>
       <c r="H92" t="n">
-        <v>100.361</v>
+        <v>100.201</v>
       </c>
       <c r="I92" t="n">
-        <v>99.505</v>
+        <v>99.809</v>
       </c>
       <c r="J92" t="n">
-        <v>100.361</v>
+        <v>99.809</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M92" s="5" t="n">
-        <v>-1.39</v>
+        <v>1.9</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>2.641</v>
       </c>
       <c r="N92" t="n">
-        <v>113134.82</v>
+        <v>106631.02</v>
       </c>
       <c r="O92" t="n">
-        <v>111562.24</v>
+        <v>109447.15</v>
       </c>
     </row>
     <row r="93">
@@ -7771,7 +7754,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -7780,45 +7763,45 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>100.621</v>
+        <v>100.066</v>
       </c>
       <c r="H93" t="n">
-        <v>100.911</v>
+        <v>100.316</v>
       </c>
       <c r="I93" t="n">
-        <v>100.07</v>
+        <v>99.59099999999999</v>
       </c>
       <c r="J93" t="n">
-        <v>100.911</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M93" s="5" t="n">
-        <v>-1.39</v>
+        <v>2.424</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>3.3694</v>
       </c>
       <c r="N93" t="n">
-        <v>111562.24</v>
+        <v>109447.15</v>
       </c>
       <c r="O93" t="n">
-        <v>110011.53</v>
+        <v>113134.82</v>
       </c>
     </row>
     <row r="94">
@@ -7828,7 +7811,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -7837,45 +7820,45 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F94" t="n">
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H94" t="n">
-        <v>101.526</v>
+        <v>100.361</v>
       </c>
       <c r="I94" t="n">
-        <v>101.192</v>
+        <v>99.505</v>
       </c>
       <c r="J94" t="n">
-        <v>101.192</v>
+        <v>100.361</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M94" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M94" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N94" t="n">
-        <v>110011.53</v>
+        <v>113134.82</v>
       </c>
       <c r="O94" t="n">
-        <v>112916.93</v>
+        <v>111562.24</v>
       </c>
     </row>
     <row r="95">
@@ -7885,7 +7868,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -7894,55 +7877,55 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95" t="n">
-        <v>101.411</v>
+        <v>100.621</v>
       </c>
       <c r="H95" t="n">
-        <v>101.491</v>
+        <v>100.911</v>
       </c>
       <c r="I95" t="n">
-        <v>101.259</v>
+        <v>100.07</v>
       </c>
       <c r="J95" t="n">
-        <v>101.259</v>
+        <v>100.911</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M95" s="2" t="n">
-        <v>2.641</v>
+        <v>-1</v>
+      </c>
+      <c r="M95" s="5" t="n">
+        <v>-1.39</v>
       </c>
       <c r="N95" t="n">
-        <v>112916.93</v>
+        <v>111562.24</v>
       </c>
       <c r="O95" t="n">
-        <v>115899.07</v>
+        <v>110011.53</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -7951,28 +7934,28 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F96" t="n">
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>121.72</v>
+        <v>101.411</v>
       </c>
       <c r="H96" t="n">
-        <v>123.03</v>
+        <v>101.526</v>
       </c>
       <c r="I96" t="n">
-        <v>119.23</v>
+        <v>101.192</v>
       </c>
       <c r="J96" t="n">
-        <v>113.29</v>
+        <v>101.192</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7980,26 +7963,26 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>6.4351</v>
+        <v>1.9</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>8.944800000000001</v>
+        <v>2.641</v>
       </c>
       <c r="N96" t="n">
-        <v>100000</v>
+        <v>110011.53</v>
       </c>
       <c r="O96" t="n">
-        <v>108944.81</v>
+        <v>112916.93</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -8008,28 +7991,28 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F97" t="n">
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>130.16</v>
+        <v>101.411</v>
       </c>
       <c r="H97" t="n">
-        <v>130.94</v>
+        <v>101.491</v>
       </c>
       <c r="I97" t="n">
-        <v>128.68</v>
+        <v>101.259</v>
       </c>
       <c r="J97" t="n">
-        <v>128.68</v>
+        <v>101.259</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -8043,9 +8026,123 @@
         <v>2.641</v>
       </c>
       <c r="N97" t="n">
+        <v>112916.93</v>
+      </c>
+      <c r="O97" t="n">
+        <v>115899.07</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H98" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="I98" t="n">
+        <v>119.23</v>
+      </c>
+      <c r="J98" t="n">
+        <v>113.29</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>6.4351</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>8.944800000000001</v>
+      </c>
+      <c r="N98" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O98" t="n">
         <v>108944.81</v>
       </c>
-      <c r="O97" t="n">
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="n">
+        <v>130.16</v>
+      </c>
+      <c r="H99" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="I99" t="n">
+        <v>128.68</v>
+      </c>
+      <c r="J99" t="n">
+        <v>128.68</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="N99" t="n">
+        <v>108944.81</v>
+      </c>
+      <c r="O99" t="n">
         <v>111822.04</v>
       </c>
     </row>
